--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D899"/>
+  <dimension ref="A1:D900"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>11885</v>
+        <v>12025</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>10685</v>
+        <v>10821</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B4">
-        <v>2083</v>
+        <v>2088</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -461,7 +461,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B5">
-        <v>2359</v>
+        <v>2449</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -489,13 +489,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B7">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C7">
         <v>14</v>
       </c>
       <c r="D7">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>combintel</v>
       </c>
       <c r="B11">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -559,13 +559,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B12">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C12">
         <v>7</v>
       </c>
       <c r="D12">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -587,7 +587,7 @@
         <v>pg_grappling</v>
       </c>
       <c r="B14">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -601,7 +601,7 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B15">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -629,7 +629,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>johnmma9</v>
       </c>
       <c r="B18">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -657,13 +657,13 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B19">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -671,10 +671,10 @@
         <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B20">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20">
         <v>57</v>
@@ -685,13 +685,13 @@
         <v>malu832757</v>
       </c>
       <c r="B21">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -780,30 +780,30 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>god.motivacao</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B28">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="C28">
-        <v>206</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>60</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>cjrnavalha</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B29">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>206</v>
       </c>
       <c r="D29">
-        <v>13</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
@@ -839,13 +839,13 @@
         <v>maxgandra</v>
       </c>
       <c r="B32">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C32">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -1228,44 +1228,44 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>_alvezbjj__</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B60">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C60">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>gustavomohallem</v>
+        <v>_alvezbjj__</v>
       </c>
       <c r="B61">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B62">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -1284,7 +1284,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>jvxz______</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B64">
         <v>14</v>
@@ -1293,35 +1293,35 @@
         <v>1</v>
       </c>
       <c r="D64">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>jujua_maral1</v>
+        <v>jvxz______</v>
       </c>
       <c r="B65">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>rayn.avaro</v>
+        <v>jujua_maral1</v>
       </c>
       <c r="B66">
         <v>13</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
@@ -1354,105 +1354,105 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ravenrodriguez___</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B69">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C69">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>marc0s.azv</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B70">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>danielbrbjj</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B71">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>danielbrbjj</v>
       </c>
       <c r="B72">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>adriano.trator</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B73">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C73">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>marcos_tailandess</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B74">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C74">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D74">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>gdazuera</v>
+        <v>im.duda02</v>
       </c>
       <c r="B75">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C75">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>anayachiottoni</v>
+        <v>n.daily22</v>
       </c>
       <c r="B76">
         <v>10</v>
@@ -1466,16 +1466,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>albertoleandromoco</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B77">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -1483,136 +1483,136 @@
         <v>arafight_pesc</v>
       </c>
       <c r="B78">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>macamariotti</v>
+        <v>gdazuera</v>
       </c>
       <c r="B79">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C79">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D79">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>luizalaguerabjj</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B80">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>cpetemma248</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B81">
         <v>9</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>edebetim_</v>
+        <v>macamariotti</v>
       </c>
       <c r="B82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C82">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D82">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>charlesduarte_mma</v>
+        <v>luizalaguerabjj</v>
       </c>
       <c r="B83">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>laisrebeiro10</v>
+        <v>cpetemma248</v>
       </c>
       <c r="B84">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D84">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>im.duda02</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B85">
         <v>8</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>dogodoyfoto</v>
+        <v>galler_peace</v>
       </c>
       <c r="B86">
+        <v>8</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
         <v>7</v>
-      </c>
-      <c r="C86">
-        <v>3</v>
-      </c>
-      <c r="D86">
-        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>propeace_fight</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B87">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>7</v>
@@ -1620,27 +1620,27 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>leozin.kick</v>
+        <v>edebetim_</v>
       </c>
       <c r="B88">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D88">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>ailinperezufc</v>
+        <v>charlesduarte_mma</v>
       </c>
       <c r="B89">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D89">
         <v>3</v>
@@ -1648,10 +1648,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>grapplerfight</v>
+        <v>laisrebeiro10</v>
       </c>
       <c r="B90">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -1662,41 +1662,41 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B91">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D91">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>diegopaivajj</v>
+        <v>leozin.kick</v>
       </c>
       <c r="B92">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>__ottonii__</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B93">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93">
         <v>3</v>
@@ -1704,55 +1704,55 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>misskelsc</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B94">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>pedro_giraldi</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B95">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C95">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B96">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>brodschack_</v>
+        <v>__ottonii__</v>
       </c>
       <c r="B97">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -1760,27 +1760,27 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>vitor_dx_mma</v>
+        <v>misskelsc</v>
       </c>
       <c r="B98">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>rrafaelins</v>
+        <v>pedro_giraldi</v>
       </c>
       <c r="B99">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C99">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D99">
         <v>5</v>
@@ -1788,83 +1788,83 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>thundergrapple</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B100">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>galler_peace</v>
+        <v>brodschack_</v>
       </c>
       <c r="B101">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D101">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>figh_grappler</v>
+        <v>vitor_dx_mma</v>
       </c>
       <c r="B102">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>eolucasrosa</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B103">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D103">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>_oliveira09_</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B104">
         <v>7</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D104">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>badboykillermma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B105">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D105">
         <v>4</v>
@@ -1872,27 +1872,27 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B106">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>cayan.pascoalbjj</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B107">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C107">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -1900,35 +1900,35 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>juniordiasmma</v>
+        <v>cayan.pascoalbjj</v>
       </c>
       <c r="B108">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>janders0202</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B109">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>fabio_gb_</v>
+        <v>janders0202</v>
       </c>
       <c r="B110">
         <v>5</v>
@@ -1937,77 +1937,77 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>alfredo_miras</v>
+        <v>fabio_gb_</v>
       </c>
       <c r="B111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>mimuniz.bjj</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B112">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C112">
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>lucascardosol__</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C113">
         <v>0</v>
       </c>
       <c r="D113">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>biabasiliojj</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B114">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>n.daily22</v>
+        <v>biabasiliojj</v>
       </c>
       <c r="B115">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -10202,7 +10202,7 @@
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>alineanne_</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B701">
         <v>0</v>
@@ -10211,12 +10211,12 @@
         <v>1</v>
       </c>
       <c r="D701">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B702">
         <v>0</v>
@@ -10230,7 +10230,7 @@
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B703">
         <v>0</v>
@@ -10244,7 +10244,7 @@
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B704">
         <v>0</v>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B705">
         <v>0</v>
@@ -10272,7 +10272,7 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B706">
         <v>0</v>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B707">
         <v>0</v>
@@ -10300,7 +10300,7 @@
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B708">
         <v>0</v>
@@ -10314,7 +10314,7 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B709">
         <v>0</v>
@@ -10328,7 +10328,7 @@
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B710">
         <v>0</v>
@@ -10342,7 +10342,7 @@
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B711">
         <v>0</v>
@@ -10356,7 +10356,7 @@
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B712">
         <v>0</v>
@@ -10370,7 +10370,7 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B713">
         <v>0</v>
@@ -10384,7 +10384,7 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B714">
         <v>0</v>
@@ -10398,7 +10398,7 @@
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B715">
         <v>0</v>
@@ -10412,7 +10412,7 @@
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B716">
         <v>0</v>
@@ -10426,7 +10426,7 @@
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B717">
         <v>0</v>
@@ -10440,7 +10440,7 @@
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B718">
         <v>0</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B719">
         <v>0</v>
@@ -10468,7 +10468,7 @@
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B720">
         <v>0</v>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B721">
         <v>0</v>
@@ -10496,7 +10496,7 @@
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B722">
         <v>0</v>
@@ -10510,7 +10510,7 @@
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B723">
         <v>0</v>
@@ -10524,7 +10524,7 @@
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B724">
         <v>0</v>
@@ -10538,7 +10538,7 @@
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B725">
         <v>0</v>
@@ -10552,7 +10552,7 @@
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B726">
         <v>0</v>
@@ -10566,7 +10566,7 @@
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B727">
         <v>0</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B728">
         <v>0</v>
@@ -10594,7 +10594,7 @@
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B729">
         <v>0</v>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B730">
         <v>0</v>
@@ -10622,7 +10622,7 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>romulerasilva</v>
+        <v>roginbrito</v>
       </c>
       <c r="B731">
         <v>0</v>
@@ -10636,7 +10636,7 @@
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>higorsaantana</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B732">
         <v>0</v>
@@ -10650,7 +10650,7 @@
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>vitorcosta_mma</v>
+        <v>higorsaantana</v>
       </c>
       <c r="B733">
         <v>0</v>
@@ -10664,7 +10664,7 @@
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>paulo.titoo</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B734">
         <v>0</v>
@@ -10678,7 +10678,7 @@
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>1000ton_n</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B735">
         <v>0</v>
@@ -10692,7 +10692,7 @@
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>strong_stg_oficial</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B736">
         <v>0</v>
@@ -10706,7 +10706,7 @@
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B737">
         <v>0</v>
@@ -10720,7 +10720,7 @@
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B738">
         <v>0</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B739">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B740">
         <v>0</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>caioparangole</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B741">
         <v>0</v>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B742">
         <v>0</v>
@@ -10790,7 +10790,7 @@
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B743">
         <v>0</v>
@@ -10804,7 +10804,7 @@
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B744">
         <v>0</v>
@@ -10818,7 +10818,7 @@
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B745">
         <v>0</v>
@@ -10832,7 +10832,7 @@
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B746">
         <v>0</v>
@@ -10846,7 +10846,7 @@
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B747">
         <v>0</v>
@@ -10860,7 +10860,7 @@
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>cristianomarcello</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B748">
         <v>0</v>
@@ -10874,7 +10874,7 @@
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>dandraco_</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B749">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B750">
         <v>0</v>
@@ -10902,7 +10902,7 @@
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B751">
         <v>0</v>
@@ -10916,7 +10916,7 @@
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B752">
         <v>0</v>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B753">
         <v>0</v>
@@ -10944,7 +10944,7 @@
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B754">
         <v>0</v>
@@ -10958,7 +10958,7 @@
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>geanne_franca_</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B755">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>vanemessina</v>
+        <v>geanne_franca_</v>
       </c>
       <c r="B756">
         <v>0</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B757">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>esteticaluharruda</v>
+        <v>dadwillians</v>
       </c>
       <c r="B758">
         <v>0</v>
@@ -11014,7 +11014,7 @@
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B759">
         <v>0</v>
@@ -11028,7 +11028,7 @@
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>_kainanlima</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B760">
         <v>0</v>
@@ -11042,7 +11042,7 @@
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B761">
         <v>0</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B762">
         <v>0</v>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B763">
         <v>0</v>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B764">
         <v>0</v>
@@ -11098,7 +11098,7 @@
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>rafaelbipolarufc</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B765">
         <v>0</v>
@@ -11112,7 +11112,7 @@
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>martinpakciarz</v>
+        <v>rafaelbipolarufc</v>
       </c>
       <c r="B766">
         <v>0</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>andrearschack</v>
+        <v>martinpakciarz</v>
       </c>
       <c r="B767">
         <v>0</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>leziamorbeck50</v>
+        <v>andrearschack</v>
       </c>
       <c r="B768">
         <v>0</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>meirelesmma</v>
+        <v>leziamorbeck50</v>
       </c>
       <c r="B769">
         <v>0</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>teamsilverio</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B770">
         <v>0</v>
@@ -11182,7 +11182,7 @@
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>tatiaradias</v>
+        <v>teamsilverio</v>
       </c>
       <c r="B771">
         <v>0</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>daniloacordeon_oficial</v>
+        <v>tatiaradias</v>
       </c>
       <c r="B772">
         <v>0</v>
@@ -11210,7 +11210,7 @@
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>thiagopssantos</v>
+        <v>daniloacordeon_oficial</v>
       </c>
       <c r="B773">
         <v>0</v>
@@ -11224,7 +11224,7 @@
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>leafarlemos</v>
+        <v>thiagopssantos</v>
       </c>
       <c r="B774">
         <v>0</v>
@@ -11238,7 +11238,7 @@
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>miltoncjr28</v>
+        <v>leafarlemos</v>
       </c>
       <c r="B775">
         <v>0</v>
@@ -11252,7 +11252,7 @@
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>almeidajjwk</v>
+        <v>miltoncjr28</v>
       </c>
       <c r="B776">
         <v>0</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>soniarmurata</v>
+        <v>almeidajjwk</v>
       </c>
       <c r="B777">
         <v>0</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>foryousaudeespecializada</v>
+        <v>soniarmurata</v>
       </c>
       <c r="B778">
         <v>0</v>
@@ -11294,7 +11294,7 @@
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>marques.__bjj</v>
+        <v>foryousaudeespecializada</v>
       </c>
       <c r="B779">
         <v>0</v>
@@ -11308,7 +11308,7 @@
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>ryu_artes_marciais</v>
+        <v>marques.__bjj</v>
       </c>
       <c r="B780">
         <v>0</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>dorgivan13_bjj</v>
+        <v>ryu_artes_marciais</v>
       </c>
       <c r="B781">
         <v>0</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>ayman__falil_06</v>
+        <v>dorgivan13_bjj</v>
       </c>
       <c r="B782">
         <v>0</v>
@@ -11350,7 +11350,7 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>otaviocarneiromma</v>
+        <v>ayman__falil_06</v>
       </c>
       <c r="B783">
         <v>0</v>
@@ -11364,7 +11364,7 @@
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>dvlucc2k26_</v>
+        <v>otaviocarneiromma</v>
       </c>
       <c r="B784">
         <v>0</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>thayanne_rodrigues_bjj</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B785">
         <v>0</v>
@@ -11392,7 +11392,7 @@
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>lurochachef</v>
+        <v>thayanne_rodrigues_bjj</v>
       </c>
       <c r="B786">
         <v>0</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>viniciusmorais.bjj</v>
+        <v>lurochachef</v>
       </c>
       <c r="B787">
         <v>0</v>
@@ -11420,7 +11420,7 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>mauriciogeorge</v>
+        <v>viniciusmorais.bjj</v>
       </c>
       <c r="B788">
         <v>0</v>
@@ -11434,7 +11434,7 @@
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>gisbedejose</v>
+        <v>mauriciogeorge</v>
       </c>
       <c r="B789">
         <v>0</v>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>laureanucalvo</v>
+        <v>gisbedejose</v>
       </c>
       <c r="B790">
         <v>0</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>galindofrontado</v>
+        <v>laureanucalvo</v>
       </c>
       <c r="B791">
         <v>0</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>chalakakavinda</v>
+        <v>galindofrontado</v>
       </c>
       <c r="B792">
         <v>0</v>
@@ -11490,7 +11490,7 @@
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>gandrapaulino</v>
+        <v>chalakakavinda</v>
       </c>
       <c r="B793">
         <v>0</v>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>pgmarquesantos</v>
+        <v>gandrapaulino</v>
       </c>
       <c r="B794">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>uluukyrgyz_tima</v>
+        <v>pgmarquesantos</v>
       </c>
       <c r="B795">
         <v>0</v>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>kells2vallone</v>
+        <v>uluukyrgyz_tima</v>
       </c>
       <c r="B796">
         <v>0</v>
@@ -11546,7 +11546,7 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>personaljakeline</v>
+        <v>kells2vallone</v>
       </c>
       <c r="B797">
         <v>0</v>
@@ -11560,7 +11560,7 @@
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>bjjfalkenberg</v>
+        <v>personaljakeline</v>
       </c>
       <c r="B798">
         <v>0</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>sergiorenatocruz1</v>
+        <v>bjjfalkenberg</v>
       </c>
       <c r="B799">
         <v>0</v>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>marcaojudobjjmaster</v>
+        <v>sergiorenatocruz1</v>
       </c>
       <c r="B800">
         <v>0</v>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>indio_mma</v>
+        <v>marcaojudobjjmaster</v>
       </c>
       <c r="B801">
         <v>0</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>covil.045</v>
+        <v>indio_mma</v>
       </c>
       <c r="B802">
         <v>0</v>
@@ -11630,7 +11630,7 @@
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>allandelano</v>
+        <v>covil.045</v>
       </c>
       <c r="B803">
         <v>0</v>
@@ -11644,7 +11644,7 @@
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>alomaraujo</v>
+        <v>allandelano</v>
       </c>
       <c r="B804">
         <v>0</v>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>theanimallifemovement</v>
+        <v>alomaraujo</v>
       </c>
       <c r="B805">
         <v>0</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>tombg_64</v>
+        <v>theanimallifemovement</v>
       </c>
       <c r="B806">
         <v>0</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>michaeloliveiramma</v>
+        <v>tombg_64</v>
       </c>
       <c r="B807">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>andreichubotaru94</v>
+        <v>michaeloliveiramma</v>
       </c>
       <c r="B808">
         <v>0</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>carinhakkz</v>
+        <v>andreichubotaru94</v>
       </c>
       <c r="B809">
         <v>0</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>helaynecrisl</v>
+        <v>carinhakkz</v>
       </c>
       <c r="B810">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>oliveiraa_00.11</v>
+        <v>helaynecrisl</v>
       </c>
       <c r="B811">
         <v>0</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>udilimaheroi</v>
+        <v>oliveiraa_00.11</v>
       </c>
       <c r="B812">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>mirnacaroline</v>
+        <v>udilimaheroi</v>
       </c>
       <c r="B813">
         <v>0</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>lmk_sport</v>
+        <v>mirnacaroline</v>
       </c>
       <c r="B814">
         <v>0</v>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>fher.nando_</v>
+        <v>lmk_sport</v>
       </c>
       <c r="B815">
         <v>0</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B816">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>adrianaramosalvesribeiro</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B817">
         <v>0</v>
@@ -11840,7 +11840,7 @@
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>djuliaarianamma</v>
+        <v>adrianaramosalvesribeiro</v>
       </c>
       <c r="B818">
         <v>0</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>raulbasilioo</v>
+        <v>djuliaarianamma</v>
       </c>
       <c r="B819">
         <v>0</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>heloisa_elohim</v>
+        <v>raulbasilioo</v>
       </c>
       <c r="B820">
         <v>0</v>
@@ -11882,7 +11882,7 @@
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>hostonhugo</v>
+        <v>heloisa_elohim</v>
       </c>
       <c r="B821">
         <v>0</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>ellida_guimaraes</v>
+        <v>hostonhugo</v>
       </c>
       <c r="B822">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>massoterapeuta_bemestarr</v>
+        <v>ellida_guimaraes</v>
       </c>
       <c r="B823">
         <v>0</v>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>alexandrefideliis</v>
+        <v>massoterapeuta_bemestarr</v>
       </c>
       <c r="B824">
         <v>0</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>pammygaryo</v>
+        <v>alexandrefideliis</v>
       </c>
       <c r="B825">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>beatrizosilveira</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B826">
         <v>0</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>bastazinifilho</v>
+        <v>beatrizosilveira</v>
       </c>
       <c r="B827">
         <v>0</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>sem_saida.12</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B828">
         <v>0</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>sougustavorosa</v>
+        <v>sem_saida.12</v>
       </c>
       <c r="B829">
         <v>0</v>
@@ -12008,7 +12008,7 @@
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>lincoln__puig77</v>
+        <v>sougustavorosa</v>
       </c>
       <c r="B830">
         <v>0</v>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>anselmo.azevedo</v>
+        <v>lincoln__puig77</v>
       </c>
       <c r="B831">
         <v>0</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B832">
         <v>0</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B833">
         <v>0</v>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B834">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B835">
         <v>0</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>marcusvgsz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B836">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B837">
         <v>0</v>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B838">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B839">
         <v>0</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B840">
         <v>0</v>
@@ -12162,7 +12162,7 @@
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B841">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B842">
         <v>0</v>
@@ -12190,7 +12190,7 @@
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>pepefightteam</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B843">
         <v>0</v>
@@ -12204,7 +12204,7 @@
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>danieldias7s</v>
+        <v>pepefightteam</v>
       </c>
       <c r="B844">
         <v>0</v>
@@ -12218,7 +12218,7 @@
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B845">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B846">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B847">
         <v>0</v>
@@ -12260,7 +12260,7 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B848">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B849">
         <v>0</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>mma.fisio</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B850">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>thaynara_victoria_</v>
+        <v>mma.fisio</v>
       </c>
       <c r="B851">
         <v>0</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>tamarapq</v>
+        <v>thaynara_victoria_</v>
       </c>
       <c r="B852">
         <v>0</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>wendel_bjj14</v>
+        <v>tamarapq</v>
       </c>
       <c r="B853">
         <v>0</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B854">
         <v>0</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B855">
         <v>0</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B856">
         <v>0</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B857">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B858">
         <v>0</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B859">
         <v>0</v>
@@ -12428,7 +12428,7 @@
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B860">
         <v>0</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B861">
         <v>0</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B862">
         <v>0</v>
@@ -12470,7 +12470,7 @@
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>danielplayboymt</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B863">
         <v>0</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>fix.pec</v>
+        <v>danielplayboymt</v>
       </c>
       <c r="B864">
         <v>0</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>chunco_424</v>
+        <v>fix.pec</v>
       </c>
       <c r="B865">
         <v>0</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>denisalagoanobjj</v>
+        <v>chunco_424</v>
       </c>
       <c r="B866">
         <v>0</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>priscilaapbatista</v>
+        <v>denisalagoanobjj</v>
       </c>
       <c r="B867">
         <v>0</v>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>josita_bjj</v>
+        <v>priscilaapbatista</v>
       </c>
       <c r="B868">
         <v>0</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>roxostrike</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B869">
         <v>0</v>
@@ -12568,7 +12568,7 @@
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>shirleypalestrina6</v>
+        <v>roxostrike</v>
       </c>
       <c r="B870">
         <v>0</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>flipebiano</v>
+        <v>shirleypalestrina6</v>
       </c>
       <c r="B871">
         <v>0</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>ruanmiqueias</v>
+        <v>flipebiano</v>
       </c>
       <c r="B872">
         <v>0</v>
@@ -12610,7 +12610,7 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>babimaciel1</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B873">
         <v>0</v>
@@ -12624,7 +12624,7 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>manoel.brum</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B874">
         <v>0</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>horadopower</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B875">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>lyvia_genuina</v>
+        <v>horadopower</v>
       </c>
       <c r="B876">
         <v>0</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>delariva_belem</v>
+        <v>lyvia_genuina</v>
       </c>
       <c r="B877">
         <v>0</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>juugxmes</v>
+        <v>delariva_belem</v>
       </c>
       <c r="B878">
         <v>0</v>
@@ -12694,7 +12694,7 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>gabrielsantosufc_</v>
+        <v>juugxmes</v>
       </c>
       <c r="B879">
         <v>0</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>_matheustiberio</v>
+        <v>gabrielsantosufc_</v>
       </c>
       <c r="B880">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>sthefany_ochoao</v>
+        <v>_matheustiberio</v>
       </c>
       <c r="B881">
         <v>0</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>reynitaoblitasbustamante</v>
+        <v>sthefany_ochoao</v>
       </c>
       <c r="B882">
         <v>0</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>joseochoa.mma</v>
+        <v>reynitaoblitasbustamante</v>
       </c>
       <c r="B883">
         <v>0</v>
@@ -12764,7 +12764,7 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>gabriellb.andrade</v>
+        <v>joseochoa.mma</v>
       </c>
       <c r="B884">
         <v>0</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>romelluistro</v>
+        <v>gabriellb.andrade</v>
       </c>
       <c r="B885">
         <v>0</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>yuricapelasso</v>
+        <v>romelluistro</v>
       </c>
       <c r="B886">
         <v>0</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>lucasfenomeno_ufc</v>
+        <v>yuricapelasso</v>
       </c>
       <c r="B887">
         <v>0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>gabriell_marcus</v>
+        <v>lucasfenomeno_ufc</v>
       </c>
       <c r="B888">
         <v>0</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>lazyboy.ufc</v>
+        <v>gabriell_marcus</v>
       </c>
       <c r="B889">
         <v>0</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>matheusdouradomma</v>
+        <v>lazyboy.ufc</v>
       </c>
       <c r="B890">
         <v>0</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>rafaelsouza7586</v>
+        <v>matheusdouradomma</v>
       </c>
       <c r="B891">
         <v>0</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>land_on_martelo_308</v>
+        <v>rafaelsouza7586</v>
       </c>
       <c r="B892">
         <v>0</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>dodge_big_johnson29</v>
+        <v>land_on_martelo_308</v>
       </c>
       <c r="B893">
         <v>0</v>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>dj__freckles</v>
+        <v>dodge_big_johnson29</v>
       </c>
       <c r="B894">
         <v>0</v>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>regis18vieira</v>
+        <v>dj__freckles</v>
       </c>
       <c r="B895">
         <v>0</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>jose_luiz_thome</v>
+        <v>regis18vieira</v>
       </c>
       <c r="B896">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>andy.techera.12</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B897">
         <v>0</v>
@@ -12960,7 +12960,7 @@
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>celiogarcia6</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B898">
         <v>0</v>
@@ -12974,28 +12974,42 @@
     </row>
     <row r="899">
       <c r="A899" t="str">
+        <v>celiogarcia6</v>
+      </c>
+      <c r="B899">
+        <v>0</v>
+      </c>
+      <c r="C899">
+        <v>1</v>
+      </c>
+      <c r="D899">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="str">
         <v>luluakio</v>
       </c>
-      <c r="B899">
-        <v>0</v>
-      </c>
-      <c r="C899">
-        <v>1</v>
-      </c>
-      <c r="D899">
+      <c r="B900">
+        <v>0</v>
+      </c>
+      <c r="C900">
+        <v>1</v>
+      </c>
+      <c r="D900">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D899"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D900"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D122"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13016,13 +13030,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>969</v>
+        <v>1109</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>909</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="3">
@@ -13030,7 +13044,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>332</v>
+        <v>422</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -13058,7 +13072,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -13072,10 +13086,10 @@
         <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>40</v>
@@ -13086,13 +13100,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -13100,97 +13114,97 @@
         <v>malu832757</v>
       </c>
       <c r="B8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B9">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>jujua_maral1</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>anaaj_camargo</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>masonharper_mma</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>rayn.avaro</v>
+        <v>jujua_maral1</v>
       </c>
       <c r="B13">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>11</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>rm.nicki</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -13198,32 +13212,32 @@
         <v>anayachiottoni</v>
       </c>
       <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
         <v>10</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mar_iarmaria</v>
+        <v>im.duda02</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>arafight_pesc</v>
+        <v>n.daily22</v>
       </c>
       <c r="B17">
         <v>10</v>
@@ -13232,21 +13246,21 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ottonianalivia</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -13254,209 +13268,209 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>laisrebeiro10</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>im.duda02</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
         <v>8</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>propeace_fight</v>
+        <v>johnmma9</v>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>leozin.kick</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
         <v>7</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>combintel</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>johnmma9</v>
+        <v>combintel</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>italothearcher</v>
+        <v>galler_peace</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>grapplerfight</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B27">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
         <v>7</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>washington_cassisno</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>mmmarc20</v>
+        <v>laisrebeiro10</v>
       </c>
       <c r="B29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>thundergrapple</v>
+        <v>leozin.kick</v>
       </c>
       <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
         <v>6</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>galler_peace</v>
+        <v>italothearcher</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>figh_grappler</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
         <v>6</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>n.daily22</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -13545,13 +13559,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>aj_mma_</v>
+        <v>maxgandra</v>
       </c>
       <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
         <v>3</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -13559,41 +13573,41 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>daniezzyy</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>elienelucindo_oficial</v>
+        <v>daniezzyy</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>mayarinhafreestyle</v>
+        <v>elienelucindo_oficial</v>
       </c>
       <c r="B43">
         <v>5</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -13601,27 +13615,27 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>marcelogabrielmma</v>
+        <v>mayarinhafreestyle</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>god.motivacao</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -13629,13 +13643,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>vincenzo_pit_monster</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B46">
         <v>2</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -13643,21 +13657,21 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>adrianoams7</v>
+        <v>vincenzo_pit_monster</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ottonimestre</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B48">
         <v>4</v>
@@ -13671,55 +13685,55 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>vndcardoso</v>
+        <v>ottonimestre</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>eolucasrosa</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>maxgandra</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>jvxz______</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -13727,13 +13741,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>luigimoraess</v>
+        <v>jvxz______</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -13741,13 +13755,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>efsantos.oficial</v>
+        <v>luigimoraess</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -13755,49 +13769,49 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>rosiortega</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>rosiortega</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>carlosalbertobarretojr</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>deboralvesoficial</v>
+        <v>carlosalbertobarretojr</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -13811,44 +13825,44 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>deboralvesoficial</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>e_car.doso</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>pg_grappling</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -14623,7 +14637,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>eliassilverio</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -14632,12 +14646,12 @@
         <v>1</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>andy.techera.12</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -14651,7 +14665,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>celiogarcia6</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -14665,7 +14679,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>jean_ferreira_br</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -14679,21 +14693,35 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
+        <v>jean_ferreira_br</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
         <v>luluakio</v>
       </c>
-      <c r="B121">
-        <v>0</v>
-      </c>
-      <c r="C121">
-        <v>1</v>
-      </c>
-      <c r="D121">
+      <c r="B122">
+        <v>0</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D122"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>12541</v>
+        <v>12586</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>11314</v>
+        <v>11353</v>
       </c>
     </row>
     <row r="3">
@@ -447,13 +447,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B4">
-        <v>2938</v>
+        <v>2988</v>
       </c>
       <c r="C4">
         <v>6</v>
       </c>
       <c r="D4">
-        <v>886</v>
+        <v>936</v>
       </c>
     </row>
     <row r="5">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2093</v>
+        <v>2104</v>
       </c>
       <c r="C5">
         <v>30</v>
       </c>
       <c r="D5">
-        <v>899</v>
+        <v>910</v>
       </c>
     </row>
     <row r="6">
@@ -489,13 +489,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B7">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C7">
         <v>14</v>
       </c>
       <c r="D7">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>combintel</v>
       </c>
       <c r="B11">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -559,7 +559,7 @@
         <v>rm.nicki</v>
       </c>
       <c r="B12">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -629,7 +629,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -643,7 +643,7 @@
         <v>johnmma9</v>
       </c>
       <c r="B18">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -657,7 +657,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B19">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -671,7 +671,7 @@
         <v>malu832757</v>
       </c>
       <c r="B20">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -688,10 +688,10 @@
         <v>73</v>
       </c>
       <c r="C21">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22">
@@ -699,7 +699,7 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B22">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C22">
         <v>70</v>
@@ -797,7 +797,7 @@
         <v>god.motivacao</v>
       </c>
       <c r="B29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29">
         <v>206</v>
@@ -842,10 +842,10 @@
         <v>60</v>
       </c>
       <c r="C32">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D32">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -951,13 +951,13 @@
         <v>washington_cassisno</v>
       </c>
       <c r="B40">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C40">
         <v>13</v>
       </c>
       <c r="D40">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
@@ -1158,114 +1158,114 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>alvesmidih</v>
+        <v>im.duda02</v>
       </c>
       <c r="B55">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>marcelogabrielmma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B56">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>n.daily22</v>
       </c>
       <c r="B57">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>tabajaraharu</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B58">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C58">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>vndcardoso</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B59">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D59">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>docinhos26</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B60">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>im.duda02</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B61">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>n.daily22</v>
+        <v>docinhos26</v>
       </c>
       <c r="B62">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -1273,7 +1273,7 @@
         <v>rayn.avaro</v>
       </c>
       <c r="B63">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -1298,105 +1298,105 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>_alvezbjj__</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B65">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>jujua_maral1</v>
+        <v>_alvezbjj__</v>
       </c>
       <c r="B66">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D66">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>gustavomohallem</v>
+        <v>jujua_maral1</v>
       </c>
       <c r="B67">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>grapplerfight</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B68">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>tawanregismma</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B69">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>mar_iarmaria</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B70">
         <v>18</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>thundergrapple</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B71">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>galler_peace</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B72">
         <v>14</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>figh_grappler</v>
+        <v>galler_peace</v>
       </c>
       <c r="B73">
         <v>14</v>
@@ -1424,35 +1424,35 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>jvxz______</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B74">
         <v>14</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>rhuansales.mma</v>
+        <v>jvxz______</v>
       </c>
       <c r="B75">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B76">
         <v>16</v>
@@ -1461,21 +1461,21 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>arafight_pesc</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B77">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -1483,7 +1483,7 @@
         <v>propeace_fight</v>
       </c>
       <c r="B78">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -1508,86 +1508,86 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>ravenrodriguez___</v>
+        <v>gdazuera</v>
       </c>
       <c r="B80">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C80">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>marc0s.azv</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B81">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>danielbrbjj</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B82">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>adriano.trator</v>
+        <v>danielbrbjj</v>
       </c>
       <c r="B83">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C83">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="D83">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>marcos_tailandess</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B84">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C84">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D84">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>gdazuera</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B85">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C85">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D85">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
@@ -1760,63 +1760,63 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>eolucasrosa</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B98">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C98">
         <v>2</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>diegopaivajj</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B99">
         <v>9</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B100">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>__ottonii__</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B101">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>misskelsc</v>
+        <v>__ottonii__</v>
       </c>
       <c r="B102">
         <v>10</v>
@@ -1825,74 +1825,74 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>pedro_giraldi</v>
+        <v>misskelsc</v>
       </c>
       <c r="B103">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C103">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>brodschack_</v>
+        <v>pedro_giraldi</v>
       </c>
       <c r="B104">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C104">
+        <v>14</v>
+      </c>
+      <c r="D104">
         <v>5</v>
-      </c>
-      <c r="D104">
-        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>vitor_dx_mma</v>
+        <v>brodschack_</v>
       </c>
       <c r="B105">
         <v>9</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>guilhermemirandamma</v>
+        <v>vitor_dx_mma</v>
       </c>
       <c r="B106">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C106">
         <v>0</v>
       </c>
       <c r="D106">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>_oliveira09_</v>
+        <v>guilhermemirandamma</v>
       </c>
       <c r="B107">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C107">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>4</v>
@@ -1900,13 +1900,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>badboykillermma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B108">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D108">
         <v>4</v>
@@ -1914,27 +1914,27 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B109">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>cayan.pascoalbjj</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B110">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C110">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -1942,16 +1942,16 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>kelly_ottoni</v>
+        <v>cayan.pascoalbjj</v>
       </c>
       <c r="B111">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D111">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3580,13 +3580,13 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>yamasakinhobjj</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B228">
         <v>1</v>
       </c>
       <c r="C228">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D228">
         <v>1</v>
@@ -3594,21 +3594,21 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>cami28_l</v>
+        <v>yamasakinhobjj</v>
       </c>
       <c r="B229">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>flaviakaena</v>
+        <v>cami28_l</v>
       </c>
       <c r="B230">
         <v>3</v>
@@ -3622,133 +3622,133 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>chrislima____</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B231">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C231">
         <v>0</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>c.m_figth</v>
+        <v>chrislima____</v>
       </c>
       <c r="B232">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C232">
         <v>0</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>c.m_figth</v>
       </c>
       <c r="B233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C233">
         <v>0</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>e_car.doso</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C234">
         <v>0</v>
       </c>
       <c r="D234">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>pauloserrati</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B235">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D235">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>couragemma</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B236">
         <v>1</v>
       </c>
       <c r="C236">
+        <v>2</v>
+      </c>
+      <c r="D236">
         <v>3</v>
-      </c>
-      <c r="D236">
-        <v>2</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>kaua_limaofc</v>
+        <v>couragemma</v>
       </c>
       <c r="B237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C237">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>ruangzk</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C238">
         <v>0</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>emerson_lucaszx</v>
+        <v>ruangzk</v>
       </c>
       <c r="B239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C239">
         <v>0</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>clouddhidden</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B240">
         <v>2</v>
@@ -3762,21 +3762,21 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>_matheusifernandes</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C241">
         <v>0</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>bryantank_</v>
+        <v>_matheusifernandes</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>ruan.arcanjo01</v>
+        <v>bryantank_</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>coyote_style_hair</v>
+        <v>ruan.arcanjo01</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,30 +3818,30 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>sueli_ferreira48</v>
+        <v>coyote_style_hair</v>
       </c>
       <c r="B245">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C245">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C246">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D246">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -13240,13 +13240,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>1625</v>
+        <v>1670</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1538</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="3">
@@ -13254,41 +13254,41 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>911</v>
+        <v>961</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>430</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>pablofiorindi</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B4">
-        <v>200</v>
+        <v>119</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B5">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13299,10 +13299,10 @@
         <v>55</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -13310,13 +13310,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -13324,7 +13324,7 @@
         <v>malu832757</v>
       </c>
       <c r="B8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>rm.nicki</v>
       </c>
       <c r="B11">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -13380,7 +13380,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -13394,7 +13394,7 @@
         <v>im.duda02</v>
       </c>
       <c r="B13">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -13408,7 +13408,7 @@
         <v>n.daily22</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -13422,7 +13422,7 @@
         <v>kamile_oliveria_10</v>
       </c>
       <c r="B15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -13433,16 +13433,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>jujua_maral1</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B16">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -13450,7 +13450,7 @@
         <v>rayn.avaro</v>
       </c>
       <c r="B17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -13461,10 +13461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>grapplerfight</v>
+        <v>jujua_maral1</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -13475,35 +13475,35 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>thundergrapple</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>galler_peace</v>
+        <v>johnmma9</v>
       </c>
       <c r="B20">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>figh_grappler</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B21">
         <v>14</v>
@@ -13517,30 +13517,30 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>johnmma9</v>
+        <v>galler_peace</v>
       </c>
       <c r="B22">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>rhuansales.mma</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B23">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -13548,7 +13548,7 @@
         <v>arafight_pesc</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -13562,7 +13562,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>combintel</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -13590,7 +13590,7 @@
         <v>propeace_fight</v>
       </c>
       <c r="B27">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -13632,13 +13632,13 @@
         <v>washington_cassisno</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30">
         <v>4</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -13699,100 +13699,100 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>thiagoauper</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>guilhermemirandamma</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>victus_torquatus00</v>
+        <v>guilhermemirandamma</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ottonimestre</v>
+        <v>victus_torquatus00</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>enzoferrari680</v>
+        <v>ottonimestre</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B40">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>kelly_ottoni</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -13831,10 +13831,10 @@
         <v>4</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -13881,55 +13881,55 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>pg_grappling</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48">
         <v>4</v>
       </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>daniezzyy</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B49">
         <v>4</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>elienelucindo_oficial</v>
+        <v>daniezzyy</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>rosiortega</v>
+        <v>elienelucindo_oficial</v>
       </c>
       <c r="B51">
         <v>5</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -13937,7 +13937,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>mayarinhafreestyle</v>
+        <v>rosiortega</v>
       </c>
       <c r="B52">
         <v>5</v>
@@ -13951,27 +13951,27 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>marcelogabrielmma</v>
+        <v>mayarinhafreestyle</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>god.motivacao</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -14231,13 +14231,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>jose_luiz_thome</v>
+        <v>gdazuera</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -14245,7 +14245,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -14254,40 +14254,40 @@
         <v>1</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>emersonriosmma</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>fatima_trindade_</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -14301,13 +14301,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -14315,7 +14315,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>flaviakaena</v>
+        <v>fatima_trindade_</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -14329,21 +14329,21 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>gillesarquitetura</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ninjatheorist</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -14357,7 +14357,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>alvestank</v>
+        <v>gillesarquitetura</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -14371,35 +14371,35 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>marciooangelo</v>
+        <v>alvestank</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>peacegrappler_archive</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -14413,21 +14413,21 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>adevaldojr_</v>
+        <v>marciooangelo</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>rosacostasousa36</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -14441,7 +14441,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>helenaseveribjj</v>
+        <v>adevaldojr_</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -14455,7 +14455,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>manucanecorso.bjj</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -14469,21 +14469,21 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>claudiaottoni2025</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>claudiaottoni19</v>
+        <v>manucanecorso.bjj</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -14497,21 +14497,21 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>tavin.mendes</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>fabiieju</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -14525,13 +14525,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>sergio_alves_bjj</v>
+        <v>tavin.mendes</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -14539,27 +14539,27 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>fabiieju</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>anderson.logan.35</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -14567,7 +14567,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>djsagatoficial</v>
+        <v>sergio_alves_bjj</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -14576,18 +14576,18 @@
         <v>1</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>mmapalpitex</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -14595,13 +14595,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>djsagatoficial</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -14609,7 +14609,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>pedromadeira.s</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -14623,7 +14623,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>kauan_mantas</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -14637,7 +14637,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>erickdiaseds</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -14651,7 +14651,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>emersonapache</v>
+        <v>kauan_mantas</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -14665,7 +14665,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>nataliavidal965</v>
+        <v>erickdiaseds</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>manoel_maranhaobjjmma</v>
+        <v>emersonapache</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -14693,7 +14693,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ruanpantojanutricionista</v>
+        <v>nataliavidal965</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -14707,7 +14707,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>alexandreconsentino</v>
+        <v>manoel_maranhaobjjmma</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -14721,7 +14721,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>luizpaulomma</v>
+        <v>ruanpantojanutricionista</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -14735,7 +14735,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -14749,7 +14749,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>epicjoel2022</v>
+        <v>luizpaulomma</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -14763,7 +14763,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>tvlinsoficial</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -14777,7 +14777,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>_itamar_maximo</v>
+        <v>epicjoel2022</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -14791,7 +14791,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>mg._silvaa_</v>
+        <v>tvlinsoficial</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -14805,7 +14805,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>sarahfmaia</v>
+        <v>_itamar_maximo</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -14819,7 +14819,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>desativado_no_off33</v>
+        <v>mg._silvaa_</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -14833,21 +14833,21 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>lucasbaddoure</v>
+        <v>sarahfmaia</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>paulo_rafa_personal</v>
+        <v>desativado_no_off33</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -14861,21 +14861,21 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>endurance_guia</v>
+        <v>lucasbaddoure</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>cadupereirss</v>
+        <v>paulo_rafa_personal</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -14889,7 +14889,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>cesar.boanerges</v>
+        <v>endurance_guia</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -14903,7 +14903,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>instrutorindiovs</v>
+        <v>cadupereirss</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -14917,7 +14917,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>lopes.felipe13</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -14931,7 +14931,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>marciokeske</v>
+        <v>instrutorindiovs</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -14945,7 +14945,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>percepcar</v>
+        <v>lopes.felipe13</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -14959,7 +14959,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>_jullianadacruz</v>
+        <v>marciokeske</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -14973,7 +14973,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>eric.shpritz</v>
+        <v>percepcar</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -14987,7 +14987,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>thiagoxavier13</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -15001,7 +15001,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>gdazuera</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -15015,7 +15015,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>thiagoxavier13</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -15029,21 +15029,21 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>viniciustbf</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>marcos_tailandess</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -15057,41 +15057,41 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>disk_egg</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
       <c r="C132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>kalaga_vito</v>
+        <v>disk_egg</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ryangandraufc</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B134">
         <v>0</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D134">
         <v>1</v>

--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>12586</v>
+        <v>12665</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>11353</v>
+        <v>11432</v>
       </c>
     </row>
     <row r="3">
@@ -447,13 +447,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B4">
-        <v>2988</v>
+        <v>3067</v>
       </c>
       <c r="C4">
         <v>6</v>
       </c>
       <c r="D4">
-        <v>936</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="5">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2104</v>
+        <v>2108</v>
       </c>
       <c r="C5">
         <v>30</v>
       </c>
       <c r="D5">
-        <v>910</v>
+        <v>914</v>
       </c>
     </row>
     <row r="6">
@@ -934,30 +934,30 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>leonardomesquitamma</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B39">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D39">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>washington_cassisno</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B40">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -1214,49 +1214,49 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>marcelogabrielmma</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B59">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>tabajaraharu</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B60">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C60">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D60">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>vndcardoso</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B61">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>docinhos26</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B62">
         <v>19</v>
@@ -1265,49 +1265,49 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>rayn.avaro</v>
+        <v>docinhos26</v>
       </c>
       <c r="B63">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>tiwifenixmma</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B64">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>rhuansales.mma</v>
+        <v>tiwifenixmma</v>
       </c>
       <c r="B65">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D65">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -13240,13 +13240,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>1670</v>
+        <v>1749</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1577</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="3">
@@ -13254,13 +13254,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>961</v>
+        <v>1040</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>480</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4">
@@ -13268,13 +13268,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B4">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
@@ -13419,10 +13419,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -13433,16 +13433,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>rhuansales.mma</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B16">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -13587,35 +13587,35 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>propeace_fight</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B27">
         <v>13</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ottonianalivia</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B28">
         <v>13</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>mar_iarmaria</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B29">
         <v>13</v>
@@ -13629,13 +13629,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>washington_cassisno</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>9</v>

--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -419,41 +419,41 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13083</v>
+        <v>13170</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>11821</v>
+        <v>11908</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>pablofiorindi</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3379</v>
+        <v>3403</v>
       </c>
       <c r="C3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>967</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>pedr00jj</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>3243</v>
+        <v>3379</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D4">
-        <v>1154</v>
+        <v>967</v>
       </c>
     </row>
     <row r="5">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="7">
@@ -559,13 +559,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B12">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C12">
         <v>7</v>
       </c>
       <c r="D12">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -685,7 +685,7 @@
         <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B21">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C21">
         <v>46</v>
@@ -864,41 +864,41 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>kauepraciano</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B34">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>kaua_limamma</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B35">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>erik_.mma</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B36">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -906,16 +906,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>washington_cassisno</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B37">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C37">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -990,72 +990,72 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ottonianalivia</v>
+        <v>im.duda02</v>
       </c>
       <c r="B43">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>enzoferrari680</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B44">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>leandrosolano_mma</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B45">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C45">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>anayachiottoni</v>
+        <v>leandrosolano_mma</v>
       </c>
       <c r="B46">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D46">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>im.duda02</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B47">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
@@ -1133,7 +1133,7 @@
         <v>rhuansales.mma</v>
       </c>
       <c r="B53">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1158,30 +1158,30 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>thiagoauper</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B55">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ninjatheorist</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B56">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -13618,13 +13618,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>2167</v>
+        <v>2254</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2045</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="3">
@@ -13632,13 +13632,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>1216</v>
+        <v>1376</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>698</v>
+        <v>858</v>
       </c>
     </row>
     <row r="4">
@@ -13674,13 +13674,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -13688,7 +13688,7 @@
         <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>14</v>
@@ -13716,41 +13716,41 @@
         <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>anayachiottoni</v>
+        <v>im.duda02</v>
       </c>
       <c r="B10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>im.duda02</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B11">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -13786,7 +13786,7 @@
         <v>rhuansales.mma</v>
       </c>
       <c r="B14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -13867,13 +13867,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>propeace_fight</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B20">
         <v>17</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>15</v>
@@ -13881,35 +13881,35 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>arafight_pesc</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B21">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>thundergrapple</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>galler_peace</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B23">
         <v>16</v>
@@ -13923,7 +13923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>figh_grappler</v>
+        <v>galler_peace</v>
       </c>
       <c r="B24">
         <v>16</v>
@@ -13937,30 +13937,30 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>johnmma9</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B25">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>washington_cassisno</v>
+        <v>johnmma9</v>
       </c>
       <c r="B26">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -14651,55 +14651,55 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>e_car.doso</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>gdazuera</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>jose_luiz_thome</v>
+        <v>gdazuera</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -14707,13 +14707,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>dgswillian</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -14721,13 +14721,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ryangandraufc</v>
+        <v>dgswillian</v>
       </c>
       <c r="B81">
         <v>2</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -14735,21 +14735,21 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>fredoctmma</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -14763,69 +14763,69 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>julianoalicate</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B85">
         <v>2</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>natanborges001</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>emersonriosmma</v>
+        <v>natanborges001</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>fatima_trindade_</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -14833,7 +14833,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>fatima_trindade_</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -14847,7 +14847,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>pedromadeira.s</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -14861,7 +14861,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>flaviakaena</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -14875,30 +14875,30 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>gillesarquitetura</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>ninjatheorist</v>
+        <v>gillesarquitetura</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">

--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D942"/>
+  <dimension ref="A1:D943"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13170</v>
+        <v>13255</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>11908</v>
+        <v>11993</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +433,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3403</v>
+        <v>3423</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2153</v>
+        <v>2160</v>
       </c>
       <c r="C5">
         <v>30</v>
       </c>
       <c r="D5">
-        <v>959</v>
+        <v>966</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C6">
         <v>14</v>
@@ -545,7 +545,7 @@
         <v>combintel</v>
       </c>
       <c r="B11">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -559,13 +559,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B12">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C12">
         <v>7</v>
       </c>
       <c r="D12">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -587,7 +587,7 @@
         <v>pg_grappling</v>
       </c>
       <c r="B14">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -629,13 +629,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -643,7 +643,7 @@
         <v>johnmma9</v>
       </c>
       <c r="B18">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -657,7 +657,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B19">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -671,7 +671,7 @@
         <v>malu832757</v>
       </c>
       <c r="B20">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -780,30 +780,30 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>god.motivacao</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B28">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="C28">
-        <v>207</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>cjrnavalha</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B29">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>208</v>
       </c>
       <c r="D29">
-        <v>15</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30">
@@ -870,10 +870,10 @@
         <v>36</v>
       </c>
       <c r="C34">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D34">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -962,161 +962,161 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>italothearcher</v>
+        <v>im.duda02</v>
       </c>
       <c r="B41">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C41">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>victus_torquatus00</v>
+        <v>italothearcher</v>
       </c>
       <c r="B42">
         <v>35</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>im.duda02</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B43">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ottonianalivia</v>
+        <v>victus_torquatus00</v>
       </c>
       <c r="B44">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>enzoferrari680</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B45">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>leandrosolano_mma</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B46">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C46">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>anayachiottoni</v>
+        <v>n.daily22</v>
       </c>
       <c r="B47">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>cleyton_jesuss</v>
+        <v>leandrosolano_mma</v>
       </c>
       <c r="B48">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D48">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>n.daily22</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B49">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D49">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>shawlin13oficial</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B50">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>pedromadeira.s</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B51">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>_cardoso_caio_</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B52">
         <v>31</v>
@@ -1125,21 +1125,21 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>rhuansales.mma</v>
+        <v>_cardoso_caio_</v>
       </c>
       <c r="B53">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54">
@@ -1147,7 +1147,7 @@
         <v>kamile_oliveria_10</v>
       </c>
       <c r="B54">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1161,7 +1161,7 @@
         <v>ninjatheorist</v>
       </c>
       <c r="B55">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1172,30 +1172,30 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>thiagoauper</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B56">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>rayn.avaro</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B57">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -1242,38 +1242,38 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>marcelogabrielmma</v>
+        <v>jujua_maral1</v>
       </c>
       <c r="B61">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>tabajaraharu</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B62">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C62">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>jujua_maral1</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B63">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -1284,108 +1284,108 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>vndcardoso</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B64">
         <v>19</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>docinhos26</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B65">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>grapplerfight</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B66">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>propeace_fight</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B67">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>tiwifenixmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B68">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>mar_iarmaria</v>
+        <v>docinhos26</v>
       </c>
       <c r="B69">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>arafight_pesc</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B70">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>thundergrapple</v>
+        <v>galler_peace</v>
       </c>
       <c r="B71">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>galler_peace</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B72">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -1410,16 +1410,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>figh_grappler</v>
+        <v>tiwifenixmma</v>
       </c>
       <c r="B73">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D73">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -1497,7 +1497,7 @@
         <v>laisrebeiro10</v>
       </c>
       <c r="B79">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>8</v>
       </c>
       <c r="C86">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D86">
         <v>10</v>
@@ -1606,139 +1606,139 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>albertoleandromoco</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B87">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C87">
         <v>3</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>macamariotti</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B88">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C88">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>guilhermemirandamma</v>
+        <v>macamariotti</v>
       </c>
       <c r="B89">
         <v>7</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>luizalaguerabjj</v>
+        <v>guilhermemirandamma</v>
       </c>
       <c r="B90">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>cpetemma248</v>
+        <v>luizalaguerabjj</v>
       </c>
       <c r="B91">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C91">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>kelly_ottoni</v>
+        <v>cpetemma248</v>
       </c>
       <c r="B92">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C92">
         <v>3</v>
       </c>
       <c r="D92">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>edebetim_</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B93">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C93">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>charlesduarte_mma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B94">
+        <v>6</v>
+      </c>
+      <c r="C94">
+        <v>20</v>
+      </c>
+      <c r="D94">
         <v>9</v>
-      </c>
-      <c r="C94">
-        <v>4</v>
-      </c>
-      <c r="D94">
-        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>dogodoyfoto</v>
+        <v>charlesduarte_mma</v>
       </c>
       <c r="B95">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C95">
+        <v>4</v>
+      </c>
+      <c r="D95">
         <v>3</v>
-      </c>
-      <c r="D95">
-        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>leozin.kick</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B96">
         <v>7</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D96">
         <v>6</v>
@@ -1746,41 +1746,41 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>rrafaelins</v>
+        <v>leozin.kick</v>
       </c>
       <c r="B97">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C97">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ailinperezufc</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B98">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B99">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>ottonimestre</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B100">
         <v>9</v>
@@ -1797,63 +1797,63 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>eolucasrosa</v>
+        <v>ottonimestre</v>
       </c>
       <c r="B101">
         <v>9</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>diegopaivajj</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B102">
         <v>9</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>anderson.logan.35</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B103">
         <v>9</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D103">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B104">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2152,13 +2152,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>__bielgg</v>
+        <v>carlosalbertobarretojr</v>
       </c>
       <c r="B126">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C126">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -2166,41 +2166,41 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>juanx.pontes</v>
+        <v>__bielgg</v>
       </c>
       <c r="B127">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C127">
         <v>3</v>
       </c>
       <c r="D127">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>paxlucta</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>muricunha</v>
+        <v>paxlucta</v>
       </c>
       <c r="B129">
         <v>5</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>erickdiaseds</v>
+        <v>muricunha</v>
       </c>
       <c r="B130">
         <v>5</v>
@@ -2222,21 +2222,21 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>erickdiaseds</v>
       </c>
       <c r="B131">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C131">
         <v>0</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>f.luan_11</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B132">
         <v>7</v>
@@ -2250,35 +2250,35 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>dennerfenomeno</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B133">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>hellenzinha.alves</v>
+        <v>dennerfenomeno</v>
       </c>
       <c r="B134">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C134">
         <v>0</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>hollenberg.personal</v>
+        <v>hellenzinha.alves</v>
       </c>
       <c r="B135">
         <v>7</v>
@@ -2292,55 +2292,55 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>fredoctmma</v>
+        <v>hollenberg.personal</v>
       </c>
       <c r="B136">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C136">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>thiagodossantossilvasantos</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B137">
+        <v>3</v>
+      </c>
+      <c r="C137">
+        <v>3</v>
+      </c>
+      <c r="D137">
         <v>4</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-      <c r="D137">
-        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>elienelucindo_oficial</v>
+        <v>thiagodossantossilvasantos</v>
       </c>
       <c r="B138">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>elienelucindo_oficial</v>
       </c>
       <c r="B139">
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>combatclubsp</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B140">
         <v>6</v>
       </c>
       <c r="C140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -2362,63 +2362,63 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>edaregiao</v>
+        <v>combatclubsp</v>
       </c>
       <c r="B141">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C141">
         <v>2</v>
       </c>
       <c r="D141">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>f.ostini</v>
+        <v>edaregiao</v>
       </c>
       <c r="B142">
         <v>4</v>
       </c>
       <c r="C142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>adrianoams7</v>
+        <v>f.ostini</v>
       </c>
       <c r="B143">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>dagestan0920</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B144">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>cesar.boanerges</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B145">
         <v>5</v>
@@ -2432,35 +2432,35 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>tatibscardoso</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B146">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C146">
         <v>0</v>
       </c>
       <c r="D146">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>olifrankiw</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B147">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C147">
         <v>0</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>mayarinhafreestyle</v>
+        <v>olifrankiw</v>
       </c>
       <c r="B148">
         <v>6</v>
@@ -2474,181 +2474,181 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>mayarinhafreestyle</v>
       </c>
       <c r="B149">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C149">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D149">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>ismaeldaniell</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B150">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C150">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>rafaelmacapa_</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B151">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>aj_mma_</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B152">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D152">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>daniezzyy</v>
+        <v>rafaelmacapa_</v>
       </c>
       <c r="B153">
         <v>4</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>glm.barbosa</v>
+        <v>daniezzyy</v>
       </c>
       <c r="B154">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C154">
         <v>0</v>
       </c>
       <c r="D154">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>fernando.mma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B155">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C155">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D155">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>davizoka_mascote</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B156">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>enzo_henrik</v>
+        <v>davizoka_mascote</v>
       </c>
       <c r="B157">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>emersonriosmma</v>
+        <v>enzo_henrik</v>
       </c>
       <c r="B158">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C158">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>douglasoct_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B159">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C159">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D159">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>eric.shpritz</v>
+        <v>douglasoct_mma</v>
       </c>
       <c r="B160">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C160">
         <v>2</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>marcocanatelli</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B161">
         <v>4</v>
       </c>
       <c r="C161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -2656,114 +2656,114 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>benjafloripabjj</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B162">
         <v>4</v>
       </c>
       <c r="C162">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>heltoncm2002</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B163">
         <v>4</v>
       </c>
       <c r="C163">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>pitbullandrade</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B164">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>zedelano</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B165">
         <v>3</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>salost.ofc</v>
+        <v>zedelano</v>
       </c>
       <c r="B166">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C166">
         <v>0</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>gabrielsouzamma</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B167">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B168">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>carlosalbertobarretojr</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C169">
         <v>0</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -3496,35 +3496,35 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>jose_luiz_thome</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B222">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C222">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>efsantos.oficial</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B223">
         <v>1</v>
       </c>
       <c r="C223">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D223">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>marifferreirac</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3533,40 +3533,40 @@
         <v>1</v>
       </c>
       <c r="D224">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>pauloserrati</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B225">
         <v>1</v>
       </c>
       <c r="C225">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D225">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>mineirinho_jj</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B226">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D226">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>juliochagasmma</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B227">
         <v>2</v>
@@ -3580,35 +3580,35 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>orafao1</v>
+        <v>juliochagasmma</v>
       </c>
       <c r="B228">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C228">
         <v>0</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>lopesbrunao</v>
+        <v>orafao1</v>
       </c>
       <c r="B229">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C229">
         <v>0</v>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>claudiaottoni19</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B230">
         <v>2</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>sr.valter</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B231">
         <v>2</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B232">
         <v>2</v>
@@ -3650,49 +3650,49 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>meol.socialmidia</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B233">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C233">
         <v>0</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>yamasakinhobjj</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B234">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D234">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>cami28_l</v>
+        <v>yamasakinhobjj</v>
       </c>
       <c r="B235">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>flaviakaena</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B236">
         <v>3</v>
@@ -3706,21 +3706,21 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>chrislima____</v>
+        <v>cami28_l</v>
       </c>
       <c r="B237">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C237">
         <v>0</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>c.m_figth</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B238">
         <v>3</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>chrislima____</v>
       </c>
       <c r="B239">
         <v>2</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>e_car.doso</v>
+        <v>c.m_figth</v>
       </c>
       <c r="B240">
         <v>3</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>dgswillian</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B241">
         <v>2</v>
@@ -3776,21 +3776,21 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>couragemma</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B242">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C242">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D242">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>kaua_limaofc</v>
+        <v>dgswillian</v>
       </c>
       <c r="B243">
         <v>2</v>
@@ -3799,26 +3799,26 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>ruangzk</v>
+        <v>couragemma</v>
       </c>
       <c r="B244">
         <v>1</v>
       </c>
       <c r="C244">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>emerson_lucaszx</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B245">
         <v>2</v>
@@ -3832,49 +3832,49 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>clouddhidden</v>
+        <v>ruangzk</v>
       </c>
       <c r="B246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C246">
         <v>0</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>_matheusifernandes</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C247">
         <v>0</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>bryantank_</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B248">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C248">
         <v>0</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>ruan.arcanjo01</v>
+        <v>_matheusifernandes</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>coyote_style_hair</v>
+        <v>bryantank_</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -3902,21 +3902,21 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>sueli_ferreira48</v>
+        <v>ruan.arcanjo01</v>
       </c>
       <c r="B251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C251">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>edsoncostateixeirabjj</v>
+        <v>coyote_style_hair</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,13 +3930,13 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>klein_hila</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B253">
         <v>2</v>
       </c>
       <c r="C253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D253">
         <v>0</v>
@@ -3944,27 +3944,27 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>edsoncostateixeirabjj</v>
       </c>
       <c r="B254">
         <v>1</v>
       </c>
       <c r="C254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D254">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>vnciuss__df</v>
+        <v>klein_hila</v>
       </c>
       <c r="B255">
         <v>2</v>
       </c>
       <c r="C255">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D255">
         <v>0</v>
@@ -3972,27 +3972,27 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>jhee_dias</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B256">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C256">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>tassiogiloficial</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B257">
         <v>2</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D257">
         <v>0</v>
@@ -4000,21 +4000,21 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B258">
         <v>2</v>
       </c>
       <c r="C258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>richards_brusen</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B259">
         <v>2</v>
@@ -4028,21 +4028,21 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>natalan_wilgner</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B260">
         <v>2</v>
       </c>
       <c r="C260">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D260">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>leticiamartinspro</v>
+        <v>richards_brusen</v>
       </c>
       <c r="B261">
         <v>2</v>
@@ -4056,21 +4056,21 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>danilo_marquesc</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D262">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>lucasspaulista</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B263">
         <v>2</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>danilo_marquesc</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>lucasspaulista</v>
       </c>
       <c r="B265">
         <v>2</v>
@@ -4112,35 +4112,35 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>julianoalicate</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B266">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>natanborges001</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B267">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D267">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>select_from_joao</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B268">
         <v>2</v>
@@ -4149,18 +4149,18 @@
         <v>1</v>
       </c>
       <c r="D268">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>cristianpsicologo</v>
+        <v>natanborges001</v>
       </c>
       <c r="B269">
         <v>1</v>
       </c>
       <c r="C269">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D269">
         <v>2</v>
@@ -4168,35 +4168,35 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>fabaotipster</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B270">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B271">
         <v>1</v>
       </c>
       <c r="C271">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D271">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>helenaseveribjj</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,41 +4210,41 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>marciokeske</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B273">
         <v>1</v>
       </c>
       <c r="C273">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D273">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>ommariotti</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B274">
         <v>1</v>
       </c>
       <c r="C274">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D274">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>felipebunesufc</v>
+        <v>marciokeske</v>
       </c>
       <c r="B275">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C275">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D275">
         <v>0</v>
@@ -4252,35 +4252,35 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>icarohilton</v>
+        <v>ommariotti</v>
       </c>
       <c r="B276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C276">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>jesabelmelo9</v>
+        <v>felipebunesufc</v>
       </c>
       <c r="B277">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C277">
         <v>1</v>
       </c>
       <c r="D277">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>iranbez</v>
+        <v>icarohilton</v>
       </c>
       <c r="B278">
         <v>2</v>
@@ -4294,27 +4294,27 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>sthe._.araujo</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B279">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>clayton77silva</v>
+        <v>iranbez</v>
       </c>
       <c r="B280">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C280">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>raycon_mma</v>
+        <v>sthe._.araujo</v>
       </c>
       <c r="B281">
         <v>2</v>
@@ -4336,13 +4336,13 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>sarahfmaia</v>
+        <v>clayton77silva</v>
       </c>
       <c r="B282">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C282">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>jean_ferreira_br</v>
+        <v>raycon_mma</v>
       </c>
       <c r="B283">
         <v>2</v>
@@ -4364,13 +4364,13 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>sarahfmaia</v>
       </c>
       <c r="B284">
         <v>2</v>
       </c>
       <c r="C284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -4378,35 +4378,35 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B285">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C285">
         <v>0</v>
       </c>
       <c r="D285">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>aliferpaulo_</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B286">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C286">
         <v>0</v>
       </c>
       <c r="D286">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>sambagabrieloficial</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B287">
         <v>2</v>
@@ -4420,35 +4420,35 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>raelduraes</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B288">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C288">
         <v>0</v>
       </c>
       <c r="D288">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>martta.mariah</v>
+        <v>raelduraes</v>
       </c>
       <c r="B289">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C289">
         <v>0</v>
       </c>
       <c r="D289">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B290">
         <v>2</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>_bety_marcal</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B291">
         <v>2</v>
@@ -4476,13 +4476,13 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B292">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C292">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D292">
         <v>0</v>
@@ -4490,13 +4490,13 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>wesley_bjjvc</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B293">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C293">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B294">
         <v>2</v>
@@ -4518,21 +4518,21 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B295">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C295">
         <v>0</v>
       </c>
       <c r="D295">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B296">
         <v>1</v>
@@ -4546,21 +4546,21 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>fabi.godooy</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B297">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C297">
         <v>0</v>
       </c>
       <c r="D297">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>davicorbella</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B298">
         <v>2</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>joegam3r</v>
+        <v>davicorbella</v>
       </c>
       <c r="B299">
         <v>2</v>
@@ -4588,35 +4588,35 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>graalino</v>
+        <v>joegam3r</v>
       </c>
       <c r="B300">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C300">
         <v>0</v>
       </c>
       <c r="D300">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>ramanatoscanellibjj</v>
+        <v>graalino</v>
       </c>
       <c r="B301">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C301">
         <v>0</v>
       </c>
       <c r="D301">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>mariabeltapagani</v>
+        <v>ramanatoscanellibjj</v>
       </c>
       <c r="B302">
         <v>2</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>auriceliaribeiro_</v>
+        <v>mariabeltapagani</v>
       </c>
       <c r="B303">
         <v>2</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>craig_cohen1</v>
+        <v>auriceliaribeiro_</v>
       </c>
       <c r="B304">
         <v>2</v>
@@ -4658,35 +4658,35 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>glessios_silva</v>
+        <v>craig_cohen1</v>
       </c>
       <c r="B305">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C305">
         <v>0</v>
       </c>
       <c r="D305">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>fabioincalado</v>
+        <v>glessios_silva</v>
       </c>
       <c r="B306">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C306">
         <v>0</v>
       </c>
       <c r="D306">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>vanderleiamellogois</v>
+        <v>fabioincalado</v>
       </c>
       <c r="B307">
         <v>2</v>
@@ -4700,91 +4700,91 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>pedrinhosbjj</v>
+        <v>vanderleiamellogois</v>
       </c>
       <c r="B308">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C308">
         <v>0</v>
       </c>
       <c r="D308">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>_jaquealms</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B309">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C309">
         <v>0</v>
       </c>
       <c r="D309">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>caio.fermianoo</v>
+        <v>_jaquealms</v>
       </c>
       <c r="B310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C310">
         <v>0</v>
       </c>
       <c r="D310">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>corrozzzive</v>
+        <v>caio.fermianoo</v>
       </c>
       <c r="B311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C311">
         <v>0</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>araujojonaspenhade</v>
+        <v>corrozzzive</v>
       </c>
       <c r="B312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C312">
         <v>0</v>
       </c>
       <c r="D312">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>duuleitee</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B313">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C313">
         <v>0</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>pvd_._dudis</v>
+        <v>duuleitee</v>
       </c>
       <c r="B314">
         <v>2</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B315">
         <v>2</v>
@@ -4812,30 +4812,30 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>tatianeaguiarp</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B316">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C316">
         <v>0</v>
       </c>
       <c r="D316">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B317">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C317">
         <v>0</v>
       </c>
       <c r="D317">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -10048,35 +10048,35 @@
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>luizcosta_mma</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B690">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C690">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D690">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>taylor_71kg</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B691">
         <v>0</v>
       </c>
       <c r="C691">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D691">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>_vpft</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B692">
         <v>0</v>
@@ -10090,21 +10090,21 @@
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>viniciustbf</v>
+        <v>_vpft</v>
       </c>
       <c r="B693">
         <v>0</v>
       </c>
       <c r="C693">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D693">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>dayanaa1511</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B694">
         <v>0</v>
@@ -10113,40 +10113,40 @@
         <v>2</v>
       </c>
       <c r="D694">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>danielfranzesilva</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B695">
         <v>0</v>
       </c>
       <c r="C695">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D695">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B696">
         <v>0</v>
       </c>
       <c r="C696">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D696">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>vanessamelomma</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B697">
         <v>0</v>
@@ -10160,21 +10160,21 @@
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>michelle_mirele</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B698">
         <v>0</v>
       </c>
       <c r="C698">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D698">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>geyziellsouza</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B699">
         <v>0</v>
@@ -10188,21 +10188,21 @@
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>guerreirammaofc</v>
+        <v>geyziellsouza</v>
       </c>
       <c r="B700">
         <v>0</v>
       </c>
       <c r="C700">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D700">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>kalaga_vito</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B701">
         <v>0</v>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>vitorshowman</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B702">
         <v>0</v>
@@ -10225,12 +10225,12 @@
         <v>2</v>
       </c>
       <c r="D702">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B703">
         <v>0</v>
@@ -10244,21 +10244,21 @@
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B704">
         <v>0</v>
       </c>
       <c r="C704">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D704">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B705">
         <v>0</v>
@@ -10272,21 +10272,21 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>orlando_alfa09</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B706">
         <v>0</v>
       </c>
       <c r="C706">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D706">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B707">
         <v>0</v>
@@ -10300,7 +10300,7 @@
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>manumito.oficial</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B708">
         <v>0</v>
@@ -10314,63 +10314,63 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>coutz11</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B709">
         <v>0</v>
       </c>
       <c r="C709">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D709">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>eglaudiomma</v>
+        <v>coutz11</v>
       </c>
       <c r="B710">
         <v>0</v>
       </c>
       <c r="C710">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D710">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>lokomemo_protetores</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B711">
         <v>0</v>
       </c>
       <c r="C711">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D711">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>carlosnoelblack</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B712">
         <v>0</v>
       </c>
       <c r="C712">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D712">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>rafaelcmjj</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B713">
         <v>0</v>
@@ -10384,21 +10384,21 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>rahikikhalid</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B714">
         <v>0</v>
       </c>
       <c r="C714">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D714">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>leonardopateira</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B715">
         <v>0</v>
@@ -10412,21 +10412,21 @@
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>thalytabjj</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B716">
         <v>0</v>
       </c>
       <c r="C716">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D716">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>rafaelantonio.rj</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B717">
         <v>0</v>
@@ -10440,35 +10440,35 @@
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>yasminreis_oficiall</v>
+        <v>rafaelantonio.rj</v>
       </c>
       <c r="B718">
         <v>0</v>
       </c>
       <c r="C718">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D718">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>dnoxsport</v>
+        <v>yasminreis_oficiall</v>
       </c>
       <c r="B719">
         <v>0</v>
       </c>
       <c r="C719">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D719">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>armysenju</v>
+        <v>dnoxsport</v>
       </c>
       <c r="B720">
         <v>0</v>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>kamtalksmma</v>
+        <v>armysenju</v>
       </c>
       <c r="B721">
         <v>0</v>
@@ -10496,49 +10496,49 @@
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>arleyleboss</v>
+        <v>kamtalksmma</v>
       </c>
       <c r="B722">
         <v>0</v>
       </c>
       <c r="C722">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D722">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>jj_miguel05</v>
+        <v>arleyleboss</v>
       </c>
       <c r="B723">
         <v>0</v>
       </c>
       <c r="C723">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D723">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>dra.izabeldelfino_</v>
+        <v>jj_miguel05</v>
       </c>
       <c r="B724">
         <v>0</v>
       </c>
       <c r="C724">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D724">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>janjaovix</v>
+        <v>dra.izabeldelfino_</v>
       </c>
       <c r="B725">
         <v>0</v>
@@ -10552,7 +10552,7 @@
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B726">
         <v>0</v>
@@ -10566,7 +10566,7 @@
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B727">
         <v>0</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>paulomartins.mma</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B728">
         <v>0</v>
@@ -10594,27 +10594,27 @@
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>daniel_natel</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B729">
         <v>0</v>
       </c>
       <c r="C729">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D729">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>dhuks11</v>
+        <v>daniel_natel</v>
       </c>
       <c r="B730">
         <v>0</v>
       </c>
       <c r="C730">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D730">
         <v>0</v>
@@ -10622,7 +10622,7 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>macksomlee</v>
+        <v>dhuks11</v>
       </c>
       <c r="B731">
         <v>0</v>
@@ -10631,40 +10631,40 @@
         <v>1</v>
       </c>
       <c r="D731">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>y_nichimura</v>
+        <v>macksomlee</v>
       </c>
       <c r="B732">
         <v>0</v>
       </c>
       <c r="C732">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D732">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>mayconzilli</v>
+        <v>y_nichimura</v>
       </c>
       <c r="B733">
         <v>0</v>
       </c>
       <c r="C733">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D733">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>patascubo</v>
+        <v>mayconzilli</v>
       </c>
       <c r="B734">
         <v>0</v>
@@ -10678,7 +10678,7 @@
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>jeffesonmeirelles</v>
+        <v>patascubo</v>
       </c>
       <c r="B735">
         <v>0</v>
@@ -10692,7 +10692,7 @@
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>denilson.unit</v>
+        <v>jeffesonmeirelles</v>
       </c>
       <c r="B736">
         <v>0</v>
@@ -10706,7 +10706,7 @@
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>vieirabjj____</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B737">
         <v>0</v>
@@ -10720,7 +10720,7 @@
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>canalgolpebaixo</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B738">
         <v>0</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>leandro__parpinelli</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B739">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>bruno_pontes1992</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B740">
         <v>0</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>dudaadantass</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B741">
         <v>0</v>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>_pedro0h</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B742">
         <v>0</v>
@@ -10790,7 +10790,7 @@
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>alineanne_</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B743">
         <v>0</v>
@@ -10799,12 +10799,12 @@
         <v>1</v>
       </c>
       <c r="D743">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B744">
         <v>0</v>
@@ -10818,7 +10818,7 @@
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B745">
         <v>0</v>
@@ -10832,7 +10832,7 @@
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B746">
         <v>0</v>
@@ -10846,7 +10846,7 @@
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B747">
         <v>0</v>
@@ -10860,7 +10860,7 @@
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B748">
         <v>0</v>
@@ -10874,7 +10874,7 @@
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B749">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B750">
         <v>0</v>
@@ -10902,7 +10902,7 @@
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B751">
         <v>0</v>
@@ -10916,7 +10916,7 @@
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B752">
         <v>0</v>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B753">
         <v>0</v>
@@ -10944,7 +10944,7 @@
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B754">
         <v>0</v>
@@ -10958,7 +10958,7 @@
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B755">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B756">
         <v>0</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B757">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B758">
         <v>0</v>
@@ -11014,7 +11014,7 @@
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B759">
         <v>0</v>
@@ -11028,7 +11028,7 @@
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B760">
         <v>0</v>
@@ -11042,7 +11042,7 @@
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B761">
         <v>0</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B762">
         <v>0</v>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B763">
         <v>0</v>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B764">
         <v>0</v>
@@ -11098,7 +11098,7 @@
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B765">
         <v>0</v>
@@ -11112,7 +11112,7 @@
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B766">
         <v>0</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B767">
         <v>0</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B768">
         <v>0</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B769">
         <v>0</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B770">
         <v>0</v>
@@ -11182,7 +11182,7 @@
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B771">
         <v>0</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>romulerasilva</v>
+        <v>roginbrito</v>
       </c>
       <c r="B772">
         <v>0</v>
@@ -11210,7 +11210,7 @@
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>higorsaantana</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B773">
         <v>0</v>
@@ -11224,7 +11224,7 @@
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>vitorcosta_mma</v>
+        <v>higorsaantana</v>
       </c>
       <c r="B774">
         <v>0</v>
@@ -11238,7 +11238,7 @@
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>paulo.titoo</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B775">
         <v>0</v>
@@ -11252,7 +11252,7 @@
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>1000ton_n</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B776">
         <v>0</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>strong_stg_oficial</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B777">
         <v>0</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B778">
         <v>0</v>
@@ -11294,7 +11294,7 @@
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B779">
         <v>0</v>
@@ -11308,7 +11308,7 @@
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B780">
         <v>0</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B781">
         <v>0</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>caioparangole</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B782">
         <v>0</v>
@@ -11350,7 +11350,7 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B783">
         <v>0</v>
@@ -11364,7 +11364,7 @@
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B784">
         <v>0</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B785">
         <v>0</v>
@@ -11392,7 +11392,7 @@
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B786">
         <v>0</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B787">
         <v>0</v>
@@ -11420,7 +11420,7 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B788">
         <v>0</v>
@@ -11434,7 +11434,7 @@
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>cristianomarcello</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B789">
         <v>0</v>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>dandraco_</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B790">
         <v>0</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B791">
         <v>0</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B792">
         <v>0</v>
@@ -11490,7 +11490,7 @@
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B793">
         <v>0</v>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B794">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B795">
         <v>0</v>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>geanne_franca_</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B796">
         <v>0</v>
@@ -11546,7 +11546,7 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>vanemessina</v>
+        <v>geanne_franca_</v>
       </c>
       <c r="B797">
         <v>0</v>
@@ -11560,7 +11560,7 @@
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B798">
         <v>0</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>esteticaluharruda</v>
+        <v>dadwillians</v>
       </c>
       <c r="B799">
         <v>0</v>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B800">
         <v>0</v>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>_kainanlima</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B801">
         <v>0</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B802">
         <v>0</v>
@@ -11630,7 +11630,7 @@
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B803">
         <v>0</v>
@@ -11644,7 +11644,7 @@
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B804">
         <v>0</v>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B805">
         <v>0</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>rafaelbipolarufc</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B806">
         <v>0</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>martinpakciarz</v>
+        <v>rafaelbipolarufc</v>
       </c>
       <c r="B807">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>andrearschack</v>
+        <v>martinpakciarz</v>
       </c>
       <c r="B808">
         <v>0</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>leziamorbeck50</v>
+        <v>andrearschack</v>
       </c>
       <c r="B809">
         <v>0</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>meirelesmma</v>
+        <v>leziamorbeck50</v>
       </c>
       <c r="B810">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>teamsilverio</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B811">
         <v>0</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>tatiaradias</v>
+        <v>teamsilverio</v>
       </c>
       <c r="B812">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>daniloacordeon_oficial</v>
+        <v>tatiaradias</v>
       </c>
       <c r="B813">
         <v>0</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>thiagopssantos</v>
+        <v>daniloacordeon_oficial</v>
       </c>
       <c r="B814">
         <v>0</v>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>leafarlemos</v>
+        <v>thiagopssantos</v>
       </c>
       <c r="B815">
         <v>0</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>miltoncjr28</v>
+        <v>leafarlemos</v>
       </c>
       <c r="B816">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>almeidajjwk</v>
+        <v>miltoncjr28</v>
       </c>
       <c r="B817">
         <v>0</v>
@@ -11840,7 +11840,7 @@
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>soniarmurata</v>
+        <v>almeidajjwk</v>
       </c>
       <c r="B818">
         <v>0</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>foryousaudeespecializada</v>
+        <v>soniarmurata</v>
       </c>
       <c r="B819">
         <v>0</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>marques.__bjj</v>
+        <v>foryousaudeespecializada</v>
       </c>
       <c r="B820">
         <v>0</v>
@@ -11882,7 +11882,7 @@
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>ryu_artes_marciais</v>
+        <v>marques.__bjj</v>
       </c>
       <c r="B821">
         <v>0</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>dorgivan13_bjj</v>
+        <v>ryu_artes_marciais</v>
       </c>
       <c r="B822">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>ayman__falil_06</v>
+        <v>dorgivan13_bjj</v>
       </c>
       <c r="B823">
         <v>0</v>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>otaviocarneiromma</v>
+        <v>ayman__falil_06</v>
       </c>
       <c r="B824">
         <v>0</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>dvlucc2k26_</v>
+        <v>otaviocarneiromma</v>
       </c>
       <c r="B825">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>thayanne_rodrigues_bjj</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B826">
         <v>0</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>lurochachef</v>
+        <v>thayanne_rodrigues_bjj</v>
       </c>
       <c r="B827">
         <v>0</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>viniciusmorais.bjj</v>
+        <v>lurochachef</v>
       </c>
       <c r="B828">
         <v>0</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>mauriciogeorge</v>
+        <v>viniciusmorais.bjj</v>
       </c>
       <c r="B829">
         <v>0</v>
@@ -12008,7 +12008,7 @@
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>gisbedejose</v>
+        <v>mauriciogeorge</v>
       </c>
       <c r="B830">
         <v>0</v>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>laureanucalvo</v>
+        <v>gisbedejose</v>
       </c>
       <c r="B831">
         <v>0</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>galindofrontado</v>
+        <v>laureanucalvo</v>
       </c>
       <c r="B832">
         <v>0</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>chalakakavinda</v>
+        <v>galindofrontado</v>
       </c>
       <c r="B833">
         <v>0</v>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>gandrapaulino</v>
+        <v>chalakakavinda</v>
       </c>
       <c r="B834">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>pgmarquesantos</v>
+        <v>gandrapaulino</v>
       </c>
       <c r="B835">
         <v>0</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>uluukyrgyz_tima</v>
+        <v>pgmarquesantos</v>
       </c>
       <c r="B836">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>kells2vallone</v>
+        <v>uluukyrgyz_tima</v>
       </c>
       <c r="B837">
         <v>0</v>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>personaljakeline</v>
+        <v>kells2vallone</v>
       </c>
       <c r="B838">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>bjjfalkenberg</v>
+        <v>personaljakeline</v>
       </c>
       <c r="B839">
         <v>0</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>sergiorenatocruz1</v>
+        <v>bjjfalkenberg</v>
       </c>
       <c r="B840">
         <v>0</v>
@@ -12162,7 +12162,7 @@
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>marcaojudobjjmaster</v>
+        <v>sergiorenatocruz1</v>
       </c>
       <c r="B841">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>indio_mma</v>
+        <v>marcaojudobjjmaster</v>
       </c>
       <c r="B842">
         <v>0</v>
@@ -12190,7 +12190,7 @@
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>covil.045</v>
+        <v>indio_mma</v>
       </c>
       <c r="B843">
         <v>0</v>
@@ -12204,7 +12204,7 @@
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>allandelano</v>
+        <v>covil.045</v>
       </c>
       <c r="B844">
         <v>0</v>
@@ -12218,7 +12218,7 @@
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>alomaraujo</v>
+        <v>allandelano</v>
       </c>
       <c r="B845">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>theanimallifemovement</v>
+        <v>alomaraujo</v>
       </c>
       <c r="B846">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>tombg_64</v>
+        <v>theanimallifemovement</v>
       </c>
       <c r="B847">
         <v>0</v>
@@ -12260,7 +12260,7 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>michaeloliveiramma</v>
+        <v>tombg_64</v>
       </c>
       <c r="B848">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>andreichubotaru94</v>
+        <v>michaeloliveiramma</v>
       </c>
       <c r="B849">
         <v>0</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>carinhakkz</v>
+        <v>andreichubotaru94</v>
       </c>
       <c r="B850">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>helaynecrisl</v>
+        <v>carinhakkz</v>
       </c>
       <c r="B851">
         <v>0</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>oliveiraa_00.11</v>
+        <v>helaynecrisl</v>
       </c>
       <c r="B852">
         <v>0</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>udilimaheroi</v>
+        <v>oliveiraa_00.11</v>
       </c>
       <c r="B853">
         <v>0</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>mirnacaroline</v>
+        <v>udilimaheroi</v>
       </c>
       <c r="B854">
         <v>0</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>lmk_sport</v>
+        <v>mirnacaroline</v>
       </c>
       <c r="B855">
         <v>0</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>fher.nando_</v>
+        <v>lmk_sport</v>
       </c>
       <c r="B856">
         <v>0</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B857">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>adrianaramosalvesribeiro</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B858">
         <v>0</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>djuliaarianamma</v>
+        <v>adrianaramosalvesribeiro</v>
       </c>
       <c r="B859">
         <v>0</v>
@@ -12428,7 +12428,7 @@
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>raulbasilioo</v>
+        <v>djuliaarianamma</v>
       </c>
       <c r="B860">
         <v>0</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>heloisa_elohim</v>
+        <v>raulbasilioo</v>
       </c>
       <c r="B861">
         <v>0</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>hostonhugo</v>
+        <v>heloisa_elohim</v>
       </c>
       <c r="B862">
         <v>0</v>
@@ -12470,7 +12470,7 @@
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>ellida_guimaraes</v>
+        <v>hostonhugo</v>
       </c>
       <c r="B863">
         <v>0</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>massoterapeuta_bemestarr</v>
+        <v>ellida_guimaraes</v>
       </c>
       <c r="B864">
         <v>0</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>alexandrefideliis</v>
+        <v>massoterapeuta_bemestarr</v>
       </c>
       <c r="B865">
         <v>0</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>pammygaryo</v>
+        <v>alexandrefideliis</v>
       </c>
       <c r="B866">
         <v>0</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>beatrizosilveira</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B867">
         <v>0</v>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>bastazinifilho</v>
+        <v>beatrizosilveira</v>
       </c>
       <c r="B868">
         <v>0</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>sem_saida.12</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B869">
         <v>0</v>
@@ -12568,7 +12568,7 @@
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>sougustavorosa</v>
+        <v>sem_saida.12</v>
       </c>
       <c r="B870">
         <v>0</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>lincoln__puig77</v>
+        <v>sougustavorosa</v>
       </c>
       <c r="B871">
         <v>0</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>anselmo.azevedo</v>
+        <v>lincoln__puig77</v>
       </c>
       <c r="B872">
         <v>0</v>
@@ -12610,7 +12610,7 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B873">
         <v>0</v>
@@ -12624,7 +12624,7 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B874">
         <v>0</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B875">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B876">
         <v>0</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>marcusvgsz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B877">
         <v>0</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B878">
         <v>0</v>
@@ -12694,7 +12694,7 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B879">
         <v>0</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B880">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B881">
         <v>0</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B882">
         <v>0</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B883">
         <v>0</v>
@@ -12764,7 +12764,7 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>pepefightteam</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B884">
         <v>0</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>danieldias7s</v>
+        <v>pepefightteam</v>
       </c>
       <c r="B885">
         <v>0</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B886">
         <v>0</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B887">
         <v>0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B888">
         <v>0</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B889">
         <v>0</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B890">
         <v>0</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>mma.fisio</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B891">
         <v>0</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>thaynara_victoria_</v>
+        <v>mma.fisio</v>
       </c>
       <c r="B892">
         <v>0</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>tamarapq</v>
+        <v>thaynara_victoria_</v>
       </c>
       <c r="B893">
         <v>0</v>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>wendel_bjj14</v>
+        <v>tamarapq</v>
       </c>
       <c r="B894">
         <v>0</v>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B895">
         <v>0</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B896">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B897">
         <v>0</v>
@@ -12960,7 +12960,7 @@
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B898">
         <v>0</v>
@@ -12974,7 +12974,7 @@
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B899">
         <v>0</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B900">
         <v>0</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B901">
         <v>0</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B902">
         <v>0</v>
@@ -13030,7 +13030,7 @@
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B903">
         <v>0</v>
@@ -13044,7 +13044,7 @@
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>danielplayboymt</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B904">
         <v>0</v>
@@ -13058,7 +13058,7 @@
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>fix.pec</v>
+        <v>danielplayboymt</v>
       </c>
       <c r="B905">
         <v>0</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>chunco_424</v>
+        <v>fix.pec</v>
       </c>
       <c r="B906">
         <v>0</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>denisalagoanobjj</v>
+        <v>chunco_424</v>
       </c>
       <c r="B907">
         <v>0</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>priscilaapbatista</v>
+        <v>denisalagoanobjj</v>
       </c>
       <c r="B908">
         <v>0</v>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>josita_bjj</v>
+        <v>priscilaapbatista</v>
       </c>
       <c r="B909">
         <v>0</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>roxostrike</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B910">
         <v>0</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>shirleypalestrina6</v>
+        <v>roxostrike</v>
       </c>
       <c r="B911">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>flipebiano</v>
+        <v>shirleypalestrina6</v>
       </c>
       <c r="B912">
         <v>0</v>
@@ -13170,7 +13170,7 @@
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>ruanmiqueias</v>
+        <v>flipebiano</v>
       </c>
       <c r="B913">
         <v>0</v>
@@ -13184,7 +13184,7 @@
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>babimaciel1</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B914">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>manoel.brum</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B915">
         <v>0</v>
@@ -13212,7 +13212,7 @@
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>horadopower</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B916">
         <v>0</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>lyvia_genuina</v>
+        <v>horadopower</v>
       </c>
       <c r="B917">
         <v>0</v>
@@ -13240,7 +13240,7 @@
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>delariva_belem</v>
+        <v>lyvia_genuina</v>
       </c>
       <c r="B918">
         <v>0</v>
@@ -13254,7 +13254,7 @@
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>juugxmes</v>
+        <v>delariva_belem</v>
       </c>
       <c r="B919">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>gabrielsantosufc_</v>
+        <v>juugxmes</v>
       </c>
       <c r="B920">
         <v>0</v>
@@ -13282,7 +13282,7 @@
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>_matheustiberio</v>
+        <v>gabrielsantosufc_</v>
       </c>
       <c r="B921">
         <v>0</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>sthefany_ochoao</v>
+        <v>_matheustiberio</v>
       </c>
       <c r="B922">
         <v>0</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>reynitaoblitasbustamante</v>
+        <v>sthefany_ochoao</v>
       </c>
       <c r="B923">
         <v>0</v>
@@ -13324,7 +13324,7 @@
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>joseochoa.mma</v>
+        <v>reynitaoblitasbustamante</v>
       </c>
       <c r="B924">
         <v>0</v>
@@ -13338,7 +13338,7 @@
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>gabriellb.andrade</v>
+        <v>joseochoa.mma</v>
       </c>
       <c r="B925">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>romelluistro</v>
+        <v>gabriellb.andrade</v>
       </c>
       <c r="B926">
         <v>0</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>yuricapelasso</v>
+        <v>romelluistro</v>
       </c>
       <c r="B927">
         <v>0</v>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>lucasfenomeno_ufc</v>
+        <v>yuricapelasso</v>
       </c>
       <c r="B928">
         <v>0</v>
@@ -13394,7 +13394,7 @@
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>gabriell_marcus</v>
+        <v>lucasfenomeno_ufc</v>
       </c>
       <c r="B929">
         <v>0</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>lazyboy.ufc</v>
+        <v>gabriell_marcus</v>
       </c>
       <c r="B930">
         <v>0</v>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>matheusdouradomma</v>
+        <v>lazyboy.ufc</v>
       </c>
       <c r="B931">
         <v>0</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>rafaelsouza7586</v>
+        <v>matheusdouradomma</v>
       </c>
       <c r="B932">
         <v>0</v>
@@ -13450,7 +13450,7 @@
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>land_on_martelo_308</v>
+        <v>rafaelsouza7586</v>
       </c>
       <c r="B933">
         <v>0</v>
@@ -13464,7 +13464,7 @@
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>dodge_big_johnson29</v>
+        <v>land_on_martelo_308</v>
       </c>
       <c r="B934">
         <v>0</v>
@@ -13478,7 +13478,7 @@
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>dj__freckles</v>
+        <v>dodge_big_johnson29</v>
       </c>
       <c r="B935">
         <v>0</v>
@@ -13492,7 +13492,7 @@
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>regis18vieira</v>
+        <v>dj__freckles</v>
       </c>
       <c r="B936">
         <v>0</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>andy.techera.12</v>
+        <v>regis18vieira</v>
       </c>
       <c r="B937">
         <v>0</v>
@@ -13520,7 +13520,7 @@
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>celiogarcia6</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B938">
         <v>0</v>
@@ -13534,7 +13534,7 @@
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>luluakio</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B939">
         <v>0</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>barreto.boxe</v>
+        <v>luluakio</v>
       </c>
       <c r="B940">
         <v>0</v>
@@ -13562,7 +13562,7 @@
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>lusoaresjj</v>
+        <v>barreto.boxe</v>
       </c>
       <c r="B941">
         <v>0</v>
@@ -13576,28 +13576,42 @@
     </row>
     <row r="942">
       <c r="A942" t="str">
+        <v>lusoaresjj</v>
+      </c>
+      <c r="B942">
+        <v>0</v>
+      </c>
+      <c r="C942">
+        <v>1</v>
+      </c>
+      <c r="D942">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="str">
         <v>sharingan_mma</v>
       </c>
-      <c r="B942">
-        <v>0</v>
-      </c>
-      <c r="C942">
-        <v>1</v>
-      </c>
-      <c r="D942">
+      <c r="B943">
+        <v>0</v>
+      </c>
+      <c r="C943">
+        <v>1</v>
+      </c>
+      <c r="D943">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D942"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D943"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:D180"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13618,13 +13632,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>2254</v>
+        <v>2339</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2132</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="3">
@@ -13632,7 +13646,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>1376</v>
+        <v>1396</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -13660,13 +13674,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
@@ -13674,7 +13688,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -13702,7 +13716,7 @@
         <v>malu832757</v>
       </c>
       <c r="B8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -13716,13 +13730,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -13730,7 +13744,7 @@
         <v>im.duda02</v>
       </c>
       <c r="B10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -13744,7 +13758,7 @@
         <v>anayachiottoni</v>
       </c>
       <c r="B11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -13755,21 +13769,21 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>anaaj_camargo</v>
+        <v>n.daily22</v>
       </c>
       <c r="B12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>n.daily22</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B13">
         <v>28</v>
@@ -13778,7 +13792,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -13786,13 +13800,13 @@
         <v>rhuansales.mma</v>
       </c>
       <c r="B14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -13800,7 +13814,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -13814,7 +13828,7 @@
         <v>kamile_oliveria_10</v>
       </c>
       <c r="B16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -13828,7 +13842,7 @@
         <v>rayn.avaro</v>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -13842,7 +13856,7 @@
         <v>jujua_maral1</v>
       </c>
       <c r="B18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -13856,7 +13870,7 @@
         <v>grapplerfight</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -13867,13 +13881,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>washington_cassisno</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B20">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>15</v>
@@ -13881,30 +13895,30 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>propeace_fight</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B21">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>arafight_pesc</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -13912,7 +13926,7 @@
         <v>thundergrapple</v>
       </c>
       <c r="B23">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -13926,7 +13940,7 @@
         <v>galler_peace</v>
       </c>
       <c r="B24">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -13940,7 +13954,7 @@
         <v>figh_grappler</v>
       </c>
       <c r="B25">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -13954,7 +13968,7 @@
         <v>johnmma9</v>
       </c>
       <c r="B26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -13968,7 +13982,7 @@
         <v>ottonianalivia</v>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -13982,41 +13996,41 @@
         <v>mmmarc20</v>
       </c>
       <c r="B28">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>combintel</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B29">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>mar_iarmaria</v>
+        <v>combintel</v>
       </c>
       <c r="B30">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -14024,7 +14038,7 @@
         <v>laisrebeiro10</v>
       </c>
       <c r="B31">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -14038,24 +14052,24 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B32">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>guilhermemirandamma</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
         <v>7</v>
@@ -14063,30 +14077,30 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>italothearcher</v>
+        <v>guilhermemirandamma</v>
       </c>
       <c r="B34">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>kelly_ottoni</v>
+        <v>italothearcher</v>
       </c>
       <c r="B35">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -14133,55 +14147,55 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>enzoferrari680</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>victus_torquatus00</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>victus_torquatus00</v>
       </c>
       <c r="B41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>maxgandra</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -14189,44 +14203,44 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>god.motivacao</v>
+        <v>maxgandra</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>5</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>pg_grappling</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B45">
         <v>5</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -14301,27 +14315,27 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>decio_bjj</v>
+        <v>carlosalbertobarretojr</v>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>eolucasrosa</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -14329,21 +14343,21 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>aj_mma_</v>
+        <v>decio_bjj</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>daniezzyy</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B54">
         <v>4</v>
@@ -14352,57 +14366,57 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>elienelucindo_oficial</v>
+        <v>daniezzyy</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>luigimoraess</v>
+        <v>elienelucindo_oficial</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C56">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>marcelogabrielmma</v>
+        <v>luigimoraess</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>vincenzo_pit_monster</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -14413,7 +14427,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>rian.vitorjj</v>
+        <v>vincenzo_pit_monster</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -14427,7 +14441,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>danielrodrigues1000</v>
+        <v>rian.vitorjj</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -14441,7 +14455,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>lonbradao__777</v>
+        <v>danielrodrigues1000</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -14455,35 +14469,35 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>bruno_murata</v>
+        <v>lonbradao__777</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>adrianoams7</v>
+        <v>bruno_murata</v>
       </c>
       <c r="B63">
         <v>4</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>deboralvesoficial</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B64">
         <v>4</v>
@@ -14497,7 +14511,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>jorgeantoniopba</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B65">
         <v>4</v>
@@ -14511,7 +14525,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>rrafaelins</v>
+        <v>deboralvesoficial</v>
       </c>
       <c r="B66">
         <v>4</v>
@@ -14525,38 +14539,38 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>vndcardoso</v>
+        <v>jorgeantoniopba</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>cesar.boanerges</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>jheffzao</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -14567,21 +14581,21 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>jvxz______</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>cairorochamma</v>
+        <v>jheffzao</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -14595,7 +14609,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>victus_torquatus</v>
+        <v>jvxz______</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -14609,49 +14623,49 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>efsantos.oficial</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>hollenberg.personal</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>carlosalbertobarretojr</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ninjatheorist</v>
+        <v>hollenberg.personal</v>
       </c>
       <c r="B76">
         <v>3</v>
@@ -15197,13 +15211,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>mmapalpitex</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -15211,7 +15225,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -15225,7 +15239,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>kauan_mantas</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -15239,7 +15253,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>erickdiaseds</v>
+        <v>kauan_mantas</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -15253,7 +15267,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>emersonapache</v>
+        <v>erickdiaseds</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -15267,7 +15281,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>nataliavidal965</v>
+        <v>emersonapache</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -15281,7 +15295,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>manoel_maranhaobjjmma</v>
+        <v>nataliavidal965</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -15295,7 +15309,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>ruanpantojanutricionista</v>
+        <v>manoel_maranhaobjjmma</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -15309,7 +15323,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>alexandreconsentino</v>
+        <v>ruanpantojanutricionista</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -15323,7 +15337,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>luizpaulomma</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -15337,7 +15351,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>luizpaulomma</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -15351,21 +15365,21 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>epicjoel2022</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>tvlinsoficial</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -15379,7 +15393,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>_itamar_maximo</v>
+        <v>epicjoel2022</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -15393,7 +15407,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>mg._silvaa_</v>
+        <v>tvlinsoficial</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -15407,7 +15421,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sarahfmaia</v>
+        <v>_itamar_maximo</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -15421,7 +15435,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>desativado_no_off33</v>
+        <v>mg._silvaa_</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -15435,21 +15449,21 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>lucasbaddoure</v>
+        <v>sarahfmaia</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>paulo_rafa_personal</v>
+        <v>desativado_no_off33</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -15463,21 +15477,21 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>endurance_guia</v>
+        <v>lucasbaddoure</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>cadupereirss</v>
+        <v>paulo_rafa_personal</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -15491,7 +15505,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>instrutorindiovs</v>
+        <v>endurance_guia</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -15505,7 +15519,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>lopes.felipe13</v>
+        <v>cadupereirss</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -15519,7 +15533,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>marciokeske</v>
+        <v>instrutorindiovs</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -15533,7 +15547,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>percepcar</v>
+        <v>lopes.felipe13</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -15547,7 +15561,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>_jullianadacruz</v>
+        <v>marciokeske</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -15561,7 +15575,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>thiagoxavier13</v>
+        <v>percepcar</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -15575,7 +15589,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>marchi_vinicius</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -15589,7 +15603,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>rafa_speda</v>
+        <v>thiagoxavier13</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -15603,7 +15617,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>m1guelmolina</v>
+        <v>marchi_vinicius</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -15617,7 +15631,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>rosantos83</v>
+        <v>rafa_speda</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -15631,7 +15645,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>caiogoularts</v>
+        <v>m1guelmolina</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -15645,7 +15659,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>cassiolee013</v>
+        <v>rosantos83</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -15659,7 +15673,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>alinefurlann</v>
+        <v>caiogoularts</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -15673,7 +15687,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>felipedasilvalucas.bjj</v>
+        <v>cassiolee013</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -15687,7 +15701,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>murilomuaythai</v>
+        <v>alinefurlann</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -15701,7 +15715,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>programaparadois</v>
+        <v>felipedasilvalucas.bjj</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -15715,7 +15729,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>cotty_bigmonster</v>
+        <v>murilomuaythai</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -15729,7 +15743,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>alissonlayza</v>
+        <v>programaparadois</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -15743,7 +15757,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>perninhakickboxing</v>
+        <v>cotty_bigmonster</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -15757,41 +15771,41 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>viniciustbf</v>
+        <v>alissonlayza</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C155">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>marcos_tailandess</v>
+        <v>perninhakickboxing</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C156">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>disk_egg</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C157">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -15799,55 +15813,55 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>kalaga_vito</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D158">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>danilo_marquesc</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B159">
         <v>0</v>
       </c>
       <c r="C159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D159">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>denilson.unit</v>
+        <v>disk_egg</v>
       </c>
       <c r="B160">
         <v>0</v>
       </c>
       <c r="C160">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>vieirabjj____</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B161">
         <v>0</v>
       </c>
       <c r="C161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -15855,7 +15869,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>canalgolpebaixo</v>
+        <v>danilo_marquesc</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -15869,7 +15883,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>leandro__parpinelli</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -15883,7 +15897,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>bruno_pontes1992</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -15897,7 +15911,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -15911,7 +15925,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>dudaadantass</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -15925,7 +15939,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>mauriciomouraprev</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -15939,7 +15953,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>_pedro0h</v>
+        <v>aida_dos_sonhos</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -15953,7 +15967,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>eliassilverio</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -15962,12 +15976,12 @@
         <v>1</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>andy.techera.12</v>
+        <v>mauriciomouraprev</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -15976,12 +15990,12 @@
         <v>1</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>celiogarcia6</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -15990,12 +16004,12 @@
         <v>1</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>jean_ferreira_br</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -16009,7 +16023,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>luluakio</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -16023,7 +16037,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>adriano.trator</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -16037,7 +16051,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>barreto.boxe</v>
+        <v>luluakio</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -16051,7 +16065,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>pauloserrati</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -16065,7 +16079,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>lusoaresjj</v>
+        <v>barreto.boxe</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -16079,21 +16093,49 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
+        <v>pauloserrati</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>lusoaresjj</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
         <v>sharingan_mma</v>
       </c>
-      <c r="B178">
-        <v>0</v>
-      </c>
-      <c r="C178">
-        <v>1</v>
-      </c>
-      <c r="D178">
+      <c r="B180">
+        <v>0</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D178"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D180"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D945"/>
+  <dimension ref="A1:D946"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13284</v>
+        <v>13294</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12022</v>
+        <v>12032</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3423</v>
+        <v>3463</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>1314</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="4">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2164</v>
+        <v>2168</v>
       </c>
       <c r="C5">
         <v>30</v>
       </c>
       <c r="D5">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7">
@@ -545,7 +545,7 @@
         <v>combintel</v>
       </c>
       <c r="B11">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -629,7 +629,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -643,7 +643,7 @@
         <v>johnmma9</v>
       </c>
       <c r="B18">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -657,7 +657,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B19">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -671,13 +671,13 @@
         <v>malu832757</v>
       </c>
       <c r="B20">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
@@ -783,7 +783,7 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B28">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -1018,30 +1018,30 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>n.daily22</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B45">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>anayachiottoni</v>
+        <v>n.daily22</v>
       </c>
       <c r="B46">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -1060,91 +1060,91 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>leandrosolano_mma</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B48">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C48">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>cleyton_jesuss</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B49">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>leandrosolano_mma</v>
       </c>
       <c r="B50">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D50">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>rhuansales.mma</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B51">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D51">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>shawlin13oficial</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B52">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>pedromadeira.s</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B53">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>_cardoso_caio_</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B54">
         <v>31</v>
@@ -1153,21 +1153,21 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>rayn.avaro</v>
+        <v>_cardoso_caio_</v>
       </c>
       <c r="B55">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
@@ -1214,55 +1214,55 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>eliassilverio</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B59">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C59">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>jujua_maral1</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B60">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D60">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>alvesmidih</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B61">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>propeace_fight</v>
+        <v>jujua_maral1</v>
       </c>
       <c r="B62">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>16</v>
@@ -1270,77 +1270,77 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>mar_iarmaria</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B63">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>arafight_pesc</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B64">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>marcelogabrielmma</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B65">
         <v>23</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>grapplerfight</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B66">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D66">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>tabajaraharu</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B67">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C67">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>vndcardoso</v>
+        <v>galler_peace</v>
       </c>
       <c r="B68">
         <v>19</v>
@@ -1349,12 +1349,12 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>docinhos26</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B69">
         <v>19</v>
@@ -1363,49 +1363,49 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>thundergrapple</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B70">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D70">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>galler_peace</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B71">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>figh_grappler</v>
+        <v>docinhos26</v>
       </c>
       <c r="B72">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -1634,72 +1634,72 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>macamariotti</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B89">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C89">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>guilhermemirandamma</v>
+        <v>macamariotti</v>
       </c>
       <c r="B90">
         <v>7</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D90">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>luizalaguerabjj</v>
+        <v>guilhermemirandamma</v>
       </c>
       <c r="B91">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>cpetemma248</v>
+        <v>luizalaguerabjj</v>
       </c>
       <c r="B92">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C92">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>cpetemma248</v>
       </c>
       <c r="B93">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -2068,80 +2068,80 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>jorgeantoniopba</v>
+        <v>carlosalbertobarretojr</v>
       </c>
       <c r="B120">
         <v>8</v>
       </c>
       <c r="C120">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>alfredo_miras</v>
+        <v>jorgeantoniopba</v>
       </c>
       <c r="B121">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>mimuniz.bjj</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B122">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C122">
         <v>0</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>lucascardosol__</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C123">
         <v>0</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>biabasiliojj</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B124">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>deboralvesoficial</v>
+        <v>biabasiliojj</v>
       </c>
       <c r="B125">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>carlosalbertobarretojr</v>
+        <v>deboralvesoficial</v>
       </c>
       <c r="B126">
         <v>7</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>fabinho_falcao_</v>
+        <v>natanborges001</v>
       </c>
       <c r="B178">
         <v>2</v>
@@ -2889,54 +2889,54 @@
         <v>2</v>
       </c>
       <c r="D178">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>odeivisoncardoso</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B179">
         <v>2</v>
       </c>
       <c r="C179">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D179">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B180">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D180">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>peacegrappler_archive</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B181">
         <v>3</v>
       </c>
       <c r="C181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D181">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>reifernandes</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B182">
         <v>3</v>
@@ -2950,44 +2950,44 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B183">
         <v>3</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D183">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>mauriciomouraprev</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B184">
         <v>3</v>
       </c>
       <c r="C184">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D184">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>natanborges001</v>
+        <v>mauriciomouraprev</v>
       </c>
       <c r="B185">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C185">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D185">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -3398,13 +3398,13 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>cairorochamma</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B215">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D215">
         <v>1</v>
@@ -3412,41 +3412,41 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B216">
         <v>2</v>
       </c>
       <c r="C216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D216">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>alexsandra_kairos</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B217">
         <v>2</v>
       </c>
       <c r="C217">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B218">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D218">
         <v>0</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>jocyrefan_bjj_mma</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B219">
         <v>3</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>multiplicaaba</v>
+        <v>jocyrefan_bjj_mma</v>
       </c>
       <c r="B220">
         <v>3</v>
@@ -3482,13 +3482,13 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>disk_egg</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B221">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C221">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -3496,63 +3496,63 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>disk_egg</v>
       </c>
       <c r="B222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C222">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>jean_ferreira_br</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B223">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C223">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>jose_luiz_thome</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B224">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D224">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>efsantos.oficial</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B225">
         <v>1</v>
       </c>
       <c r="C225">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D225">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>marifferreirac</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3561,32 +3561,32 @@
         <v>1</v>
       </c>
       <c r="D226">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>pauloserrati</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C227">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D227">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>mineirinho_jj</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B228">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D228">
         <v>1</v>
@@ -3594,35 +3594,35 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>juliochagasmma</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>orafao1</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B230">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C230">
         <v>0</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>lopesbrunao</v>
+        <v>juliochagasmma</v>
       </c>
       <c r="B231">
         <v>2</v>
@@ -3636,21 +3636,21 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>claudiaottoni19</v>
+        <v>orafao1</v>
       </c>
       <c r="B232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C232">
         <v>0</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>sr.valter</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B233">
         <v>2</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B234">
         <v>2</v>
@@ -3678,27 +3678,27 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>meol.socialmidia</v>
+        <v>sr.valter</v>
       </c>
       <c r="B235">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C235">
         <v>0</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>yamasakinhobjj</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B236">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B237">
         <v>3</v>
@@ -3720,21 +3720,21 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>cami28_l</v>
+        <v>yamasakinhobjj</v>
       </c>
       <c r="B238">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D238">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>flaviakaena</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B239">
         <v>3</v>
@@ -3748,21 +3748,21 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>chrislima____</v>
+        <v>cami28_l</v>
       </c>
       <c r="B240">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C240">
         <v>0</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>c.m_figth</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B241">
         <v>3</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>chrislima____</v>
       </c>
       <c r="B242">
         <v>2</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>e_car.doso</v>
+        <v>c.m_figth</v>
       </c>
       <c r="B243">
         <v>3</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>dgswillian</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B244">
         <v>2</v>
@@ -3818,77 +3818,77 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>ufc_paramountsports</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C245">
         <v>0</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>couragemma</v>
+        <v>dgswillian</v>
       </c>
       <c r="B246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C246">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D246">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>kaua_limaofc</v>
+        <v>couragemma</v>
       </c>
       <c r="B247">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C247">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ruangzk</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B248">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C248">
         <v>0</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>emerson_lucaszx</v>
+        <v>ruangzk</v>
       </c>
       <c r="B249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C249">
         <v>0</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>clouddhidden</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B250">
         <v>2</v>
@@ -3902,21 +3902,21 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>_matheusifernandes</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C251">
         <v>0</v>
       </c>
       <c r="D251">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>bryantank_</v>
+        <v>_matheusifernandes</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>ruan.arcanjo01</v>
+        <v>bryantank_</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>coyote_style_hair</v>
+        <v>ruan.arcanjo01</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,83 +3958,83 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>sueli_ferreira48</v>
+        <v>coyote_style_hair</v>
       </c>
       <c r="B255">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C255">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>edsoncostateixeirabjj</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B256">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D256">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>klein_hila</v>
+        <v>edsoncostateixeirabjj</v>
       </c>
       <c r="B257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>klein_hila</v>
       </c>
       <c r="B258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>vnciuss__df</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B259">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C259">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D259">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B260">
         <v>2</v>
       </c>
       <c r="C260">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>tassiogiloficial</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B261">
         <v>2</v>
@@ -4056,35 +4056,35 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B262">
         <v>2</v>
       </c>
       <c r="C262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D262">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>richards_brusen</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B263">
         <v>2</v>
       </c>
       <c r="C263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D263">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>natalan_wilgner</v>
+        <v>richards_brusen</v>
       </c>
       <c r="B264">
         <v>2</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>leticiamartinspro</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B265">
         <v>2</v>
@@ -4112,72 +4112,72 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>danilo_marquesc</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B266">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D266">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>lucasspaulista</v>
+        <v>danilo_marquesc</v>
       </c>
       <c r="B267">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>lucasspaulista</v>
       </c>
       <c r="B268">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D268">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D269">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>julianoalicate</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B270">
         <v>2</v>
       </c>
       <c r="C270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D270">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -13630,16 +13630,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="946">
+      <c r="A946" t="str">
+        <v>thaisadantas</v>
+      </c>
+      <c r="B946">
+        <v>0</v>
+      </c>
+      <c r="C946">
+        <v>1</v>
+      </c>
+      <c r="D946">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D945"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D946"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D183"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13660,13 +13674,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>2368</v>
+        <v>2378</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2246</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="3">
@@ -13674,13 +13688,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>1396</v>
+        <v>1436</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>858</v>
+        <v>898</v>
       </c>
     </row>
     <row r="4">
@@ -13702,13 +13716,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6">
@@ -13716,13 +13730,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -13744,13 +13758,13 @@
         <v>malu832757</v>
       </c>
       <c r="B8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -13783,58 +13797,58 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>n.daily22</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>anayachiottoni</v>
+        <v>n.daily22</v>
       </c>
       <c r="B12">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>anaaj_camargo</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B13">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>rhuansales.mma</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -13842,7 +13856,7 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -13856,13 +13870,13 @@
         <v>kamile_oliveria_10</v>
       </c>
       <c r="B16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -13870,83 +13884,83 @@
         <v>rayn.avaro</v>
       </c>
       <c r="B17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>jujua_maral1</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B18">
         <v>21</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>propeace_fight</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B19">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>arafight_pesc</v>
+        <v>jujua_maral1</v>
       </c>
       <c r="B20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>washington_cassisno</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B21">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>grapplerfight</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -13954,7 +13968,7 @@
         <v>johnmma9</v>
       </c>
       <c r="B23">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -13965,7 +13979,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ottonianalivia</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B24">
         <v>19</v>
@@ -13974,91 +13988,91 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>thundergrapple</v>
+        <v>galler_peace</v>
       </c>
       <c r="B25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>galler_peace</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B26">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>figh_grappler</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B27">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>mmmarc20</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B28">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>mar_iarmaria</v>
+        <v>combintel</v>
       </c>
       <c r="B29">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>combintel</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B30">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -14080,7 +14094,7 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B32">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -14178,7 +14192,7 @@
         <v>cjrnavalhaoficial</v>
       </c>
       <c r="B39">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -14301,27 +14315,27 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>thiagodossantossilvasantos</v>
+        <v>carlosalbertobarretojr</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>anderson.logan.35</v>
+        <v>thiagodossantossilvasantos</v>
       </c>
       <c r="B49">
         <v>4</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -14329,30 +14343,30 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>mayarinhafreestyle</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>carlosalbertobarretojr</v>
+        <v>mayarinhafreestyle</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -14511,30 +14525,30 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bruno_murata</v>
+        <v>natanborges001</v>
       </c>
       <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
         <v>4</v>
-      </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>natanborges001</v>
+        <v>bruno_murata</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -14665,13 +14679,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>cairorochamma</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -14679,24 +14693,24 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>efsantos.oficial</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -14707,27 +14721,27 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>hollenberg.personal</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -14735,7 +14749,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>e_car.doso</v>
+        <v>hollenberg.personal</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -14749,7 +14763,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>gdazuera</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -14763,21 +14777,21 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>jose_luiz_thome</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>dgswillian</v>
+        <v>gdazuera</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -14791,13 +14805,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ufc_paramountsports</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -14805,13 +14819,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ryangandraufc</v>
+        <v>dgswillian</v>
       </c>
       <c r="B84">
         <v>2</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -14819,21 +14833,21 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>fredoctmma</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -14847,30 +14861,30 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>julianoalicate</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -16189,9 +16203,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>thaisadantas</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D182"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D183"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D946"/>
+  <dimension ref="A1:D947"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13294</v>
+        <v>13317</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12032</v>
+        <v>12055</v>
       </c>
     </row>
     <row r="3">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="7">
@@ -559,13 +559,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B12">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C12">
         <v>7</v>
       </c>
       <c r="D12">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13">
@@ -671,13 +671,13 @@
         <v>malu832757</v>
       </c>
       <c r="B20">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
@@ -934,198 +934,198 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>_.maduoliveira_</v>
+        <v>im.duda02</v>
       </c>
       <c r="B39">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>leonardomesquitamma</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B40">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>im.duda02</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B41">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ottonianalivia</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B42">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>italothearcher</v>
+        <v>n.daily22</v>
       </c>
       <c r="B43">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C43">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>victus_torquatus00</v>
+        <v>italothearcher</v>
       </c>
       <c r="B44">
         <v>35</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>anayachiottoni</v>
+        <v>victus_torquatus00</v>
       </c>
       <c r="B45">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>n.daily22</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B46">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>enzoferrari680</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B47">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B48">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>rhuansales.mma</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B49">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>leandrosolano_mma</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B50">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C50">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>cleyton_jesuss</v>
+        <v>leandrosolano_mma</v>
       </c>
       <c r="B51">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D51">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>rayn.avaro</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B52">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D52">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
@@ -1186,128 +1186,128 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>thiagoauper</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B57">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>gra_jpereira</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B58">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>propeace_fight</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B59">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>eliassilverio</v>
+        <v>jujua_maral1</v>
       </c>
       <c r="B60">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C60">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>arafight_pesc</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B61">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>jujua_maral1</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B62">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D62">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>grapplerfight</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B63">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>alvesmidih</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B64">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>mar_iarmaria</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B65">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -1438,44 +1438,44 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>gustavomohallem</v>
+        <v>laisrebeiro10</v>
       </c>
       <c r="B75">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>tawanregismma</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B76">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>laisrebeiro10</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B77">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -1508,83 +1508,83 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>manoel_maranhaobjjmma</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B80">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>gdazuera</v>
+        <v>manoel_maranhaobjjmma</v>
       </c>
       <c r="B81">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C81">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ravenrodriguez___</v>
+        <v>gdazuera</v>
       </c>
       <c r="B82">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C82">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>marc0s.azv</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B83">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D83">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>danielbrbjj</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B84">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C84">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>kelly_ottoni</v>
+        <v>danielbrbjj</v>
       </c>
       <c r="B85">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85">
         <v>7</v>
@@ -2502,13 +2502,13 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B151">
         <v>3</v>
       </c>
       <c r="C151">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>3</v>
@@ -2516,153 +2516,153 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ismaeldaniell</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B152">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C152">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>rafaelmacapa_</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B153">
         <v>4</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>daniezzyy</v>
+        <v>rafaelmacapa_</v>
       </c>
       <c r="B154">
         <v>4</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D154">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>glm.barbosa</v>
+        <v>daniezzyy</v>
       </c>
       <c r="B155">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>fernando.mma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C156">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>davizoka_mascote</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>enzo_henrik</v>
+        <v>davizoka_mascote</v>
       </c>
       <c r="B158">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C158">
         <v>0</v>
       </c>
       <c r="D158">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>emersonriosmma</v>
+        <v>enzo_henrik</v>
       </c>
       <c r="B159">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C159">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>douglasoct_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B160">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C160">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D160">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>eric.shpritz</v>
+        <v>douglasoct_mma</v>
       </c>
       <c r="B161">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C161">
         <v>2</v>
       </c>
       <c r="D161">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>marcocanatelli</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B162">
         <v>4</v>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -2670,108 +2670,108 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>benjafloripabjj</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B163">
         <v>4</v>
       </c>
       <c r="C163">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>heltoncm2002</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B164">
         <v>4</v>
       </c>
       <c r="C164">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>pitbullandrade</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B165">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
       <c r="D165">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>zedelano</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B166">
         <v>3</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D166">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>salost.ofc</v>
+        <v>zedelano</v>
       </c>
       <c r="B167">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C167">
         <v>0</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>gabrielsouzamma</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B168">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D168">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B169">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>y.arthur_01</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B170">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -2782,63 +2782,63 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>leobahiamma</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B171">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C171">
         <v>0</v>
       </c>
       <c r="D171">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>s__simone__</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B172">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C172">
         <v>0</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>maxbjj_0</v>
+        <v>s__simone__</v>
       </c>
       <c r="B173">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C173">
         <v>0</v>
       </c>
       <c r="D173">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>vincenzo_pit_monster</v>
+        <v>maxbjj_0</v>
       </c>
       <c r="B174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C174">
         <v>0</v>
       </c>
       <c r="D174">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>rian.vitorjj</v>
+        <v>vincenzo_pit_monster</v>
       </c>
       <c r="B175">
         <v>2</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>danielrodrigues1000</v>
+        <v>rian.vitorjj</v>
       </c>
       <c r="B176">
         <v>2</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>lonbradao__777</v>
+        <v>danielrodrigues1000</v>
       </c>
       <c r="B177">
         <v>2</v>
@@ -2880,21 +2880,21 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>natanborges001</v>
+        <v>lonbradao__777</v>
       </c>
       <c r="B178">
         <v>2</v>
       </c>
       <c r="C178">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D178">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>fabinho_falcao_</v>
+        <v>natanborges001</v>
       </c>
       <c r="B179">
         <v>2</v>
@@ -2903,54 +2903,54 @@
         <v>2</v>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>odeivisoncardoso</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B180">
         <v>2</v>
       </c>
       <c r="C180">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D180">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B181">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D181">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>peacegrappler_archive</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B182">
         <v>3</v>
       </c>
       <c r="C182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D182">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>reifernandes</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B183">
         <v>3</v>
@@ -2964,55 +2964,55 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B184">
         <v>3</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>mauriciomouraprev</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B185">
         <v>3</v>
       </c>
       <c r="C185">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D185">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>mah__vergueiro</v>
+        <v>mauriciomouraprev</v>
       </c>
       <c r="B186">
         <v>3</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B187">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -3020,35 +3020,35 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>h.codasqueves</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B188">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>alexandreconsentino</v>
+        <v>h.codasqueves</v>
       </c>
       <c r="B189">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>lipe.ftt</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B190">
         <v>4</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B191">
         <v>4</v>
@@ -3076,21 +3076,21 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>vitorpetrino</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B192">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C192">
         <v>0</v>
       </c>
       <c r="D192">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>thompsonborralho</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B193">
         <v>3</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>devessonjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B194">
         <v>3</v>
@@ -3118,63 +3118,63 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>devessonjj</v>
       </c>
       <c r="B195">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C195">
         <v>0</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>artewebpersonalizados</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B196">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C196">
         <v>0</v>
       </c>
       <c r="D196">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B197">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C197">
         <v>0</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>victorhenriquebjj</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B198">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C198">
         <v>0</v>
       </c>
       <c r="D198">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>eduardorobjj</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B199">
         <v>2</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorobjj</v>
       </c>
       <c r="B200">
         <v>2</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>aerowellsports</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B201">
         <v>2</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>royrosiano</v>
+        <v>aerowellsports</v>
       </c>
       <c r="B202">
         <v>2</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>febrancatti</v>
+        <v>royrosiano</v>
       </c>
       <c r="B203">
         <v>2</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>sensei_rogerio_baltazar</v>
+        <v>febrancatti</v>
       </c>
       <c r="B204">
         <v>2</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>jpaulo.mma</v>
+        <v>sensei_rogerio_baltazar</v>
       </c>
       <c r="B205">
         <v>2</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>william_beckett12345</v>
+        <v>jpaulo.mma</v>
       </c>
       <c r="B206">
         <v>2</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>_falcao95_</v>
+        <v>william_beckett12345</v>
       </c>
       <c r="B207">
         <v>2</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>janyson.s</v>
+        <v>_falcao95_</v>
       </c>
       <c r="B208">
         <v>2</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>rodrigo.personal.muaythai</v>
+        <v>janyson.s</v>
       </c>
       <c r="B209">
         <v>2</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>andre_cr_daniel</v>
+        <v>rodrigo.personal.muaythai</v>
       </c>
       <c r="B210">
         <v>2</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>wilsinho.campos</v>
+        <v>andre_cr_daniel</v>
       </c>
       <c r="B211">
         <v>2</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>jheffzao</v>
+        <v>wilsinho.campos</v>
       </c>
       <c r="B212">
         <v>2</v>
@@ -3370,41 +3370,41 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>felipedasilvalucas.bjj</v>
+        <v>jheffzao</v>
       </c>
       <c r="B213">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C213">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>motumbo_jr</v>
+        <v>felipedasilvalucas.bjj</v>
       </c>
       <c r="B214">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D214">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>julianoalicate</v>
+        <v>motumbo_jr</v>
       </c>
       <c r="B215">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D215">
         <v>1</v>
@@ -3412,13 +3412,13 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>cairorochamma</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B216">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D216">
         <v>1</v>
@@ -3426,41 +3426,41 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B217">
         <v>2</v>
       </c>
       <c r="C217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D217">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>alexsandra_kairos</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B218">
         <v>2</v>
       </c>
       <c r="C218">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B219">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C219">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>jocyrefan_bjj_mma</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B220">
         <v>3</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>multiplicaaba</v>
+        <v>jocyrefan_bjj_mma</v>
       </c>
       <c r="B221">
         <v>3</v>
@@ -3496,13 +3496,13 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>disk_egg</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B222">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C222">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -3510,80 +3510,80 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>disk_egg</v>
       </c>
       <c r="B223">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C223">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D223">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>jean_ferreira_br</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B224">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C224">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>jose_luiz_thome</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B225">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D225">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>efsantos.oficial</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B226">
         <v>1</v>
       </c>
       <c r="C226">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D226">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>ufc_paramountsports</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>marifferreirac</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -3594,35 +3594,35 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>pauloserrati</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B229">
         <v>1</v>
       </c>
       <c r="C229">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D229">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>mineirinho_jj</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C230">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D230">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>juliochagasmma</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B231">
         <v>2</v>
@@ -3636,35 +3636,35 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>orafao1</v>
+        <v>juliochagasmma</v>
       </c>
       <c r="B232">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C232">
         <v>0</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>lopesbrunao</v>
+        <v>orafao1</v>
       </c>
       <c r="B233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C233">
         <v>0</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>claudiaottoni19</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B234">
         <v>2</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sr.valter</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B235">
         <v>2</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B236">
         <v>2</v>
@@ -3706,49 +3706,49 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>meol.socialmidia</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C237">
         <v>0</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>yamasakinhobjj</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B238">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>yamasakinhobjj</v>
       </c>
       <c r="B239">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>cami28_l</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B240">
         <v>3</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>flaviakaena</v>
+        <v>cami28_l</v>
       </c>
       <c r="B241">
         <v>3</v>
@@ -3776,133 +3776,133 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>chrislima____</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B242">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C242">
         <v>0</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>c.m_figth</v>
+        <v>chrislima____</v>
       </c>
       <c r="B243">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C243">
         <v>0</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>c.m_figth</v>
       </c>
       <c r="B244">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C244">
         <v>0</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>e_car.doso</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B245">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C245">
         <v>0</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>dgswillian</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B246">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C246">
         <v>0</v>
       </c>
       <c r="D246">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>couragemma</v>
+        <v>dgswillian</v>
       </c>
       <c r="B247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C247">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D247">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>kaua_limaofc</v>
+        <v>couragemma</v>
       </c>
       <c r="B248">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>ruangzk</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C249">
         <v>0</v>
       </c>
       <c r="D249">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>emerson_lucaszx</v>
+        <v>ruangzk</v>
       </c>
       <c r="B250">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C250">
         <v>0</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>clouddhidden</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B251">
         <v>2</v>
@@ -3916,21 +3916,21 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>_matheusifernandes</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C252">
         <v>0</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>bryantank_</v>
+        <v>_matheusifernandes</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>ruan.arcanjo01</v>
+        <v>bryantank_</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>coyote_style_hair</v>
+        <v>ruan.arcanjo01</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,83 +3972,83 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>sueli_ferreira48</v>
+        <v>coyote_style_hair</v>
       </c>
       <c r="B256">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C256">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>edsoncostateixeirabjj</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D257">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>klein_hila</v>
+        <v>edsoncostateixeirabjj</v>
       </c>
       <c r="B258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D258">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>klein_hila</v>
       </c>
       <c r="B259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>vnciuss__df</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B260">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C260">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D260">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B261">
         <v>2</v>
       </c>
       <c r="C261">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>tassiogiloficial</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B262">
         <v>2</v>
@@ -4070,35 +4070,35 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B263">
         <v>2</v>
       </c>
       <c r="C263">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D263">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>richards_brusen</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B264">
         <v>2</v>
       </c>
       <c r="C264">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D264">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>natalan_wilgner</v>
+        <v>richards_brusen</v>
       </c>
       <c r="B265">
         <v>2</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>leticiamartinspro</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B266">
         <v>2</v>
@@ -4126,69 +4126,69 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>danilo_marquesc</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B267">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D267">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>lucasspaulista</v>
+        <v>danilo_marquesc</v>
       </c>
       <c r="B268">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D268">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>lucasspaulista</v>
       </c>
       <c r="B269">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C269">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D269">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B270">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D270">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>select_from_joao</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B271">
         <v>2</v>
       </c>
       <c r="C271">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D271">
         <v>0</v>
@@ -4196,41 +4196,41 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>cristianpsicologo</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B272">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C272">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D272">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>fabaotipster</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B273">
         <v>1</v>
       </c>
       <c r="C273">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D273">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B274">
         <v>1</v>
       </c>
       <c r="C274">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D274">
         <v>1</v>
@@ -4238,13 +4238,13 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>helenaseveribjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B275">
         <v>1</v>
       </c>
       <c r="C275">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D275">
         <v>1</v>
@@ -4252,49 +4252,49 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>marciokeske</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B276">
         <v>1</v>
       </c>
       <c r="C276">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>ommariotti</v>
+        <v>marciokeske</v>
       </c>
       <c r="B277">
         <v>1</v>
       </c>
       <c r="C277">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D277">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>felipebunesufc</v>
+        <v>ommariotti</v>
       </c>
       <c r="B278">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C278">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D278">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>icarohilton</v>
+        <v>felipebunesufc</v>
       </c>
       <c r="B279">
         <v>2</v>
@@ -4308,35 +4308,35 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>jesabelmelo9</v>
+        <v>icarohilton</v>
       </c>
       <c r="B280">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>iranbez</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B281">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>sthe._.araujo</v>
+        <v>iranbez</v>
       </c>
       <c r="B282">
         <v>2</v>
@@ -4350,13 +4350,13 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>clayton77silva</v>
+        <v>sthe._.araujo</v>
       </c>
       <c r="B283">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C283">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D283">
         <v>0</v>
@@ -4364,13 +4364,13 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>raycon_mma</v>
+        <v>clayton77silva</v>
       </c>
       <c r="B284">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C284">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>sarahfmaia</v>
+        <v>raycon_mma</v>
       </c>
       <c r="B285">
         <v>2</v>
@@ -4392,13 +4392,13 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>sarahfmaia</v>
       </c>
       <c r="B286">
         <v>2</v>
       </c>
       <c r="C286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D286">
         <v>0</v>
@@ -4406,35 +4406,35 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B287">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C287">
         <v>0</v>
       </c>
       <c r="D287">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>aliferpaulo_</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B288">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C288">
         <v>0</v>
       </c>
       <c r="D288">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>sambagabrieloficial</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B289">
         <v>2</v>
@@ -4448,35 +4448,35 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>raelduraes</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B290">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C290">
         <v>0</v>
       </c>
       <c r="D290">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>martta.mariah</v>
+        <v>raelduraes</v>
       </c>
       <c r="B291">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C291">
         <v>0</v>
       </c>
       <c r="D291">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B292">
         <v>2</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>_bety_marcal</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B293">
         <v>2</v>
@@ -4504,13 +4504,13 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C294">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D294">
         <v>0</v>
@@ -4518,13 +4518,13 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>wesley_bjjvc</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B295">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C295">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B296">
         <v>2</v>
@@ -4546,21 +4546,21 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B297">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C297">
         <v>0</v>
       </c>
       <c r="D297">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B298">
         <v>1</v>
@@ -4574,21 +4574,21 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>fabi.godooy</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B299">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C299">
         <v>0</v>
       </c>
       <c r="D299">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>davicorbella</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B300">
         <v>2</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>joegam3r</v>
+        <v>davicorbella</v>
       </c>
       <c r="B301">
         <v>2</v>
@@ -4616,35 +4616,35 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>graalino</v>
+        <v>joegam3r</v>
       </c>
       <c r="B302">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C302">
         <v>0</v>
       </c>
       <c r="D302">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>ramanatoscanellibjj</v>
+        <v>graalino</v>
       </c>
       <c r="B303">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C303">
         <v>0</v>
       </c>
       <c r="D303">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>mariabeltapagani</v>
+        <v>ramanatoscanellibjj</v>
       </c>
       <c r="B304">
         <v>2</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>auriceliaribeiro_</v>
+        <v>mariabeltapagani</v>
       </c>
       <c r="B305">
         <v>2</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>craig_cohen1</v>
+        <v>auriceliaribeiro_</v>
       </c>
       <c r="B306">
         <v>2</v>
@@ -4686,35 +4686,35 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>glessios_silva</v>
+        <v>craig_cohen1</v>
       </c>
       <c r="B307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C307">
         <v>0</v>
       </c>
       <c r="D307">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>fabioincalado</v>
+        <v>glessios_silva</v>
       </c>
       <c r="B308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C308">
         <v>0</v>
       </c>
       <c r="D308">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>vanderleiamellogois</v>
+        <v>fabioincalado</v>
       </c>
       <c r="B309">
         <v>2</v>
@@ -4728,91 +4728,91 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>pedrinhosbjj</v>
+        <v>vanderleiamellogois</v>
       </c>
       <c r="B310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C310">
         <v>0</v>
       </c>
       <c r="D310">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>_jaquealms</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C311">
         <v>0</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>caio.fermianoo</v>
+        <v>_jaquealms</v>
       </c>
       <c r="B312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C312">
         <v>0</v>
       </c>
       <c r="D312">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>corrozzzive</v>
+        <v>caio.fermianoo</v>
       </c>
       <c r="B313">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C313">
         <v>0</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>araujojonaspenhade</v>
+        <v>corrozzzive</v>
       </c>
       <c r="B314">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C314">
         <v>0</v>
       </c>
       <c r="D314">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>duuleitee</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B315">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C315">
         <v>0</v>
       </c>
       <c r="D315">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>pvd_._dudis</v>
+        <v>duuleitee</v>
       </c>
       <c r="B316">
         <v>2</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B317">
         <v>2</v>
@@ -4840,21 +4840,21 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>tatianeaguiarp</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B318">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C318">
         <v>0</v>
       </c>
       <c r="D318">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>ottonhona</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B319">
         <v>1</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>alcateiaartesmarciais</v>
+        <v>ottonhona</v>
       </c>
       <c r="B320">
         <v>1</v>
@@ -4882,49 +4882,49 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>marcov__7</v>
+        <v>alcateiaartesmarciais</v>
       </c>
       <c r="B321">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C321">
         <v>0</v>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>anachierico_</v>
+        <v>marcov__7</v>
       </c>
       <c r="B322">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C322">
         <v>0</v>
       </c>
       <c r="D322">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>toraostreet</v>
+        <v>anachierico_</v>
       </c>
       <c r="B323">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C323">
         <v>0</v>
       </c>
       <c r="D323">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>bears635</v>
+        <v>toraostreet</v>
       </c>
       <c r="B324">
         <v>2</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>vivi_fitnees</v>
+        <v>bears635</v>
       </c>
       <c r="B325">
         <v>2</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>shockmonteiro</v>
+        <v>vivi_fitnees</v>
       </c>
       <c r="B326">
         <v>2</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>murilomuaythai</v>
+        <v>shockmonteiro</v>
       </c>
       <c r="B327">
         <v>2</v>
@@ -4980,35 +4980,35 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>suel.f1270</v>
+        <v>murilomuaythai</v>
       </c>
       <c r="B328">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C328">
         <v>0</v>
       </c>
       <c r="D328">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>thiagoxavier13</v>
+        <v>suel.f1270</v>
       </c>
       <c r="B329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C329">
         <v>0</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>fatima_trindade_</v>
+        <v>thiagoxavier13</v>
       </c>
       <c r="B330">
         <v>2</v>
@@ -5022,21 +5022,21 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>gillesarquitetura</v>
+        <v>fatima_trindade_</v>
       </c>
       <c r="B331">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C331">
         <v>0</v>
       </c>
       <c r="D331">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>alvestank</v>
+        <v>gillesarquitetura</v>
       </c>
       <c r="B332">
         <v>1</v>
@@ -5050,35 +5050,35 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>marciooangelo</v>
+        <v>alvestank</v>
       </c>
       <c r="B333">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C333">
         <v>0</v>
       </c>
       <c r="D333">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>adevaldojr_</v>
+        <v>marciooangelo</v>
       </c>
       <c r="B334">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C334">
         <v>0</v>
       </c>
       <c r="D334">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>rosacostasousa36</v>
+        <v>adevaldojr_</v>
       </c>
       <c r="B335">
         <v>1</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>manucanecorso.bjj</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B336">
         <v>1</v>
@@ -5106,63 +5106,63 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>claudiaottoni2025</v>
+        <v>manucanecorso.bjj</v>
       </c>
       <c r="B337">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C337">
         <v>0</v>
       </c>
       <c r="D337">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>tavin.mendes</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B338">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C338">
         <v>0</v>
       </c>
       <c r="D338">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>tavin.mendes</v>
       </c>
       <c r="B339">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C339">
         <v>0</v>
       </c>
       <c r="D339">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>fabiieju</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B340">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C340">
         <v>0</v>
       </c>
       <c r="D340">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>marqueswanderson</v>
+        <v>fabiieju</v>
       </c>
       <c r="B341">
         <v>1</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>adauto2505</v>
+        <v>marqueswanderson</v>
       </c>
       <c r="B342">
         <v>1</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>joaogagoarta</v>
+        <v>adauto2505</v>
       </c>
       <c r="B343">
         <v>1</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>npb.enterprise</v>
+        <v>joaogagoarta</v>
       </c>
       <c r="B344">
         <v>1</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>mma.idiot</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B345">
         <v>1</v>
@@ -10090,35 +10090,35 @@
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>luizcosta_mma</v>
+        <v>rodrigo.nsx</v>
       </c>
       <c r="B693">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C693">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D693">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>taylor_71kg</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B694">
         <v>0</v>
       </c>
       <c r="C694">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D694">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>_vpft</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B695">
         <v>0</v>
@@ -10132,21 +10132,21 @@
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>viniciustbf</v>
+        <v>_vpft</v>
       </c>
       <c r="B696">
         <v>0</v>
       </c>
       <c r="C696">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D696">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>dayanaa1511</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B697">
         <v>0</v>
@@ -10155,40 +10155,40 @@
         <v>2</v>
       </c>
       <c r="D697">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>danielfranzesilva</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B698">
         <v>0</v>
       </c>
       <c r="C698">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D698">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B699">
         <v>0</v>
       </c>
       <c r="C699">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D699">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>vanessamelomma</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B700">
         <v>0</v>
@@ -10202,21 +10202,21 @@
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>michelle_mirele</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B701">
         <v>0</v>
       </c>
       <c r="C701">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D701">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>geyziellsouza</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B702">
         <v>0</v>
@@ -10230,21 +10230,21 @@
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>guerreirammaofc</v>
+        <v>geyziellsouza</v>
       </c>
       <c r="B703">
         <v>0</v>
       </c>
       <c r="C703">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D703">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>kalaga_vito</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B704">
         <v>0</v>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>vitorshowman</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B705">
         <v>0</v>
@@ -10267,12 +10267,12 @@
         <v>2</v>
       </c>
       <c r="D705">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B706">
         <v>0</v>
@@ -10286,21 +10286,21 @@
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B707">
         <v>0</v>
       </c>
       <c r="C707">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D707">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B708">
         <v>0</v>
@@ -10314,21 +10314,21 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>orlando_alfa09</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B709">
         <v>0</v>
       </c>
       <c r="C709">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D709">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B710">
         <v>0</v>
@@ -10342,7 +10342,7 @@
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>manumito.oficial</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B711">
         <v>0</v>
@@ -10356,63 +10356,63 @@
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>coutz11</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B712">
         <v>0</v>
       </c>
       <c r="C712">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D712">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>eglaudiomma</v>
+        <v>coutz11</v>
       </c>
       <c r="B713">
         <v>0</v>
       </c>
       <c r="C713">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D713">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>lokomemo_protetores</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B714">
         <v>0</v>
       </c>
       <c r="C714">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D714">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>carlosnoelblack</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B715">
         <v>0</v>
       </c>
       <c r="C715">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D715">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>rafaelcmjj</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B716">
         <v>0</v>
@@ -10426,21 +10426,21 @@
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>rahikikhalid</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B717">
         <v>0</v>
       </c>
       <c r="C717">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D717">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>leonardopateira</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B718">
         <v>0</v>
@@ -10454,21 +10454,21 @@
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>thalytabjj</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B719">
         <v>0</v>
       </c>
       <c r="C719">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D719">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>rafaelantonio.rj</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B720">
         <v>0</v>
@@ -10482,35 +10482,35 @@
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>yasminreis_oficiall</v>
+        <v>rafaelantonio.rj</v>
       </c>
       <c r="B721">
         <v>0</v>
       </c>
       <c r="C721">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D721">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>dnoxsport</v>
+        <v>yasminreis_oficiall</v>
       </c>
       <c r="B722">
         <v>0</v>
       </c>
       <c r="C722">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D722">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>armysenju</v>
+        <v>dnoxsport</v>
       </c>
       <c r="B723">
         <v>0</v>
@@ -10524,7 +10524,7 @@
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>kamtalksmma</v>
+        <v>armysenju</v>
       </c>
       <c r="B724">
         <v>0</v>
@@ -10538,49 +10538,49 @@
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>arleyleboss</v>
+        <v>kamtalksmma</v>
       </c>
       <c r="B725">
         <v>0</v>
       </c>
       <c r="C725">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D725">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>jj_miguel05</v>
+        <v>arleyleboss</v>
       </c>
       <c r="B726">
         <v>0</v>
       </c>
       <c r="C726">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D726">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>dra.izabeldelfino_</v>
+        <v>jj_miguel05</v>
       </c>
       <c r="B727">
         <v>0</v>
       </c>
       <c r="C727">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D727">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>janjaovix</v>
+        <v>dra.izabeldelfino_</v>
       </c>
       <c r="B728">
         <v>0</v>
@@ -10594,7 +10594,7 @@
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B729">
         <v>0</v>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B730">
         <v>0</v>
@@ -10622,7 +10622,7 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>paulomartins.mma</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B731">
         <v>0</v>
@@ -10636,27 +10636,27 @@
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>daniel_natel</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B732">
         <v>0</v>
       </c>
       <c r="C732">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D732">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>dhuks11</v>
+        <v>daniel_natel</v>
       </c>
       <c r="B733">
         <v>0</v>
       </c>
       <c r="C733">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D733">
         <v>0</v>
@@ -10664,7 +10664,7 @@
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>macksomlee</v>
+        <v>dhuks11</v>
       </c>
       <c r="B734">
         <v>0</v>
@@ -10673,40 +10673,40 @@
         <v>1</v>
       </c>
       <c r="D734">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>y_nichimura</v>
+        <v>macksomlee</v>
       </c>
       <c r="B735">
         <v>0</v>
       </c>
       <c r="C735">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D735">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>mayconzilli</v>
+        <v>y_nichimura</v>
       </c>
       <c r="B736">
         <v>0</v>
       </c>
       <c r="C736">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D736">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>patascubo</v>
+        <v>mayconzilli</v>
       </c>
       <c r="B737">
         <v>0</v>
@@ -10720,7 +10720,7 @@
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>jeffesonmeirelles</v>
+        <v>patascubo</v>
       </c>
       <c r="B738">
         <v>0</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>denilson.unit</v>
+        <v>jeffesonmeirelles</v>
       </c>
       <c r="B739">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>vieirabjj____</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B740">
         <v>0</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>canalgolpebaixo</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B741">
         <v>0</v>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>leandro__parpinelli</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B742">
         <v>0</v>
@@ -10790,7 +10790,7 @@
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>bruno_pontes1992</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B743">
         <v>0</v>
@@ -10804,7 +10804,7 @@
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>dudaadantass</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B744">
         <v>0</v>
@@ -10818,7 +10818,7 @@
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>_pedro0h</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B745">
         <v>0</v>
@@ -10832,7 +10832,7 @@
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>alineanne_</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B746">
         <v>0</v>
@@ -10841,12 +10841,12 @@
         <v>1</v>
       </c>
       <c r="D746">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B747">
         <v>0</v>
@@ -10860,7 +10860,7 @@
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B748">
         <v>0</v>
@@ -10874,7 +10874,7 @@
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B749">
         <v>0</v>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B750">
         <v>0</v>
@@ -10902,7 +10902,7 @@
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B751">
         <v>0</v>
@@ -10916,7 +10916,7 @@
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B752">
         <v>0</v>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B753">
         <v>0</v>
@@ -10944,7 +10944,7 @@
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B754">
         <v>0</v>
@@ -10958,7 +10958,7 @@
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B755">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B756">
         <v>0</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B757">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B758">
         <v>0</v>
@@ -11014,7 +11014,7 @@
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B759">
         <v>0</v>
@@ -11028,7 +11028,7 @@
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B760">
         <v>0</v>
@@ -11042,7 +11042,7 @@
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B761">
         <v>0</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B762">
         <v>0</v>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B763">
         <v>0</v>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B764">
         <v>0</v>
@@ -11098,7 +11098,7 @@
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B765">
         <v>0</v>
@@ -11112,7 +11112,7 @@
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B766">
         <v>0</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B767">
         <v>0</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B768">
         <v>0</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B769">
         <v>0</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B770">
         <v>0</v>
@@ -11182,7 +11182,7 @@
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B771">
         <v>0</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B772">
         <v>0</v>
@@ -11210,7 +11210,7 @@
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B773">
         <v>0</v>
@@ -11224,7 +11224,7 @@
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B774">
         <v>0</v>
@@ -11238,7 +11238,7 @@
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>romulerasilva</v>
+        <v>roginbrito</v>
       </c>
       <c r="B775">
         <v>0</v>
@@ -11252,7 +11252,7 @@
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>higorsaantana</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B776">
         <v>0</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>vitorcosta_mma</v>
+        <v>higorsaantana</v>
       </c>
       <c r="B777">
         <v>0</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>paulo.titoo</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B778">
         <v>0</v>
@@ -11294,7 +11294,7 @@
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>1000ton_n</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B779">
         <v>0</v>
@@ -11308,7 +11308,7 @@
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>strong_stg_oficial</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B780">
         <v>0</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B781">
         <v>0</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B782">
         <v>0</v>
@@ -11350,7 +11350,7 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B783">
         <v>0</v>
@@ -11364,7 +11364,7 @@
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B784">
         <v>0</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>caioparangole</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B785">
         <v>0</v>
@@ -11392,7 +11392,7 @@
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B786">
         <v>0</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B787">
         <v>0</v>
@@ -11420,7 +11420,7 @@
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B788">
         <v>0</v>
@@ -11434,7 +11434,7 @@
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B789">
         <v>0</v>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B790">
         <v>0</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B791">
         <v>0</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>cristianomarcello</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B792">
         <v>0</v>
@@ -11490,7 +11490,7 @@
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>dandraco_</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B793">
         <v>0</v>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B794">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B795">
         <v>0</v>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B796">
         <v>0</v>
@@ -11546,7 +11546,7 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B797">
         <v>0</v>
@@ -11560,7 +11560,7 @@
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B798">
         <v>0</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>geanne_franca_</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B799">
         <v>0</v>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>vanemessina</v>
+        <v>geanne_franca_</v>
       </c>
       <c r="B800">
         <v>0</v>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B801">
         <v>0</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>esteticaluharruda</v>
+        <v>dadwillians</v>
       </c>
       <c r="B802">
         <v>0</v>
@@ -11630,7 +11630,7 @@
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B803">
         <v>0</v>
@@ -11644,7 +11644,7 @@
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>_kainanlima</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B804">
         <v>0</v>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B805">
         <v>0</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B806">
         <v>0</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B807">
         <v>0</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B808">
         <v>0</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>rafaelbipolarufc</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B809">
         <v>0</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>martinpakciarz</v>
+        <v>rafaelbipolarufc</v>
       </c>
       <c r="B810">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>andrearschack</v>
+        <v>martinpakciarz</v>
       </c>
       <c r="B811">
         <v>0</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>leziamorbeck50</v>
+        <v>andrearschack</v>
       </c>
       <c r="B812">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>meirelesmma</v>
+        <v>leziamorbeck50</v>
       </c>
       <c r="B813">
         <v>0</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>teamsilverio</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B814">
         <v>0</v>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>tatiaradias</v>
+        <v>teamsilverio</v>
       </c>
       <c r="B815">
         <v>0</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>daniloacordeon_oficial</v>
+        <v>tatiaradias</v>
       </c>
       <c r="B816">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>thiagopssantos</v>
+        <v>daniloacordeon_oficial</v>
       </c>
       <c r="B817">
         <v>0</v>
@@ -11840,7 +11840,7 @@
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>leafarlemos</v>
+        <v>thiagopssantos</v>
       </c>
       <c r="B818">
         <v>0</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>miltoncjr28</v>
+        <v>leafarlemos</v>
       </c>
       <c r="B819">
         <v>0</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>almeidajjwk</v>
+        <v>miltoncjr28</v>
       </c>
       <c r="B820">
         <v>0</v>
@@ -11882,7 +11882,7 @@
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>soniarmurata</v>
+        <v>almeidajjwk</v>
       </c>
       <c r="B821">
         <v>0</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>foryousaudeespecializada</v>
+        <v>soniarmurata</v>
       </c>
       <c r="B822">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>marques.__bjj</v>
+        <v>foryousaudeespecializada</v>
       </c>
       <c r="B823">
         <v>0</v>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>ryu_artes_marciais</v>
+        <v>marques.__bjj</v>
       </c>
       <c r="B824">
         <v>0</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>dorgivan13_bjj</v>
+        <v>ryu_artes_marciais</v>
       </c>
       <c r="B825">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>ayman__falil_06</v>
+        <v>dorgivan13_bjj</v>
       </c>
       <c r="B826">
         <v>0</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>otaviocarneiromma</v>
+        <v>ayman__falil_06</v>
       </c>
       <c r="B827">
         <v>0</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>dvlucc2k26_</v>
+        <v>otaviocarneiromma</v>
       </c>
       <c r="B828">
         <v>0</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>thayanne_rodrigues_bjj</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B829">
         <v>0</v>
@@ -12008,7 +12008,7 @@
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>lurochachef</v>
+        <v>thayanne_rodrigues_bjj</v>
       </c>
       <c r="B830">
         <v>0</v>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>viniciusmorais.bjj</v>
+        <v>lurochachef</v>
       </c>
       <c r="B831">
         <v>0</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>mauriciogeorge</v>
+        <v>viniciusmorais.bjj</v>
       </c>
       <c r="B832">
         <v>0</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>gisbedejose</v>
+        <v>mauriciogeorge</v>
       </c>
       <c r="B833">
         <v>0</v>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>laureanucalvo</v>
+        <v>gisbedejose</v>
       </c>
       <c r="B834">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>galindofrontado</v>
+        <v>laureanucalvo</v>
       </c>
       <c r="B835">
         <v>0</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>chalakakavinda</v>
+        <v>galindofrontado</v>
       </c>
       <c r="B836">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>gandrapaulino</v>
+        <v>chalakakavinda</v>
       </c>
       <c r="B837">
         <v>0</v>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>pgmarquesantos</v>
+        <v>gandrapaulino</v>
       </c>
       <c r="B838">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>uluukyrgyz_tima</v>
+        <v>pgmarquesantos</v>
       </c>
       <c r="B839">
         <v>0</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>kells2vallone</v>
+        <v>uluukyrgyz_tima</v>
       </c>
       <c r="B840">
         <v>0</v>
@@ -12162,7 +12162,7 @@
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>personaljakeline</v>
+        <v>kells2vallone</v>
       </c>
       <c r="B841">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>bjjfalkenberg</v>
+        <v>personaljakeline</v>
       </c>
       <c r="B842">
         <v>0</v>
@@ -12190,7 +12190,7 @@
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>sergiorenatocruz1</v>
+        <v>bjjfalkenberg</v>
       </c>
       <c r="B843">
         <v>0</v>
@@ -12204,7 +12204,7 @@
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>marcaojudobjjmaster</v>
+        <v>sergiorenatocruz1</v>
       </c>
       <c r="B844">
         <v>0</v>
@@ -12218,7 +12218,7 @@
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>indio_mma</v>
+        <v>marcaojudobjjmaster</v>
       </c>
       <c r="B845">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>covil.045</v>
+        <v>indio_mma</v>
       </c>
       <c r="B846">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>allandelano</v>
+        <v>covil.045</v>
       </c>
       <c r="B847">
         <v>0</v>
@@ -12260,7 +12260,7 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>alomaraujo</v>
+        <v>allandelano</v>
       </c>
       <c r="B848">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>theanimallifemovement</v>
+        <v>alomaraujo</v>
       </c>
       <c r="B849">
         <v>0</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>tombg_64</v>
+        <v>theanimallifemovement</v>
       </c>
       <c r="B850">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>michaeloliveiramma</v>
+        <v>tombg_64</v>
       </c>
       <c r="B851">
         <v>0</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>andreichubotaru94</v>
+        <v>michaeloliveiramma</v>
       </c>
       <c r="B852">
         <v>0</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>carinhakkz</v>
+        <v>andreichubotaru94</v>
       </c>
       <c r="B853">
         <v>0</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>helaynecrisl</v>
+        <v>carinhakkz</v>
       </c>
       <c r="B854">
         <v>0</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>oliveiraa_00.11</v>
+        <v>helaynecrisl</v>
       </c>
       <c r="B855">
         <v>0</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>udilimaheroi</v>
+        <v>oliveiraa_00.11</v>
       </c>
       <c r="B856">
         <v>0</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>mirnacaroline</v>
+        <v>udilimaheroi</v>
       </c>
       <c r="B857">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>lmk_sport</v>
+        <v>mirnacaroline</v>
       </c>
       <c r="B858">
         <v>0</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>fher.nando_</v>
+        <v>lmk_sport</v>
       </c>
       <c r="B859">
         <v>0</v>
@@ -12428,7 +12428,7 @@
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B860">
         <v>0</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>adrianaramosalvesribeiro</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B861">
         <v>0</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>djuliaarianamma</v>
+        <v>adrianaramosalvesribeiro</v>
       </c>
       <c r="B862">
         <v>0</v>
@@ -12470,7 +12470,7 @@
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>raulbasilioo</v>
+        <v>djuliaarianamma</v>
       </c>
       <c r="B863">
         <v>0</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>heloisa_elohim</v>
+        <v>raulbasilioo</v>
       </c>
       <c r="B864">
         <v>0</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>hostonhugo</v>
+        <v>heloisa_elohim</v>
       </c>
       <c r="B865">
         <v>0</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>ellida_guimaraes</v>
+        <v>hostonhugo</v>
       </c>
       <c r="B866">
         <v>0</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>massoterapeuta_bemestarr</v>
+        <v>ellida_guimaraes</v>
       </c>
       <c r="B867">
         <v>0</v>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>alexandrefideliis</v>
+        <v>massoterapeuta_bemestarr</v>
       </c>
       <c r="B868">
         <v>0</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>pammygaryo</v>
+        <v>alexandrefideliis</v>
       </c>
       <c r="B869">
         <v>0</v>
@@ -12568,7 +12568,7 @@
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>beatrizosilveira</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B870">
         <v>0</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>bastazinifilho</v>
+        <v>beatrizosilveira</v>
       </c>
       <c r="B871">
         <v>0</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>sem_saida.12</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B872">
         <v>0</v>
@@ -12610,7 +12610,7 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>sougustavorosa</v>
+        <v>sem_saida.12</v>
       </c>
       <c r="B873">
         <v>0</v>
@@ -12624,7 +12624,7 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>lincoln__puig77</v>
+        <v>sougustavorosa</v>
       </c>
       <c r="B874">
         <v>0</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>anselmo.azevedo</v>
+        <v>lincoln__puig77</v>
       </c>
       <c r="B875">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B876">
         <v>0</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B877">
         <v>0</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B878">
         <v>0</v>
@@ -12694,7 +12694,7 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B879">
         <v>0</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>marcusvgsz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B880">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B881">
         <v>0</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B882">
         <v>0</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B883">
         <v>0</v>
@@ -12764,7 +12764,7 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B884">
         <v>0</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B885">
         <v>0</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B886">
         <v>0</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>pepefightteam</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B887">
         <v>0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>danieldias7s</v>
+        <v>pepefightteam</v>
       </c>
       <c r="B888">
         <v>0</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B889">
         <v>0</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B890">
         <v>0</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B891">
         <v>0</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B892">
         <v>0</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B893">
         <v>0</v>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>mma.fisio</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B894">
         <v>0</v>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>thaynara_victoria_</v>
+        <v>mma.fisio</v>
       </c>
       <c r="B895">
         <v>0</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>tamarapq</v>
+        <v>thaynara_victoria_</v>
       </c>
       <c r="B896">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>wendel_bjj14</v>
+        <v>tamarapq</v>
       </c>
       <c r="B897">
         <v>0</v>
@@ -12960,7 +12960,7 @@
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B898">
         <v>0</v>
@@ -12974,7 +12974,7 @@
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B899">
         <v>0</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B900">
         <v>0</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B901">
         <v>0</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B902">
         <v>0</v>
@@ -13030,7 +13030,7 @@
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B903">
         <v>0</v>
@@ -13044,7 +13044,7 @@
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B904">
         <v>0</v>
@@ -13058,7 +13058,7 @@
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B905">
         <v>0</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B906">
         <v>0</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>danielplayboymt</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B907">
         <v>0</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>fix.pec</v>
+        <v>danielplayboymt</v>
       </c>
       <c r="B908">
         <v>0</v>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>chunco_424</v>
+        <v>fix.pec</v>
       </c>
       <c r="B909">
         <v>0</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>denisalagoanobjj</v>
+        <v>chunco_424</v>
       </c>
       <c r="B910">
         <v>0</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>priscilaapbatista</v>
+        <v>denisalagoanobjj</v>
       </c>
       <c r="B911">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>josita_bjj</v>
+        <v>priscilaapbatista</v>
       </c>
       <c r="B912">
         <v>0</v>
@@ -13170,7 +13170,7 @@
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>roxostrike</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B913">
         <v>0</v>
@@ -13184,7 +13184,7 @@
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>shirleypalestrina6</v>
+        <v>roxostrike</v>
       </c>
       <c r="B914">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>flipebiano</v>
+        <v>shirleypalestrina6</v>
       </c>
       <c r="B915">
         <v>0</v>
@@ -13212,7 +13212,7 @@
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>ruanmiqueias</v>
+        <v>flipebiano</v>
       </c>
       <c r="B916">
         <v>0</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>babimaciel1</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B917">
         <v>0</v>
@@ -13240,7 +13240,7 @@
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>manoel.brum</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B918">
         <v>0</v>
@@ -13254,7 +13254,7 @@
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>horadopower</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B919">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>lyvia_genuina</v>
+        <v>horadopower</v>
       </c>
       <c r="B920">
         <v>0</v>
@@ -13282,7 +13282,7 @@
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>delariva_belem</v>
+        <v>lyvia_genuina</v>
       </c>
       <c r="B921">
         <v>0</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>juugxmes</v>
+        <v>delariva_belem</v>
       </c>
       <c r="B922">
         <v>0</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>gabrielsantosufc_</v>
+        <v>juugxmes</v>
       </c>
       <c r="B923">
         <v>0</v>
@@ -13324,7 +13324,7 @@
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>_matheustiberio</v>
+        <v>gabrielsantosufc_</v>
       </c>
       <c r="B924">
         <v>0</v>
@@ -13338,7 +13338,7 @@
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>sthefany_ochoao</v>
+        <v>_matheustiberio</v>
       </c>
       <c r="B925">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>reynitaoblitasbustamante</v>
+        <v>sthefany_ochoao</v>
       </c>
       <c r="B926">
         <v>0</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>joseochoa.mma</v>
+        <v>reynitaoblitasbustamante</v>
       </c>
       <c r="B927">
         <v>0</v>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>gabriellb.andrade</v>
+        <v>joseochoa.mma</v>
       </c>
       <c r="B928">
         <v>0</v>
@@ -13394,7 +13394,7 @@
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>romelluistro</v>
+        <v>gabriellb.andrade</v>
       </c>
       <c r="B929">
         <v>0</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>yuricapelasso</v>
+        <v>romelluistro</v>
       </c>
       <c r="B930">
         <v>0</v>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>lucasfenomeno_ufc</v>
+        <v>yuricapelasso</v>
       </c>
       <c r="B931">
         <v>0</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>gabriell_marcus</v>
+        <v>lucasfenomeno_ufc</v>
       </c>
       <c r="B932">
         <v>0</v>
@@ -13450,7 +13450,7 @@
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>lazyboy.ufc</v>
+        <v>gabriell_marcus</v>
       </c>
       <c r="B933">
         <v>0</v>
@@ -13464,7 +13464,7 @@
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>matheusdouradomma</v>
+        <v>lazyboy.ufc</v>
       </c>
       <c r="B934">
         <v>0</v>
@@ -13478,7 +13478,7 @@
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>rafaelsouza7586</v>
+        <v>matheusdouradomma</v>
       </c>
       <c r="B935">
         <v>0</v>
@@ -13492,7 +13492,7 @@
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>land_on_martelo_308</v>
+        <v>rafaelsouza7586</v>
       </c>
       <c r="B936">
         <v>0</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>dodge_big_johnson29</v>
+        <v>land_on_martelo_308</v>
       </c>
       <c r="B937">
         <v>0</v>
@@ -13520,7 +13520,7 @@
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>dj__freckles</v>
+        <v>dodge_big_johnson29</v>
       </c>
       <c r="B938">
         <v>0</v>
@@ -13534,7 +13534,7 @@
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>regis18vieira</v>
+        <v>dj__freckles</v>
       </c>
       <c r="B939">
         <v>0</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>andy.techera.12</v>
+        <v>regis18vieira</v>
       </c>
       <c r="B940">
         <v>0</v>
@@ -13562,7 +13562,7 @@
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>celiogarcia6</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B941">
         <v>0</v>
@@ -13576,7 +13576,7 @@
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>luluakio</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B942">
         <v>0</v>
@@ -13590,7 +13590,7 @@
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>barreto.boxe</v>
+        <v>luluakio</v>
       </c>
       <c r="B943">
         <v>0</v>
@@ -13604,7 +13604,7 @@
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>lusoaresjj</v>
+        <v>barreto.boxe</v>
       </c>
       <c r="B944">
         <v>0</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>sharingan_mma</v>
+        <v>lusoaresjj</v>
       </c>
       <c r="B945">
         <v>0</v>
@@ -13632,28 +13632,42 @@
     </row>
     <row r="946">
       <c r="A946" t="str">
+        <v>sharingan_mma</v>
+      </c>
+      <c r="B946">
+        <v>0</v>
+      </c>
+      <c r="C946">
+        <v>1</v>
+      </c>
+      <c r="D946">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="str">
         <v>thaisadantas</v>
       </c>
-      <c r="B946">
-        <v>0</v>
-      </c>
-      <c r="C946">
-        <v>1</v>
-      </c>
-      <c r="D946">
+      <c r="B947">
+        <v>0</v>
+      </c>
+      <c r="C947">
+        <v>1</v>
+      </c>
+      <c r="D947">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D946"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D947"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D183"/>
+  <dimension ref="A1:D184"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13674,13 +13688,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>2378</v>
+        <v>2401</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2256</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="3">
@@ -13730,13 +13744,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -13758,13 +13772,13 @@
         <v>malu832757</v>
       </c>
       <c r="B8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -13772,13 +13786,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -13786,41 +13800,41 @@
         <v>im.duda02</v>
       </c>
       <c r="B10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>anayachiottoni</v>
+        <v>n.daily22</v>
       </c>
       <c r="B11">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>n.daily22</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B12">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -13828,55 +13842,55 @@
         <v>rhuansales.mma</v>
       </c>
       <c r="B13">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>anaaj_camargo</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>masonharper_mma</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B15">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B16">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -13884,13 +13898,13 @@
         <v>rayn.avaro</v>
       </c>
       <c r="B17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -13898,13 +13912,13 @@
         <v>propeace_fight</v>
       </c>
       <c r="B18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -13912,13 +13926,13 @@
         <v>arafight_pesc</v>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -13926,13 +13940,13 @@
         <v>jujua_maral1</v>
       </c>
       <c r="B20">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -13979,21 +13993,21 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>thundergrapple</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>galler_peace</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B25">
         <v>19</v>
@@ -14007,7 +14021,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>figh_grappler</v>
+        <v>galler_peace</v>
       </c>
       <c r="B26">
         <v>19</v>
@@ -14021,58 +14035,58 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>mmmarc20</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B27">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ottonianalivia</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B28">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>combintel</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B29">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>mar_iarmaria</v>
+        <v>combintel</v>
       </c>
       <c r="B30">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -14080,13 +14094,13 @@
         <v>laisrebeiro10</v>
       </c>
       <c r="B31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -14108,13 +14122,13 @@
         <v>kelly_ottoni</v>
       </c>
       <c r="B33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -14413,66 +14427,66 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>daniezzyy</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>elienelucindo_oficial</v>
+        <v>daniezzyy</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>luigimoraess</v>
+        <v>elienelucindo_oficial</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C57">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>marcelogabrielmma</v>
+        <v>luigimoraess</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>vincenzo_pit_monster</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -14483,7 +14497,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>rian.vitorjj</v>
+        <v>vincenzo_pit_monster</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -14497,7 +14511,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>danielrodrigues1000</v>
+        <v>rian.vitorjj</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -14511,7 +14525,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>lonbradao__777</v>
+        <v>danielrodrigues1000</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -14525,49 +14539,49 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>natanborges001</v>
+        <v>lonbradao__777</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>bruno_murata</v>
+        <v>natanborges001</v>
       </c>
       <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64">
         <v>4</v>
-      </c>
-      <c r="C64">
-        <v>1</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>adrianoams7</v>
+        <v>bruno_murata</v>
       </c>
       <c r="B65">
         <v>4</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>ninjatheorist</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B66">
         <v>4</v>
@@ -14581,7 +14595,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>deboralvesoficial</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B67">
         <v>4</v>
@@ -14595,7 +14609,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>jorgeantoniopba</v>
+        <v>deboralvesoficial</v>
       </c>
       <c r="B68">
         <v>4</v>
@@ -14609,7 +14623,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>rrafaelins</v>
+        <v>jorgeantoniopba</v>
       </c>
       <c r="B69">
         <v>4</v>
@@ -14623,21 +14637,21 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>vndcardoso</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>cesar.boanerges</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B71">
         <v>3</v>
@@ -14651,10 +14665,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>jheffzao</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -14665,41 +14679,41 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>jvxz______</v>
+        <v>jheffzao</v>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>julianoalicate</v>
+        <v>jvxz______</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>cairorochamma</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -14707,24 +14721,24 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>efsantos.oficial</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -14735,83 +14749,83 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ufc_paramountsports</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>hollenberg.personal</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>hollenberg.personal</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>e_car.doso</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>gdazuera</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>jose_luiz_thome</v>
+        <v>gdazuera</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -14819,13 +14833,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>dgswillian</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -14833,13 +14847,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ryangandraufc</v>
+        <v>dgswillian</v>
       </c>
       <c r="B85">
         <v>2</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -14847,21 +14861,21 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>fredoctmma</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -14875,27 +14889,27 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>emersonriosmma</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -14903,13 +14917,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>fatima_trindade_</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B90">
         <v>2</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -14917,7 +14931,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>fatima_trindade_</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -14931,7 +14945,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>pedromadeira.s</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -14945,7 +14959,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>flaviakaena</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -14959,21 +14973,21 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>gillesarquitetura</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>alvestank</v>
+        <v>gillesarquitetura</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -14987,7 +15001,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>alvestank</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -15001,35 +15015,35 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>marciooangelo</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>peacegrappler_archive</v>
+        <v>marciooangelo</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>adevaldojr_</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -15043,7 +15057,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>rosacostasousa36</v>
+        <v>adevaldojr_</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -15057,7 +15071,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>helenaseveribjj</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -15071,7 +15085,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>manucanecorso.bjj</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -15085,35 +15099,35 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>claudiaottoni2025</v>
+        <v>manucanecorso.bjj</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>claudiaottoni19</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>tavin.mendes</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -15127,21 +15141,21 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>eric.shpritz</v>
+        <v>tavin.mendes</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106">
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B107">
         <v>2</v>
@@ -15155,21 +15169,21 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>fabiieju</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
         <v>0</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>marqueswanderson</v>
+        <v>fabiieju</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -15183,7 +15197,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>adauto2505</v>
+        <v>marqueswanderson</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -15197,7 +15211,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>joaogagoarta</v>
+        <v>adauto2505</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -15211,7 +15225,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>npb.enterprise</v>
+        <v>joaogagoarta</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -15225,7 +15239,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>mma.idiot</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -15897,55 +15911,55 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>viniciustbf</v>
+        <v>rodrigo.nsx</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C161">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D161">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>disk_egg</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B162">
         <v>0</v>
       </c>
       <c r="C162">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>kalaga_vito</v>
+        <v>disk_egg</v>
       </c>
       <c r="B163">
         <v>0</v>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>danilo_marquesc</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B164">
         <v>0</v>
       </c>
       <c r="C164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -15953,7 +15967,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>denilson.unit</v>
+        <v>danilo_marquesc</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -15967,7 +15981,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>vieirabjj____</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -15981,7 +15995,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>canalgolpebaixo</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -15995,7 +16009,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>leandro__parpinelli</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -16009,7 +16023,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>bruno_pontes1992</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -16023,7 +16037,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -16037,7 +16051,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>dudaadantass</v>
+        <v>aida_dos_sonhos</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -16051,7 +16065,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>mauriciomouraprev</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -16065,7 +16079,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>_pedro0h</v>
+        <v>mauriciomouraprev</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -16079,7 +16093,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>eliassilverio</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -16088,12 +16102,12 @@
         <v>1</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>andy.techera.12</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -16107,7 +16121,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>celiogarcia6</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -16121,7 +16135,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>luluakio</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -16135,7 +16149,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>adriano.trator</v>
+        <v>luluakio</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -16149,7 +16163,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>barreto.boxe</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -16163,7 +16177,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>pauloserrati</v>
+        <v>barreto.boxe</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -16177,7 +16191,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>lusoaresjj</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -16191,7 +16205,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>sharingan_mma</v>
+        <v>lusoaresjj</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -16205,21 +16219,35 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
+        <v>sharingan_mma</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
         <v>thaisadantas</v>
       </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-      <c r="C183">
-        <v>1</v>
-      </c>
-      <c r="D183">
+      <c r="B184">
+        <v>0</v>
+      </c>
+      <c r="C184">
+        <v>1</v>
+      </c>
+      <c r="D184">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D183"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D184"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13317</v>
+        <v>13375</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12055</v>
+        <v>12113</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3463</v>
+        <v>3503</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>1354</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="4">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2168</v>
+        <v>2172</v>
       </c>
       <c r="C5">
         <v>30</v>
       </c>
       <c r="D5">
-        <v>974</v>
+        <v>978</v>
       </c>
     </row>
     <row r="6">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="7">
@@ -545,13 +545,13 @@
         <v>combintel</v>
       </c>
       <c r="B11">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -559,13 +559,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B12">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C12">
         <v>7</v>
       </c>
       <c r="D12">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13">
@@ -629,13 +629,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -671,13 +671,13 @@
         <v>malu832757</v>
       </c>
       <c r="B20">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
@@ -965,41 +965,41 @@
         <v>ottonianalivia</v>
       </c>
       <c r="B41">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>leonardomesquitamma</v>
+        <v>n.daily22</v>
       </c>
       <c r="B42">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>n.daily22</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B43">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -1018,44 +1018,44 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>victus_torquatus00</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B45">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>anayachiottoni</v>
+        <v>victus_torquatus00</v>
       </c>
       <c r="B46">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B47">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -1074,30 +1074,30 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>enzoferrari680</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B49">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>rayn.avaro</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B50">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -1172,114 +1172,114 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ninjatheorist</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B56">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>propeace_fight</v>
+        <v>arafight_pesc</v>
       </c>
       <c r="B57">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>thiagoauper</v>
+        <v>jujua_maral1</v>
       </c>
       <c r="B58">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>arafight_pesc</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B59">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>jujua_maral1</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B60">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>gra_jpereira</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B61">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>eliassilverio</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B62">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C62">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>mar_iarmaria</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B63">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D63">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
@@ -1424,30 +1424,30 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>_alvezbjj__</v>
+        <v>laisrebeiro10</v>
       </c>
       <c r="B74">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>laisrebeiro10</v>
+        <v>_alvezbjj__</v>
       </c>
       <c r="B75">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D75">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
@@ -13688,13 +13688,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>2401</v>
+        <v>2459</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2279</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="3">
@@ -13702,13 +13702,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>1436</v>
+        <v>1476</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>898</v>
+        <v>938</v>
       </c>
     </row>
     <row r="4">
@@ -13730,13 +13730,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6">
@@ -13744,13 +13744,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -13772,13 +13772,13 @@
         <v>malu832757</v>
       </c>
       <c r="B8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -13786,13 +13786,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -13814,13 +13814,13 @@
         <v>n.daily22</v>
       </c>
       <c r="B11">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -13856,55 +13856,55 @@
         <v>kamile_oliveria_10</v>
       </c>
       <c r="B14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>anaaj_camargo</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>masonharper_mma</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B16">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>rayn.avaro</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B17">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -13912,13 +13912,13 @@
         <v>propeace_fight</v>
       </c>
       <c r="B18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -13926,13 +13926,13 @@
         <v>arafight_pesc</v>
       </c>
       <c r="B19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -13940,102 +13940,102 @@
         <v>jujua_maral1</v>
       </c>
       <c r="B20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>grapplerfight</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>washington_cassisno</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B22">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>johnmma9</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B23">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ottonianalivia</v>
+        <v>johnmma9</v>
       </c>
       <c r="B24">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>thundergrapple</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B25">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>galler_peace</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B26">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>figh_grappler</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B27">
         <v>19</v>
@@ -14049,21 +14049,21 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>mmmarc20</v>
+        <v>galler_peace</v>
       </c>
       <c r="B28">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>mar_iarmaria</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B29">
         <v>19</v>
@@ -14072,7 +14072,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -14080,13 +14080,13 @@
         <v>combintel</v>
       </c>
       <c r="B30">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -14094,13 +14094,13 @@
         <v>laisrebeiro10</v>
       </c>
       <c r="B31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">

--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -433,13 +433,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3503</v>
+        <v>3583</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>1394</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="4">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="7">
@@ -783,7 +783,7 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B28">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -853,13 +853,13 @@
         <v>washington_cassisno</v>
       </c>
       <c r="B33">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C33">
         <v>17</v>
       </c>
       <c r="D33">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
@@ -13702,13 +13702,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>1476</v>
+        <v>1556</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>938</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="4">
@@ -13744,13 +13744,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -13951,44 +13951,44 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ottonianalivia</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B21">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>grapplerfight</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>washington_cassisno</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B23">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -14108,7 +14108,7 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B32">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C32">
         <v>0</v>

--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -419,7 +419,7 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13375</v>
+        <v>13378</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -433,13 +433,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3583</v>
+        <v>3663</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>1474</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="4">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7">
@@ -671,13 +671,13 @@
         <v>malu832757</v>
       </c>
       <c r="B20">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -856,7 +856,7 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D33">
         <v>34</v>
@@ -1004,86 +1004,86 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>italothearcher</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B44">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C44">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>anayachiottoni</v>
       </c>
       <c r="B45">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>victus_torquatus00</v>
+        <v>italothearcher</v>
       </c>
       <c r="B46">
         <v>35</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>anayachiottoni</v>
+        <v>victus_torquatus00</v>
       </c>
       <c r="B47">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>rhuansales.mma</v>
+        <v>rayn.avaro</v>
       </c>
       <c r="B48">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>rayn.avaro</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B49">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
@@ -1144,21 +1144,21 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>pedromadeira.s</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B54">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>_cardoso_caio_</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B55">
         <v>31</v>
@@ -1167,21 +1167,21 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>propeace_fight</v>
+        <v>_cardoso_caio_</v>
       </c>
       <c r="B56">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
@@ -1189,13 +1189,13 @@
         <v>arafight_pesc</v>
       </c>
       <c r="B57">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58">
@@ -1256,114 +1256,114 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>gra_jpereira</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B62">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D62">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>eliassilverio</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B63">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C63">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>grapplerfight</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B64">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>alvesmidih</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B65">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>marcelogabrielmma</v>
+        <v>galler_peace</v>
       </c>
       <c r="B66">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>thundergrapple</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B67">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>galler_peace</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B68">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>figh_grappler</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B69">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
@@ -1522,100 +1522,100 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>manoel_maranhaobjjmma</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B81">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>gdazuera</v>
+        <v>manoel_maranhaobjjmma</v>
       </c>
       <c r="B82">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C82">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ravenrodriguez___</v>
+        <v>gdazuera</v>
       </c>
       <c r="B83">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C83">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>marc0s.azv</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B84">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>danielbrbjj</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B85">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>adriano.trator</v>
+        <v>danielbrbjj</v>
       </c>
       <c r="B86">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C86">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="D86">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>marcos_tailandess</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B87">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C87">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88">
@@ -2572,111 +2572,111 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>glm.barbosa</v>
+        <v>natanborges001</v>
       </c>
       <c r="B156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>fernando.mma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B157">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C157">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D157">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>davizoka_mascote</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>enzo_henrik</v>
+        <v>davizoka_mascote</v>
       </c>
       <c r="B159">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C159">
         <v>0</v>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>emersonriosmma</v>
+        <v>enzo_henrik</v>
       </c>
       <c r="B160">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C160">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>douglasoct_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B161">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C161">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D161">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>eric.shpritz</v>
+        <v>douglasoct_mma</v>
       </c>
       <c r="B162">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C162">
         <v>2</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>marcocanatelli</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B163">
         <v>4</v>
       </c>
       <c r="C163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -2684,108 +2684,108 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>benjafloripabjj</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B164">
         <v>4</v>
       </c>
       <c r="C164">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>heltoncm2002</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B165">
         <v>4</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>pitbullandrade</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C166">
         <v>1</v>
       </c>
       <c r="D166">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>zedelano</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B167">
         <v>3</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D167">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>salost.ofc</v>
+        <v>zedelano</v>
       </c>
       <c r="B168">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C168">
         <v>0</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>gabrielsouzamma</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B169">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D169">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B170">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>y.arthur_01</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B171">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -2796,63 +2796,63 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>leobahiamma</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B172">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C172">
         <v>0</v>
       </c>
       <c r="D172">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>s__simone__</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B173">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C173">
         <v>0</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>maxbjj_0</v>
+        <v>s__simone__</v>
       </c>
       <c r="B174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C174">
         <v>0</v>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>vincenzo_pit_monster</v>
+        <v>maxbjj_0</v>
       </c>
       <c r="B175">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C175">
         <v>0</v>
       </c>
       <c r="D175">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>rian.vitorjj</v>
+        <v>vincenzo_pit_monster</v>
       </c>
       <c r="B176">
         <v>2</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>danielrodrigues1000</v>
+        <v>rian.vitorjj</v>
       </c>
       <c r="B177">
         <v>2</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>lonbradao__777</v>
+        <v>danielrodrigues1000</v>
       </c>
       <c r="B178">
         <v>2</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>natanborges001</v>
+        <v>lonbradao__777</v>
       </c>
       <c r="B179">
         <v>2</v>
       </c>
       <c r="C179">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D179">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -5330,13 +5330,13 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>yurimartins1_</v>
+        <v>djsagatoficial</v>
       </c>
       <c r="B353">
         <v>1</v>
       </c>
       <c r="C353">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B354">
         <v>1</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B355">
         <v>1</v>
@@ -5372,13 +5372,13 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B356">
         <v>1</v>
       </c>
       <c r="C356">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D356">
         <v>0</v>
@@ -5386,13 +5386,13 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>kawannsenaboxe</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B357">
         <v>1</v>
       </c>
       <c r="C357">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>guiiviieira_</v>
+        <v>kawannsenaboxe</v>
       </c>
       <c r="B358">
         <v>1</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B359">
         <v>1</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B360">
         <v>1</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>danni_goncalves12</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B361">
         <v>1</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B362">
         <v>1</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B363">
         <v>1</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B364">
         <v>1</v>
@@ -5498,13 +5498,13 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>fagnerosensei</v>
+        <v>gildojiu</v>
       </c>
       <c r="B365">
         <v>1</v>
       </c>
       <c r="C365">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B366">
         <v>1</v>
@@ -5526,13 +5526,13 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>030sami</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B367">
         <v>1</v>
       </c>
       <c r="C367">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D367">
         <v>0</v>
@@ -5540,35 +5540,35 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>giulia.fasolato</v>
+        <v>030sami</v>
       </c>
       <c r="B368">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C368">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D368">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>selipereirapereira</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B369">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C369">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D369">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>d.silvamma</v>
+        <v>selipereirapereira</v>
       </c>
       <c r="B370">
         <v>1</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>kalindrafaria</v>
+        <v>d.silvamma</v>
       </c>
       <c r="B371">
         <v>1</v>
@@ -5596,35 +5596,35 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B372">
         <v>1</v>
       </c>
       <c r="C372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D372">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B373">
         <v>1</v>
       </c>
       <c r="C373">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D373">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B374">
         <v>1</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B375">
         <v>1</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>killemquick</v>
+        <v>andreibjj</v>
       </c>
       <c r="B376">
         <v>1</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>chuck_tlp</v>
+        <v>killemquick</v>
       </c>
       <c r="B377">
         <v>1</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>henriquemmunhoz</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B378">
         <v>1</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>flavio_tuba8</v>
+        <v>henriquemmunhoz</v>
       </c>
       <c r="B379">
         <v>1</v>
@@ -5708,13 +5708,13 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>koliseu.br</v>
+        <v>flavio_tuba8</v>
       </c>
       <c r="B380">
         <v>1</v>
       </c>
       <c r="C380">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D380">
         <v>0</v>
@@ -5722,30 +5722,30 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>koliseu.br</v>
       </c>
       <c r="B381">
         <v>1</v>
       </c>
       <c r="C381">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D381">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>djsagatoficial</v>
+        <v>aida_dos_sonhos</v>
       </c>
       <c r="B382">
         <v>1</v>
       </c>
       <c r="C382">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D382">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -10272,7 +10272,7 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>vitorshowman</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B706">
         <v>0</v>
@@ -10281,12 +10281,12 @@
         <v>2</v>
       </c>
       <c r="D706">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B707">
         <v>0</v>
@@ -10300,21 +10300,21 @@
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B708">
         <v>0</v>
       </c>
       <c r="C708">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D708">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B709">
         <v>0</v>
@@ -10328,21 +10328,21 @@
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>orlando_alfa09</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B710">
         <v>0</v>
       </c>
       <c r="C710">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D710">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B711">
         <v>0</v>
@@ -10356,7 +10356,7 @@
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>manumito.oficial</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B712">
         <v>0</v>
@@ -10370,63 +10370,63 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>coutz11</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B713">
         <v>0</v>
       </c>
       <c r="C713">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D713">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>eglaudiomma</v>
+        <v>coutz11</v>
       </c>
       <c r="B714">
         <v>0</v>
       </c>
       <c r="C714">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D714">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>lokomemo_protetores</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B715">
         <v>0</v>
       </c>
       <c r="C715">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D715">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>carlosnoelblack</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B716">
         <v>0</v>
       </c>
       <c r="C716">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D716">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>rafaelcmjj</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B717">
         <v>0</v>
@@ -10440,21 +10440,21 @@
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>rahikikhalid</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B718">
         <v>0</v>
       </c>
       <c r="C718">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D718">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>leonardopateira</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B719">
         <v>0</v>
@@ -10468,21 +10468,21 @@
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>thalytabjj</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B720">
         <v>0</v>
       </c>
       <c r="C720">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D720">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>rafaelantonio.rj</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B721">
         <v>0</v>
@@ -10496,35 +10496,35 @@
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>yasminreis_oficiall</v>
+        <v>rafaelantonio.rj</v>
       </c>
       <c r="B722">
         <v>0</v>
       </c>
       <c r="C722">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D722">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>dnoxsport</v>
+        <v>yasminreis_oficiall</v>
       </c>
       <c r="B723">
         <v>0</v>
       </c>
       <c r="C723">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D723">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>armysenju</v>
+        <v>dnoxsport</v>
       </c>
       <c r="B724">
         <v>0</v>
@@ -10538,7 +10538,7 @@
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>kamtalksmma</v>
+        <v>armysenju</v>
       </c>
       <c r="B725">
         <v>0</v>
@@ -10552,49 +10552,49 @@
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>arleyleboss</v>
+        <v>kamtalksmma</v>
       </c>
       <c r="B726">
         <v>0</v>
       </c>
       <c r="C726">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D726">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>jj_miguel05</v>
+        <v>arleyleboss</v>
       </c>
       <c r="B727">
         <v>0</v>
       </c>
       <c r="C727">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D727">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>dra.izabeldelfino_</v>
+        <v>jj_miguel05</v>
       </c>
       <c r="B728">
         <v>0</v>
       </c>
       <c r="C728">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D728">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>janjaovix</v>
+        <v>dra.izabeldelfino_</v>
       </c>
       <c r="B729">
         <v>0</v>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B730">
         <v>0</v>
@@ -10622,7 +10622,7 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B731">
         <v>0</v>
@@ -10636,7 +10636,7 @@
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>paulomartins.mma</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B732">
         <v>0</v>
@@ -10650,27 +10650,27 @@
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>daniel_natel</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B733">
         <v>0</v>
       </c>
       <c r="C733">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D733">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>dhuks11</v>
+        <v>daniel_natel</v>
       </c>
       <c r="B734">
         <v>0</v>
       </c>
       <c r="C734">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D734">
         <v>0</v>
@@ -10678,7 +10678,7 @@
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>macksomlee</v>
+        <v>dhuks11</v>
       </c>
       <c r="B735">
         <v>0</v>
@@ -10687,40 +10687,40 @@
         <v>1</v>
       </c>
       <c r="D735">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>y_nichimura</v>
+        <v>macksomlee</v>
       </c>
       <c r="B736">
         <v>0</v>
       </c>
       <c r="C736">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D736">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>mayconzilli</v>
+        <v>y_nichimura</v>
       </c>
       <c r="B737">
         <v>0</v>
       </c>
       <c r="C737">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D737">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>patascubo</v>
+        <v>mayconzilli</v>
       </c>
       <c r="B738">
         <v>0</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>jeffesonmeirelles</v>
+        <v>patascubo</v>
       </c>
       <c r="B739">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>denilson.unit</v>
+        <v>jeffesonmeirelles</v>
       </c>
       <c r="B740">
         <v>0</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>vieirabjj____</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B741">
         <v>0</v>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>canalgolpebaixo</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B742">
         <v>0</v>
@@ -10790,7 +10790,7 @@
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>leandro__parpinelli</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B743">
         <v>0</v>
@@ -10804,7 +10804,7 @@
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>bruno_pontes1992</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B744">
         <v>0</v>
@@ -10818,7 +10818,7 @@
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>dudaadantass</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B745">
         <v>0</v>
@@ -13688,7 +13688,7 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>2459</v>
+        <v>2462</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -13702,13 +13702,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>1556</v>
+        <v>1636</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1018</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="4">
@@ -13744,13 +13744,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -13772,13 +13772,13 @@
         <v>malu832757</v>
       </c>
       <c r="B8">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -13828,41 +13828,41 @@
         <v>anayachiottoni</v>
       </c>
       <c r="B12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>rhuansales.mma</v>
+        <v>kamile_oliveria_10</v>
       </c>
       <c r="B13">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>kamile_oliveria_10</v>
+        <v>rhuansales.mma</v>
       </c>
       <c r="B14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -13870,13 +13870,13 @@
         <v>rayn.avaro</v>
       </c>
       <c r="B15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -13912,13 +13912,13 @@
         <v>propeace_fight</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -13926,13 +13926,13 @@
         <v>arafight_pesc</v>
       </c>
       <c r="B19">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -13951,77 +13951,77 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>washington_cassisno</v>
+        <v>grapplerfight</v>
       </c>
       <c r="B21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ottonianalivia</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B22">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>grapplerfight</v>
+        <v>ottonianalivia</v>
       </c>
       <c r="B23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>johnmma9</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B24">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>mmmarc20</v>
+        <v>galler_peace</v>
       </c>
       <c r="B25">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>mar_iarmaria</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B26">
         <v>20</v>
@@ -14030,49 +14030,49 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>thundergrapple</v>
+        <v>johnmma9</v>
       </c>
       <c r="B27">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>galler_peace</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B28">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>figh_grappler</v>
+        <v>mar_iarmaria</v>
       </c>
       <c r="B29">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -14455,52 +14455,52 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>elienelucindo_oficial</v>
+        <v>natanborges001</v>
       </c>
       <c r="B57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>luigimoraess</v>
+        <v>elienelucindo_oficial</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C58">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>marcelogabrielmma</v>
+        <v>luigimoraess</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>vincenzo_pit_monster</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -14511,7 +14511,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>rian.vitorjj</v>
+        <v>vincenzo_pit_monster</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -14525,7 +14525,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>danielrodrigues1000</v>
+        <v>rian.vitorjj</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -14539,7 +14539,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>lonbradao__777</v>
+        <v>danielrodrigues1000</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -14553,16 +14553,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>natanborges001</v>
+        <v>lonbradao__777</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -14805,41 +14805,41 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>e_car.doso</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
         <v>3</v>
       </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
       <c r="D82">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>gdazuera</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>jose_luiz_thome</v>
+        <v>gdazuera</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -14847,13 +14847,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>dgswillian</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -14861,13 +14861,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>ryangandraufc</v>
+        <v>dgswillian</v>
       </c>
       <c r="B86">
         <v>2</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -14875,21 +14875,21 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>fredoctmma</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -14903,27 +14903,27 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>emersonriosmma</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B90">
         <v>2</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -14931,13 +14931,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>fatima_trindade_</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -14945,7 +14945,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>fatima_trindade_</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -14959,7 +14959,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>pedromadeira.s</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -14973,7 +14973,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>flaviakaena</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -14987,21 +14987,21 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>gillesarquitetura</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>alvestank</v>
+        <v>gillesarquitetura</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -15015,7 +15015,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>alvestank</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -15029,35 +15029,35 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>marciooangelo</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>peacegrappler_archive</v>
+        <v>marciooangelo</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>adevaldojr_</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -15071,7 +15071,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>rosacostasousa36</v>
+        <v>adevaldojr_</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -15085,7 +15085,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>helenaseveribjj</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -15099,7 +15099,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>manucanecorso.bjj</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -15113,35 +15113,35 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>claudiaottoni2025</v>
+        <v>manucanecorso.bjj</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>claudiaottoni19</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>tavin.mendes</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -15155,21 +15155,21 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>eric.shpritz</v>
+        <v>tavin.mendes</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -15183,21 +15183,21 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>fabiieju</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>marqueswanderson</v>
+        <v>fabiieju</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -15211,7 +15211,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>adauto2505</v>
+        <v>marqueswanderson</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -15225,7 +15225,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>joaogagoarta</v>
+        <v>adauto2505</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -15239,7 +15239,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>npb.enterprise</v>
+        <v>joaogagoarta</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -15253,41 +15253,41 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>sergio_alves_bjj</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>sergio_alves_bjj</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>morena_ramos</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -15301,7 +15301,7 @@
         <v>1</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -15309,13 +15309,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>jean_ferreira_br</v>
+        <v>morena_ramos</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -15323,13 +15323,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>mmapalpitex</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -15337,13 +15337,13 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -15351,7 +15351,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>kauan_mantas</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -15365,7 +15365,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>erickdiaseds</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -15379,7 +15379,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>emersonapache</v>
+        <v>kauan_mantas</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>nataliavidal965</v>
+        <v>erickdiaseds</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -15407,7 +15407,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>manoel_maranhaobjjmma</v>
+        <v>emersonapache</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -15421,7 +15421,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ruanpantojanutricionista</v>
+        <v>nataliavidal965</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -15435,7 +15435,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>alexandreconsentino</v>
+        <v>manoel_maranhaobjjmma</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -15449,7 +15449,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>luizpaulomma</v>
+        <v>ruanpantojanutricionista</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -15463,21 +15463,21 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>marcos_tailandess</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>luizpaulomma</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -15491,7 +15491,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>epicjoel2022</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -15505,7 +15505,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>tvlinsoficial</v>
+        <v>epicjoel2022</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -15519,7 +15519,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>_itamar_maximo</v>
+        <v>tvlinsoficial</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -15533,7 +15533,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>mg._silvaa_</v>
+        <v>_itamar_maximo</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -15547,7 +15547,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>sarahfmaia</v>
+        <v>mg._silvaa_</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -15561,7 +15561,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>desativado_no_off33</v>
+        <v>sarahfmaia</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -15575,35 +15575,35 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>lucasbaddoure</v>
+        <v>desativado_no_off33</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>paulo_rafa_personal</v>
+        <v>lucasbaddoure</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>endurance_guia</v>
+        <v>paulo_rafa_personal</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -15617,7 +15617,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>cadupereirss</v>
+        <v>endurance_guia</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -15631,7 +15631,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>instrutorindiovs</v>
+        <v>cadupereirss</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -15645,7 +15645,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>lopes.felipe13</v>
+        <v>instrutorindiovs</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -15659,7 +15659,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>marciokeske</v>
+        <v>lopes.felipe13</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -15673,7 +15673,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>percepcar</v>
+        <v>marciokeske</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -15687,7 +15687,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>_jullianadacruz</v>
+        <v>percepcar</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -15701,7 +15701,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>thiagoxavier13</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -15715,7 +15715,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>marchi_vinicius</v>
+        <v>thiagoxavier13</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -15729,7 +15729,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>rafa_speda</v>
+        <v>marchi_vinicius</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -15743,7 +15743,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>m1guelmolina</v>
+        <v>rafa_speda</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -15757,7 +15757,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>rosantos83</v>
+        <v>m1guelmolina</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -15771,7 +15771,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>caiogoularts</v>
+        <v>rosantos83</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -15785,7 +15785,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>cassiolee013</v>
+        <v>caiogoularts</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -15799,7 +15799,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>alinefurlann</v>
+        <v>cassiolee013</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -15813,7 +15813,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>felipedasilvalucas.bjj</v>
+        <v>alinefurlann</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -15827,7 +15827,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>murilomuaythai</v>
+        <v>felipedasilvalucas.bjj</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -15841,7 +15841,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>programaparadois</v>
+        <v>murilomuaythai</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -15855,7 +15855,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>cotty_bigmonster</v>
+        <v>programaparadois</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -15869,7 +15869,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>alissonlayza</v>
+        <v>cotty_bigmonster</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -15883,7 +15883,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>perninhakickboxing</v>
+        <v>alissonlayza</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -15897,7 +15897,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>perninhakickboxing</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -15911,7 +15911,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>rodrigo.nsx</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -15925,55 +15925,55 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>viniciustbf</v>
+        <v>rodrigo.nsx</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C162">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D162">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>disk_egg</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B163">
         <v>0</v>
       </c>
       <c r="C163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>kalaga_vito</v>
+        <v>disk_egg</v>
       </c>
       <c r="B164">
         <v>0</v>
       </c>
       <c r="C164">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>danilo_marquesc</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B165">
         <v>0</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -15981,13 +15981,13 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>denilson.unit</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B166">
         <v>0</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -15995,7 +15995,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>vieirabjj____</v>
+        <v>danilo_marquesc</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -16009,7 +16009,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>canalgolpebaixo</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -16023,7 +16023,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>leandro__parpinelli</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -16037,7 +16037,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>bruno_pontes1992</v>
+        <v>canalgolpebaixo</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -16051,21 +16051,21 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B171">
         <v>0</v>
       </c>
       <c r="C171">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D171">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>dudaadantass</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -16079,7 +16079,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>mauriciomouraprev</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -16093,7 +16093,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>_pedro0h</v>
+        <v>aida_dos_sonhos</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -16107,7 +16107,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>eliassilverio</v>
+        <v>mauriciomouraprev</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -16116,12 +16116,12 @@
         <v>1</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>andy.techera.12</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -16130,12 +16130,12 @@
         <v>1</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>celiogarcia6</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -16149,7 +16149,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>luluakio</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -16163,7 +16163,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>adriano.trator</v>
+        <v>luluakio</v>
       </c>
       <c r="B179">
         <v>0</v>

--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13378</v>
+        <v>13379</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12113</v>
+        <v>12114</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C5">
         <v>30</v>
       </c>
       <c r="D5">
-        <v>978</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7">
@@ -559,7 +559,7 @@
         <v>rm.nicki</v>
       </c>
       <c r="B12">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1130,30 +1130,30 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>shawlin13oficial</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B53">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>propeace_fight</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B54">
         <v>24</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
@@ -2166,69 +2166,69 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>__bielgg</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127">
         <v>3</v>
-      </c>
-      <c r="D127">
-        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>juanx.pontes</v>
+        <v>__bielgg</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C128">
         <v>3</v>
       </c>
       <c r="D128">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>paxlucta</v>
+        <v>natanborges001</v>
       </c>
       <c r="B129">
+        <v>4</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+      <c r="D129">
         <v>5</v>
-      </c>
-      <c r="C129">
-        <v>6</v>
-      </c>
-      <c r="D129">
-        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>muricunha</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B130">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>erickdiaseds</v>
+        <v>paxlucta</v>
       </c>
       <c r="B131">
         <v>5</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -2236,49 +2236,49 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>muricunha</v>
       </c>
       <c r="B132">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C132">
         <v>0</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>f.luan_11</v>
+        <v>erickdiaseds</v>
       </c>
       <c r="B133">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>dennerfenomeno</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B134">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C134">
         <v>0</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>hellenzinha.alves</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B135">
         <v>7</v>
@@ -2292,83 +2292,83 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>hollenberg.personal</v>
+        <v>dennerfenomeno</v>
       </c>
       <c r="B136">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C136">
         <v>0</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>fredoctmma</v>
+        <v>hellenzinha.alves</v>
       </c>
       <c r="B137">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C137">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>thiagodossantossilvasantos</v>
+        <v>hollenberg.personal</v>
       </c>
       <c r="B138">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C138">
         <v>0</v>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>elienelucindo_oficial</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B139">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C139">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>thiagodossantossilvasantos</v>
       </c>
       <c r="B140">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C140">
         <v>0</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>combatclubsp</v>
+        <v>elienelucindo_oficial</v>
       </c>
       <c r="B141">
         <v>6</v>
       </c>
       <c r="C141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -2376,55 +2376,55 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>edaregiao</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B142">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D142">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>f.ostini</v>
+        <v>combatclubsp</v>
       </c>
       <c r="B143">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>adrianoams7</v>
+        <v>edaregiao</v>
       </c>
       <c r="B144">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>dagestan0920</v>
+        <v>f.ostini</v>
       </c>
       <c r="B145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -2432,97 +2432,97 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>cesar.boanerges</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B146">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>tatibscardoso</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B147">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C147">
         <v>0</v>
       </c>
       <c r="D147">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>olifrankiw</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C148">
         <v>0</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>mayarinhafreestyle</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B149">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C149">
         <v>0</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>aj_mma_</v>
+        <v>olifrankiw</v>
       </c>
       <c r="B150">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>mma.idiot</v>
+        <v>mayarinhafreestyle</v>
       </c>
       <c r="B151">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C151">
         <v>0</v>
       </c>
       <c r="D151">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B152">
         <v>3</v>
       </c>
       <c r="C152">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -2530,58 +2530,58 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ismaeldaniell</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B153">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C153">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>rafaelmacapa_</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B154">
         <v>4</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>daniezzyy</v>
+        <v>rafaelmacapa_</v>
       </c>
       <c r="B155">
         <v>4</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D155">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>natanborges001</v>
+        <v>daniezzyy</v>
       </c>
       <c r="B156">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C156">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -13688,13 +13688,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2337</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="3">
@@ -13730,13 +13730,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6">
@@ -13744,13 +13744,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -13786,7 +13786,7 @@
         <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -13881,44 +13881,44 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>anaaj_camargo</v>
+        <v>propeace_fight</v>
       </c>
       <c r="B16">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>masonharper_mma</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B17">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>propeace_fight</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -14287,21 +14287,21 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>karen.ottoni</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B46">
         <v>5</v>
@@ -14315,80 +14315,80 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>rosiortega</v>
+        <v>natanborges001</v>
       </c>
       <c r="B47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>carlosalbertobarretojr</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>thiagodossantossilvasantos</v>
+        <v>rosiortega</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>anderson.logan.35</v>
+        <v>carlosalbertobarretojr</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>mayarinhafreestyle</v>
+        <v>thiagodossantossilvasantos</v>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>aj_mma_</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -14399,7 +14399,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>decio_bjj</v>
+        <v>mayarinhafreestyle</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -14413,58 +14413,58 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>eolucasrosa</v>
+        <v>decio_bjj</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>mma.idiot</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>daniezzyy</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>natanborges001</v>
+        <v>daniezzyy</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">

--- a/Engagement Rankings 2026-06.xlsx
+++ b/Engagement Rankings 2026-06.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>13379</v>
+        <v>13380</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12114</v>
+        <v>12115</v>
       </c>
     </row>
     <row r="3">
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="7">
@@ -1511,13 +1511,13 @@
         <v>kelly_ottoni</v>
       </c>
       <c r="B80">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C80">
         <v>3</v>
       </c>
       <c r="D80">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
@@ -2138,24 +2138,24 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>biabasiliojj</v>
+        <v>natanborges001</v>
       </c>
       <c r="B125">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>deboralvesoficial</v>
+        <v>biabasiliojj</v>
       </c>
       <c r="B126">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -2166,44 +2166,44 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>aj_mma_</v>
+        <v>deboralvesoficial</v>
       </c>
       <c r="B127">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>__bielgg</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128">
         <v>3</v>
-      </c>
-      <c r="D128">
-        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>natanborges001</v>
+        <v>__bielgg</v>
       </c>
       <c r="B129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C129">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D129">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -2404,63 +2404,63 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>edaregiao</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B144">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C144">
         <v>2</v>
       </c>
       <c r="D144">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>f.ostini</v>
+        <v>edaregiao</v>
       </c>
       <c r="B145">
         <v>4</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>adrianoams7</v>
+        <v>f.ostini</v>
       </c>
       <c r="B146">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>dagestan0920</v>
+        <v>adrianoams7</v>
       </c>
       <c r="B147">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D147">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>cesar.boanerges</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B148">
         <v>5</v>
@@ -2474,35 +2474,35 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>tatibscardoso</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B149">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C149">
         <v>0</v>
       </c>
       <c r="D149">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>olifrankiw</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B150">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C150">
         <v>0</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>mayarinhafreestyle</v>
+        <v>olifrankiw</v>
       </c>
       <c r="B151">
         <v>6</v>
@@ -2516,27 +2516,27 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>mma.idiot</v>
+        <v>mayarinhafreestyle</v>
       </c>
       <c r="B152">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C152">
         <v>0</v>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>mma.idiot</v>
       </c>
       <c r="B153">
         <v>3</v>
       </c>
       <c r="C153">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D153">
         <v>3</v>
@@ -2544,142 +2544,142 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>ismaeldaniell</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C154">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D154">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>rafaelmacapa_</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B155">
         <v>4</v>
       </c>
       <c r="C155">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>daniezzyy</v>
+        <v>rafaelmacapa_</v>
       </c>
       <c r="B156">
         <v>4</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>glm.barbosa</v>
+        <v>daniezzyy</v>
       </c>
       <c r="B157">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>fernando.mma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C158">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D158">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>davizoka_mascote</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B159">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>enzo_henrik</v>
+        <v>davizoka_mascote</v>
       </c>
       <c r="B160">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C160">
         <v>0</v>
       </c>
       <c r="D160">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>emersonriosmma</v>
+        <v>enzo_henrik</v>
       </c>
       <c r="B161">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C161">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>douglasoct_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B162">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C162">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D162">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>eric.shpritz</v>
+        <v>douglasoct_mma</v>
       </c>
       <c r="B163">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C163">
         <v>2</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>victorhenriquebjj</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B199">
         <v>2</v>
@@ -3183,12 +3183,12 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>eduardorobjj</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B200">
         <v>2</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorobjj</v>
       </c>
       <c r="B201">
         <v>2</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>aerowellsports</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B202">
         <v>2</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>royrosiano</v>
+        <v>aerowellsports</v>
       </c>
       <c r="B203">
         <v>2</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>febrancatti</v>
+        <v>royrosiano</v>
       </c>
       <c r="B204">
         <v>2</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>sensei_rogerio_baltazar</v>
+        <v>febrancatti</v>
       </c>
       <c r="B205">
         <v>2</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>jpaulo.mma</v>
+        <v>sensei_rogerio_baltazar</v>
       </c>
       <c r="B206">
         <v>2</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>william_beckett12345</v>
+        <v>jpaulo.mma</v>
       </c>
       <c r="B207">
         <v>2</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>_falcao95_</v>
+        <v>william_beckett12345</v>
       </c>
       <c r="B208">
         <v>2</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>janyson.s</v>
+        <v>_falcao95_</v>
       </c>
       <c r="B209">
         <v>2</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>rodrigo.personal.muaythai</v>
+        <v>janyson.s</v>
       </c>
       <c r="B210">
         <v>2</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>andre_cr_daniel</v>
+        <v>rodrigo.personal.muaythai</v>
       </c>
       <c r="B211">
         <v>2</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>wilsinho.campos</v>
+        <v>andre_cr_daniel</v>
       </c>
       <c r="B212">
         <v>2</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>jheffzao</v>
+        <v>wilsinho.campos</v>
       </c>
       <c r="B213">
         <v>2</v>
@@ -3384,41 +3384,41 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>felipedasilvalucas.bjj</v>
+        <v>jheffzao</v>
       </c>
       <c r="B214">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C214">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D214">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>motumbo_jr</v>
+        <v>felipedasilvalucas.bjj</v>
       </c>
       <c r="B215">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D215">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>julianoalicate</v>
+        <v>motumbo_jr</v>
       </c>
       <c r="B216">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D216">
         <v>1</v>
@@ -3426,13 +3426,13 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>cairorochamma</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B217">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -3440,41 +3440,41 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B218">
         <v>2</v>
       </c>
       <c r="C218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>alexsandra_kairos</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B219">
         <v>2</v>
       </c>
       <c r="C219">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B220">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D220">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>jocyrefan_bjj_mma</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B221">
         <v>3</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>multiplicaaba</v>
+        <v>jocyrefan_bjj_mma</v>
       </c>
       <c r="B222">
         <v>3</v>
@@ -3510,13 +3510,13 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>disk_egg</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C223">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D223">
         <v>0</v>
@@ -3524,80 +3524,80 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>joandersontubarao_ufc</v>
+        <v>disk_egg</v>
       </c>
       <c r="B224">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C224">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D224">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>jean_ferreira_br</v>
+        <v>joandersontubarao_ufc</v>
       </c>
       <c r="B225">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C225">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D225">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>jose_luiz_thome</v>
+        <v>jean_ferreira_br</v>
       </c>
       <c r="B226">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C226">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D226">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>efsantos.oficial</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B227">
         <v>1</v>
       </c>
       <c r="C227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D227">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>ufc_paramountsports</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B228">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>marifferreirac</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B229">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -3608,35 +3608,35 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>pauloserrati</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B230">
         <v>1</v>
       </c>
       <c r="C230">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D230">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>mineirinho_jj</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>juliochagasmma</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B232">
         <v>2</v>
@@ -3650,35 +3650,35 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>orafao1</v>
+        <v>juliochagasmma</v>
       </c>
       <c r="B233">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C233">
         <v>0</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>lopesbrunao</v>
+        <v>orafao1</v>
       </c>
       <c r="B234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C234">
         <v>0</v>
       </c>
       <c r="D234">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>claudiaottoni19</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B235">
         <v>2</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>sr.valter</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B236">
         <v>2</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B237">
         <v>2</v>
@@ -3720,49 +3720,49 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>meol.socialmidia</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B238">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C238">
         <v>0</v>
       </c>
       <c r="D238">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>yamasakinhobjj</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B239">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>mestreviniciusreviravolta</v>
+        <v>yamasakinhobjj</v>
       </c>
       <c r="B240">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>cami28_l</v>
+        <v>mestreviniciusreviravolta</v>
       </c>
       <c r="B241">
         <v>3</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>flaviakaena</v>
+        <v>cami28_l</v>
       </c>
       <c r="B242">
         <v>3</v>
@@ -3790,133 +3790,133 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>chrislima____</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B243">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C243">
         <v>0</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>c.m_figth</v>
+        <v>chrislima____</v>
       </c>
       <c r="B244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C244">
         <v>0</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>c.m_figth</v>
       </c>
       <c r="B245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C245">
         <v>0</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>e_car.doso</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C246">
         <v>0</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>dgswillian</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B247">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C247">
         <v>0</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>couragemma</v>
+        <v>dgswillian</v>
       </c>
       <c r="B248">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C248">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D248">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>kaua_limaofc</v>
+        <v>couragemma</v>
       </c>
       <c r="B249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C249">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ruangzk</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B250">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C250">
         <v>0</v>
       </c>
       <c r="D250">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>emerson_lucaszx</v>
+        <v>ruangzk</v>
       </c>
       <c r="B251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C251">
         <v>0</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>clouddhidden</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B252">
         <v>2</v>
@@ -3930,21 +3930,21 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>_matheusifernandes</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C253">
         <v>0</v>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>bryantank_</v>
+        <v>_matheusifernandes</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>ruan.arcanjo01</v>
+        <v>bryantank_</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>coyote_style_hair</v>
+        <v>ruan.arcanjo01</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,83 +3986,83 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>sueli_ferreira48</v>
+        <v>coyote_style_hair</v>
       </c>
       <c r="B257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C257">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>edsoncostateixeirabjj</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C258">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>klein_hila</v>
+        <v>edsoncostateixeirabjj</v>
       </c>
       <c r="B259">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D259">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>klein_hila</v>
       </c>
       <c r="B260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C260">
         <v>1</v>
       </c>
       <c r="D260">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>vnciuss__df</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B261">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C261">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D261">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B262">
         <v>2</v>
       </c>
       <c r="C262">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>tassiogiloficial</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B263">
         <v>2</v>
@@ -4084,35 +4084,35 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B264">
         <v>2</v>
       </c>
       <c r="C264">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D264">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>richards_brusen</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B265">
         <v>2</v>
       </c>
       <c r="C265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>natalan_wilgner</v>
+        <v>richards_brusen</v>
       </c>
       <c r="B266">
         <v>2</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>leticiamartinspro</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B267">
         <v>2</v>
@@ -4140,69 +4140,69 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>danilo_marquesc</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B268">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D268">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>lucasspaulista</v>
+        <v>danilo_marquesc</v>
       </c>
       <c r="B269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D269">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>lucasspaulista</v>
       </c>
       <c r="B270">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D270">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B271">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D271">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>select_from_joao</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B272">
         <v>2</v>
       </c>
       <c r="C272">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D272">
         <v>0</v>
@@ -4210,41 +4210,41 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>cristianpsicologo</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B273">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C273">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D273">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>fabaotipster</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B274">
         <v>1</v>
       </c>
       <c r="C274">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D274">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B275">
         <v>1</v>
       </c>
       <c r="C275">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D275">
         <v>1</v>
@@ -4252,13 +4252,13 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>helenaseveribjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B276">
         <v>1</v>
       </c>
       <c r="C276">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D276">
         <v>1</v>
@@ -4266,49 +4266,49 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>marciokeske</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B277">
         <v>1</v>
       </c>
       <c r="C277">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>ommariotti</v>
+        <v>marciokeske</v>
       </c>
       <c r="B278">
         <v>1</v>
       </c>
       <c r="C278">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D278">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>felipebunesufc</v>
+        <v>ommariotti</v>
       </c>
       <c r="B279">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C279">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>icarohilton</v>
+        <v>felipebunesufc</v>
       </c>
       <c r="B280">
         <v>2</v>
@@ -4322,35 +4322,35 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>jesabelmelo9</v>
+        <v>icarohilton</v>
       </c>
       <c r="B281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>iranbez</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B282">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C282">
         <v>1</v>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>sthe._.araujo</v>
+        <v>iranbez</v>
       </c>
       <c r="B283">
         <v>2</v>
@@ -4364,13 +4364,13 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>clayton77silva</v>
+        <v>sthe._.araujo</v>
       </c>
       <c r="B284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C284">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -4378,13 +4378,13 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>raycon_mma</v>
+        <v>clayton77silva</v>
       </c>
       <c r="B285">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C285">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>sarahfmaia</v>
+        <v>raycon_mma</v>
       </c>
       <c r="B286">
         <v>2</v>
@@ -4406,13 +4406,13 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>sarahfmaia</v>
       </c>
       <c r="B287">
         <v>2</v>
       </c>
       <c r="C287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D287">
         <v>0</v>
@@ -4420,35 +4420,35 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B288">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C288">
         <v>0</v>
       </c>
       <c r="D288">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>aliferpaulo_</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B289">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C289">
         <v>0</v>
       </c>
       <c r="D289">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>sambagabrieloficial</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B290">
         <v>2</v>
@@ -4462,35 +4462,35 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>raelduraes</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B291">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C291">
         <v>0</v>
       </c>
       <c r="D291">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>martta.mariah</v>
+        <v>raelduraes</v>
       </c>
       <c r="B292">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C292">
         <v>0</v>
       </c>
       <c r="D292">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B293">
         <v>2</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>_bety_marcal</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B294">
         <v>2</v>
@@ -4518,13 +4518,13 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B295">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C295">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D295">
         <v>0</v>
@@ -4532,13 +4532,13 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>wesley_bjjvc</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C296">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B297">
         <v>2</v>
@@ -4560,21 +4560,21 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B298">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C298">
         <v>0</v>
       </c>
       <c r="D298">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B299">
         <v>1</v>
@@ -4588,21 +4588,21 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>fabi.godooy</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B300">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C300">
         <v>0</v>
       </c>
       <c r="D300">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>davicorbella</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B301">
         <v>2</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>joegam3r</v>
+        <v>davicorbella</v>
       </c>
       <c r="B302">
         <v>2</v>
@@ -4630,35 +4630,35 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>graalino</v>
+        <v>joegam3r</v>
       </c>
       <c r="B303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C303">
         <v>0</v>
       </c>
       <c r="D303">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>ramanatoscanellibjj</v>
+        <v>graalino</v>
       </c>
       <c r="B304">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C304">
         <v>0</v>
       </c>
       <c r="D304">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>mariabeltapagani</v>
+        <v>ramanatoscanellibjj</v>
       </c>
       <c r="B305">
         <v>2</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>auriceliaribeiro_</v>
+        <v>mariabeltapagani</v>
       </c>
       <c r="B306">
         <v>2</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>craig_cohen1</v>
+        <v>auriceliaribeiro_</v>
       </c>
       <c r="B307">
         <v>2</v>
@@ -4700,35 +4700,35 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>glessios_silva</v>
+        <v>craig_cohen1</v>
       </c>
       <c r="B308">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C308">
         <v>0</v>
       </c>
       <c r="D308">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>fabioincalado</v>
+        <v>glessios_silva</v>
       </c>
       <c r="B309">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C309">
         <v>0</v>
       </c>
       <c r="D309">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>vanderleiamellogois</v>
+        <v>fabioincalado</v>
       </c>
       <c r="B310">
         <v>2</v>
@@ -4742,91 +4742,91 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>pedrinhosbjj</v>
+        <v>vanderleiamellogois</v>
       </c>
       <c r="B311">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C311">
         <v>0</v>
       </c>
       <c r="D311">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>_jaquealms</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C312">
         <v>0</v>
       </c>
       <c r="D312">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>caio.fermianoo</v>
+        <v>_jaquealms</v>
       </c>
       <c r="B313">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C313">
         <v>0</v>
       </c>
       <c r="D313">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>corrozzzive</v>
+        <v>caio.fermianoo</v>
       </c>
       <c r="B314">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C314">
         <v>0</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>araujojonaspenhade</v>
+        <v>corrozzzive</v>
       </c>
       <c r="B315">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C315">
         <v>0</v>
       </c>
       <c r="D315">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>duuleitee</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B316">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C316">
         <v>0</v>
       </c>
       <c r="D316">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>pvd_._dudis</v>
+        <v>duuleitee</v>
       </c>
       <c r="B317">
         <v>2</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B318">
         <v>2</v>
@@ -4854,21 +4854,21 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>tatianeaguiarp</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B319">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C319">
         <v>0</v>
       </c>
       <c r="D319">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>ottonhona</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B320">
         <v>1</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>alcateiaartesmarciais</v>
+        <v>ottonhona</v>
       </c>
       <c r="B321">
         <v>1</v>
@@ -4896,49 +4896,49 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>marcov__7</v>
+        <v>alcateiaartesmarciais</v>
       </c>
       <c r="B322">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C322">
         <v>0</v>
       </c>
       <c r="D322">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>anachierico_</v>
+        <v>marcov__7</v>
       </c>
       <c r="B323">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C323">
         <v>0</v>
       </c>
       <c r="D323">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>toraostreet</v>
+        <v>anachierico_</v>
       </c>
       <c r="B324">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C324">
         <v>0</v>
       </c>
       <c r="D324">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>bears635</v>
+        <v>toraostreet</v>
       </c>
       <c r="B325">
         <v>2</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>vivi_fitnees</v>
+        <v>bears635</v>
       </c>
       <c r="B326">
         <v>2</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>shockmonteiro</v>
+        <v>vivi_fitnees</v>
       </c>
       <c r="B327">
         <v>2</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>murilomuaythai</v>
+        <v>shockmonteiro</v>
       </c>
       <c r="B328">
         <v>2</v>
@@ -4994,35 +4994,35 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>suel.f1270</v>
+        <v>murilomuaythai</v>
       </c>
       <c r="B329">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C329">
         <v>0</v>
       </c>
       <c r="D329">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>thiagoxavier13</v>
+        <v>suel.f1270</v>
       </c>
       <c r="B330">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C330">
         <v>0</v>
       </c>
       <c r="D330">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>fatima_trindade_</v>
+        <v>thiagoxavier13</v>
       </c>
       <c r="B331">
         <v>2</v>
@@ -5036,21 +5036,21 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>gillesarquitetura</v>
+        <v>fatima_trindade_</v>
       </c>
       <c r="B332">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C332">
         <v>0</v>
       </c>
       <c r="D332">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>alvestank</v>
+        <v>gillesarquitetura</v>
       </c>
       <c r="B333">
         <v>1</v>
@@ -5064,35 +5064,35 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>marciooangelo</v>
+        <v>alvestank</v>
       </c>
       <c r="B334">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C334">
         <v>0</v>
       </c>
       <c r="D334">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>adevaldojr_</v>
+        <v>marciooangelo</v>
       </c>
       <c r="B335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C335">
         <v>0</v>
       </c>
       <c r="D335">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>rosacostasousa36</v>
+        <v>adevaldojr_</v>
       </c>
       <c r="B336">
         <v>1</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>manucanecorso.bjj</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B337">
         <v>1</v>
@@ -5120,63 +5120,63 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>claudiaottoni2025</v>
+        <v>manucanecorso.bjj</v>
       </c>
       <c r="B338">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C338">
         <v>0</v>
       </c>
       <c r="D338">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>tavin.mendes</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B339">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C339">
         <v>0</v>
       </c>
       <c r="D339">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>tavin.mendes</v>
       </c>
       <c r="B340">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C340">
         <v>0</v>
       </c>
       <c r="D340">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>fabiieju</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B341">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C341">
         <v>0</v>
       </c>
       <c r="D341">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>marqueswanderson</v>
+        <v>fabiieju</v>
       </c>
       <c r="B342">
         <v>1</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>adauto2505</v>
+        <v>marqueswanderson</v>
       </c>
       <c r="B343">
         <v>1</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>joaogagoarta</v>
+        <v>adauto2505</v>
       </c>
       <c r="B344">
         <v>1</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>npb.enterprise</v>
+        <v>joaogagoarta</v>
       </c>
       <c r="B345">
         <v>1</v>
@@ -13688,13 +13688,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2338</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="3">
@@ -13744,13 +13744,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -14122,13 +14122,13 @@
         <v>kelly_ottoni</v>
       </c>
       <c r="B33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -14287,44 +14287,44 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>aj_mma_</v>
+        <v>natanborges001</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>natanborges001</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -14679,7 +14679,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>jheffzao</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -14688,46 +14688,46 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>jvxz______</v>
+        <v>jheffzao</v>
       </c>
       <c r="B74">
         <v>2</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>julianoalicate</v>
+        <v>jvxz______</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75">
         <v>1</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>cairorochamma</v>
+        <v>julianoalicate</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -14735,24 +14735,24 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>victus_torquatus</v>
+        <v>cairorochamma</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>efsantos.oficial</v>
+        <v>victus_torquatus</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -14763,105 +14763,105 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ufc_paramountsports</v>
+        <v>efsantos.oficial</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>hollenberg.personal</v>
+        <v>ufc_paramountsports</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>leo.ribeiro.bjj</v>
+        <v>hollenberg.personal</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>marcos_tailandess</v>
+        <v>leo.ribeiro.bjj</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>e_car.doso</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
         <v>3</v>
       </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
       <c r="D83">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>gdazuera</v>
+        <v>e_car.doso</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>jose_luiz_thome</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>dgswillian</v>
+        <v>gdazuera</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -14875,10 +14875,10 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>ryangandraufc</v>
+        <v>jose_luiz_thome</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -14889,63 +14889,63 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>dgswillian</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>fredoctmma</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>emersonriosmma</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>fatima_trindade_</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -14959,13 +14959,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>marcosferreira.ofc1</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B93">
         <v>2</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -14973,7 +14973,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>pedromadeira.s</v>
+        <v>fatima_trindade_</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -14987,7 +14987,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>flaviakaena</v>
+        <v>marcosferreira.ofc1</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -15001,35 +15001,35 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>gillesarquitetura</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>alvestank</v>
+        <v>flaviakaena</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gillesarquitetura</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -15043,21 +15043,21 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>marciooangelo</v>
+        <v>alvestank</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>peacegrappler_archive</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -15071,21 +15071,21 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>adevaldojr_</v>
+        <v>marciooangelo</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>rosacostasousa36</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -15099,7 +15099,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>helenaseveribjj</v>
+        <v>adevaldojr_</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -15113,7 +15113,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>manucanecorso.bjj</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -15127,21 +15127,21 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>claudiaottoni2025</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>claudiaottoni19</v>
+        <v>manucanecorso.bjj</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -15155,63 +15155,63 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>tavin.mendes</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
         <v>0</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>eric.shpritz</v>
+        <v>claudiaottoni19</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
         <v>0</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ellen.cristinaaa</v>
+        <v>tavin.mendes</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>fabiieju</v>
+        <v>ellen.cristinaaa</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
         <v>0</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>marqueswanderson</v>
+        <v>fabiieju</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -15225,7 +15225,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>adauto2505</v>
+        <v>marqueswanderson</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -15239,7 +15239,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>joaogagoarta</v>
+        <v>adauto2505</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -15253,7 +15253,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>npb.enterprise</v>
+        <v>joaogagoarta</v>
       </c>
       <c r="B114">
         <v>1</v>
